--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="373">
   <si>
     <t>번호</t>
   </si>
@@ -192,7 +192,7 @@
     <t>005</t>
   </si>
   <si>
-    <t>개인회생, 신용회복위원회, 신복위, 차이, 비교, 다른 제도</t>
+    <t>개인회생, 신용회복위원회, 신복위, 차이, 비교, 다른 제도, 워크아웃, 개인워크아웃</t>
   </si>
   <si>
     <t>다른 채무조정 제도(법원 개인회생, 신용회복위원회)와 다른 점이 있나요?</t>
@@ -244,7 +244,7 @@
     <t>007</t>
   </si>
   <si>
-    <t>신청방법, 온라인, 홈페이지, 창구, 방문, 어디서</t>
+    <t>신청방법, 온라인, 홈페이지, 창구, 방문, 어디서, 접수, 신청하는 법, 신청 장소</t>
   </si>
   <si>
     <t>신청은 어떻게 하나요?</t>
@@ -365,7 +365,7 @@
     <t>012</t>
   </si>
   <si>
-    <t>채무조정안, 2주, 지연, 늦음, 안 와요</t>
+    <t>채무조정안, 2주, 지연, 늦음, 안 와요, 채무조정안 지연, 결과 안 나와요</t>
   </si>
   <si>
     <t>채무조정안 제시</t>
@@ -436,7 +436,7 @@
     <t>015</t>
   </si>
   <si>
-    <t>취소, 신청취소, 재신청, 90일</t>
+    <t>취소, 신청취소, 재신청, 90일, 철회, 신청철회, 신청 취소</t>
   </si>
   <si>
     <t>신청·서류 제출</t>
@@ -489,7 +489,7 @@
     <t>017</t>
   </si>
   <si>
-    <t>지원대상, 소상공인, 자영업자, 법인, 폐업법인</t>
+    <t>지원대상, 소상공인, 자영업자, 법인, 폐업법인, 자격, 누가, 대상자</t>
   </si>
   <si>
     <t>소상공인ㆍ자영업자만 지원 대상인가요?</t>
@@ -544,7 +544,7 @@
     <t>019</t>
   </si>
   <si>
-    <t>대상채무, 가계대출, 사업자대출, 신규대출, 모든 대출</t>
+    <t>대상채무, 가계대출, 사업자대출, 신규대출, 모든 대출, 대출종류, 어떤 대출</t>
   </si>
   <si>
     <t>보유하고 있는 모든 대출이 지원 가능한가요?</t>
@@ -619,7 +619,7 @@
     <t>022</t>
   </si>
   <si>
-    <t>경매, 강제집행, 추심중단, 법조치, 압류</t>
+    <t>경매, 강제집행, 추심중단, 법조치, 압류, 경매 중지, 소송</t>
   </si>
   <si>
     <t>새출발기금 신청 시 진행 중이던 금융기관의 법조치는 어떻게 되나요?</t>
@@ -645,7 +645,7 @@
     <t>023</t>
   </si>
   <si>
-    <t>추심, 독촉, 계속, 상계, 연락</t>
+    <t>추심, 독촉, 계속, 상계, 연락, 독촉전화, 빚독촉, 추심 중단</t>
   </si>
   <si>
     <t>새출발기금 신청 이후에도 추심이 계속 진행되고 있어요.</t>
@@ -700,7 +700,7 @@
     <t>025</t>
   </si>
   <si>
-    <t>원금감면, 감면, 탕감, 깎아</t>
+    <t>원금감면, 감면, 탕감, 깎아, 원금, 빚 탕감, 감면율</t>
   </si>
   <si>
     <t>무담보</t>
@@ -781,7 +781,7 @@
     <t>028</t>
   </si>
   <si>
-    <t>상환기간, 기간변경, 중도상환, 조기상환</t>
+    <t>상환기간, 기간변경, 중도상환, 조기상환, 기간 연장, 미리 갚기</t>
   </si>
   <si>
     <t>상환 중</t>
@@ -806,7 +806,7 @@
     <t>029</t>
   </si>
   <si>
-    <t>공공정보, 신용정보, 해제, 신용회복, 신용등급</t>
+    <t>공공정보, 신용정보, 해제, 신용회복, 신용등급, 신용점수, 연체기록, 기록 삭제</t>
   </si>
   <si>
     <t>신용정보</t>
@@ -853,6 +853,303 @@
     <t>새출발기금 홈페이지 자주하는 질문 &gt; 도덕적해이 (https://www.newstartfund.or.kr/Faq/List.do)</t>
   </si>
   <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>협약기관, 협약 금융기관, 금융기관 조회, 가입기관, 협약 확인, 미협약</t>
+  </si>
+  <si>
+    <t>새출발기금 협약 금융기관은 어디서 확인할 수 있나요?</t>
+  </si>
+  <si>
+    <t>협약에 가입한 금융기관 목록은 새출발기금 홈페이지 '금융기관 조회'에서 확인한다. 협약 가입 금융기관의 대출만 채무조정 대상이며, 가입 여부는 각 금융기관이 스스로 정한다. 지원이 어려우면 신복위 개인워크아웃·법원 회생 등 다른 채무조정 제도를 이용한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 새출발기금 협약 가입 채권금융기관 목록은 새출발기금 홈페이지 ‘금융기관 조회’를 통해 확인 가능합니다.
+□ 새출발기금은 신청 차주가 보유한 대출 중 「새출발기금 지원 협약」에 가입한 채권금융기관 대출채권에 대해 채무조정을 지원하고 있으며, 협약 가입여부는 각 채권금융기관의 자율적인 의사결정에 따라 결정됩니다.
+ㅇ 새출발기금을 통한 지원이 어려우실 경우, 타 채무조정 제도(신복위 개인워크아웃 및 법원 회생 등)를 이용하여 주시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>금융기관 조회, 협약 가입 금융기관</t>
+  </si>
+  <si>
+    <t>모든 금융기관 대출이 다 지원됩니다</t>
+  </si>
+  <si>
+    <t>새출발기금 홈페이지 '금융기관 조회'</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>재기지원, 성실상환자, 재도전, 도약지원금, 노란우산, 지원사업, 추가지원</t>
+  </si>
+  <si>
+    <t>채무조정 외에 지원이 있나요?</t>
+  </si>
+  <si>
+    <t>채무조정 성실상환자를 대상으로 유관기관과 함께 재기지원 사업(재도전 교육, 재도전 특별자금 등 종합패키지, 도약지원금, 경영환경개선 등)을 운영한다. 새출발기금 웹플랫폼 공지와 알림톡으로 안내하며, 조기 마감·종료될 수 있고 보증·대출은 지원기관 기준으로 최종 결정된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 새출발기금은 유관기관과 연계하여 채무조정 성실상환자를 대상으로 다양한 재기지원 사업을 운영하고 있습니다.
+ㅇ 2024년부터 신용보증재단중앙회, 소상공인시장진흥공단과 함께 재도전 교육, 채무해소 재기지원 종합패키지(재도전 특별자금 등 9가지 프로그램)를 운영하고 있으며,
+ㅇ 2025년에는 중소기업중앙회(노란우산), 소상공인연합회, 부산시와 협업하여 도약지원금 및 경영환경개선 등의 재기지원 사업을 운영하고 있습니다.
+ㅇ 새출발기금 성실상환자 재기지원 사업은 새출발기금 웹플랫폼을 통한 공지 및 개별 알림톡 등으로 안내드리고 있사오니 향후 많은 신청 바랍니다.
+※ 새출발기금 성실상환자 재기지원 사업은 신청 상황에 따라 조기 마감 및 사업 종료될 수 있으며, 특히, 보증 및 대출지원의 경우 지원기관 기준에 따라 최종 지원 여부가 결정됨을 참고하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>성실상환자 재기지원 사업, 웹플랫폼 공지</t>
+  </si>
+  <si>
+    <t>신청하시면 자금 지원을 꼭 받으실 수 있습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 웹플랫폼 공지</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>개인회생, 회생폐지, 폐지 후 신청, 회생중, 회생 취소, 전환</t>
+  </si>
+  <si>
+    <t>새출발기금 접수 기간 중 개인회생을 폐지하고 새출발기금을 신청할 수 있나요?</t>
+  </si>
+  <si>
+    <t>지원 대상이고 보유 채무도 지원 대상이면 개인회생을 폐지한 뒤 새출발기금을 신청할 수 있다. 두 제도는 특징과 방식이 달라 본인 상황에 유리한 제도를 고르도록 안내한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 귀하께서 새출발기금의 지원 대상에 해당하며, 보유하신 채무가 새출발기금 지원 대상에 해당하는 경우, 개인회생 제도 폐지 후 새출발기금 신청이 가능합니다.
+ㅇ 다만, 개인회생 제도와 새출발기금의 채무조정은 특징과 방식이 상이하므로 고객님의 상황을 고려하여 유리한 제도를 선택하시기를 당부드립니다.</t>
+  </si>
+  <si>
+    <t>개인회생 폐지 후 신청, 유리한 제도 선택</t>
+  </si>
+  <si>
+    <t>새출발기금이 무조건 더 유리합니다</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>사업자 2개, 사업자 두 개, 복수사업자, 사업장 여러 개, 대표자, 개인과 법인</t>
+  </si>
+  <si>
+    <t>한명의 대표자가 사업자 2개를 운영하는 경우, 모두 신청이 가능한가요?</t>
+  </si>
+  <si>
+    <t>한 대표자가 개인사업자와 법인 소상공인을 각각 운영하면 사업자별로 신청할 수 있다. 개인사업자 사업장 두 곳을 운영하면 1개 사업자로 1회만 신청할 수 있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 한명의 대표자가 개인사업자와 법인 소상공인 두 가지 사업자를 각각 운영하는 경우, 각 사업자로  신청 가능합니다.
+ㅇ 다만, 한명의 대표자가 두 개의 개인사업자 사업장을 운영하는 경우, 1개의 사업자로 1회에 한하여 신청 가능합니다.</t>
+  </si>
+  <si>
+    <t>사업자별 신청, 1개 사업자 1회</t>
+  </si>
+  <si>
+    <t>사업장마다 따로 신청하시면 됩니다</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>외국인, 외국 국적, 국적, 체류</t>
+  </si>
+  <si>
+    <t>외국인도 채무조정 신청이 가능한가요?</t>
+  </si>
+  <si>
+    <t>외국인도 사업자등록증을 갖고 지원기간 안에 사업을 하는 등 지원 대상에 해당하면 채무조정을 신청할 수 있다. 단계별 심사 기준을 통과해야 채무조정을 받을 수 있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 외국인에 경우에도 사업자등록증을 보유하고 지원기간 내 사업을 영위하는 등 새출발기금 지원 대상에 해당되는 경우, 채무조정 신청이 가능합니다.
+ㅇ 다만, 지원 단계별 엄격한 심사 기준을 통과하는 경우에 한하여 채무조정 혜택을 부여하여 도덕적 해이 발생을 방지하고 있습니다.</t>
+  </si>
+  <si>
+    <t>사업자등록증, 단계별 심사</t>
+  </si>
+  <si>
+    <t>외국인은 신청할 수 없습니다</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>소상공인확인서, 확인서, 소진공, 착한임대인, 서류, 중소기업현황정보시스템</t>
+  </si>
+  <si>
+    <t>소상공인시장진흥공단(이하 “소진공”)에서 발급한 소상공인확인서도 가능한가요?</t>
+  </si>
+  <si>
+    <t>소상공인시장진흥공단(소진공)에서 발급한 소상공인확인서는 쓸 수 없다. 착한임대인 세제혜택용이라 일반 소상공인확인서와 다르다(참고: 중소기업현황정보시스템 sminfo.mss.go.kr).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 불가능합니다. 소진공에서 발급한 소상공인확인서는 착한임대인 세제해택을 위한 것으로, 일반적인 소상공인확인서와 다릅니다.
+* 중소기업현황정보시스템 (sminfo.mss.go.kr)</t>
+  </si>
+  <si>
+    <t>중소기업현황정보시스템, 일반 소상공인확인서</t>
+  </si>
+  <si>
+    <t>소진공 확인서를 내셔도 됩니다</t>
+  </si>
+  <si>
+    <t>중소기업현황정보시스템 (sminfo.mss.go.kr)</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>중복조회, 중복, 두 번 조회, 채무내역, 같은 대출, 채무조회</t>
+  </si>
+  <si>
+    <t>채무조정 신청 시 채무가 중복 조회되는 이유는 무엇인가요?</t>
+  </si>
+  <si>
+    <t>채무내역을 조회하면 대출정보와 그 대출의 연체정보가 함께 나와 중복처럼 보인다. 진행 과정에서 금융회사와 확인 절차를 거치므로 약정할 때 대상 채무를 정확히 확인할 수 있다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 채무내역 조회시 대출정보와 대출 중 연체된 건의 연체정보가 함께 조회됩니다.
+ㅇ 채무조정 진행 과정에서 채권금융회사와 대출에 대한 확인 절차를 거치고 있으므로 채무조정 약정시에는 채무조정 대상 채무를 명확히 확인하실 수 있습니다.</t>
+  </si>
+  <si>
+    <t>대출정보와 연체정보 함께 조회, 약정 시 확인</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>부동의, 동의 안 함, 담보대출, 중개형, 채권매입, 금융회사 거절</t>
+  </si>
+  <si>
+    <t>담보</t>
+  </si>
+  <si>
+    <t>담보대출 채권기관이 채무조정을 부동의하면 채무조정 진행은 어떻게 되나요?</t>
+  </si>
+  <si>
+    <t>부동산 등 담보대출은 먼저 신용회복위원회 중개형 채무조정으로 지원하고, 금융회사가 부동의하면 새출발기금이 그 채권을 사들여 중개형 채무조정에 참여하는 방식으로 지원한다. 미협약기관 대출, 개인 자산형성 목적 대출 등 지원 제외 대출은 지원이 어렵다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 부동산 등 담보대출 채무조정의 경우, 신용회복위원회를 통한 중개형 채무조정으로 우선 지원하고 채권 금융회사가 중개형 채무조정에 부동의하는 경우에는 새출발기금에서 해당 채권을 매입하여 중개형 채무조정 프로그램에 참여하는 방식으로 채무조정을 지원해드립니다.
+□ 다만, 미협약기관 대출, 개인 자산형성 목적의 대출 등 새출발기금 지원 제외 대출은 지원이 어렵습니다.</t>
+  </si>
+  <si>
+    <t>중개형 채무조정, 채권 매입</t>
+  </si>
+  <si>
+    <t>금융회사가 부동의하면 채무조정이 끝납니다</t>
+  </si>
+  <si>
+    <t>신용회복위원회</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>가압류, 압류해제, 법조치 해제, 해제, 풀어, 경매취소</t>
+  </si>
+  <si>
+    <t>새출발기금 신청 전 이미 진행된 금융기관 법조치를 해제하고 싶어요.</t>
+  </si>
+  <si>
+    <t>신청 전에 금융회사가 걸어 둔 가압류 등 법조치는 신청만으로 풀리지 않는다. 원칙적으로 약정 후 채무를 다 갚아야 해제되고, 예외적으로 해당 재산가치 이상을 갚으면 해제할 수 있으며 그 금액은 약정 때 산정된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 새출발기금 신청 전 채권금융회사가 설정한 가압류 등의 법조치 해제를 원하시는 경우, 원칙적으로 채무조정 약정 후 채무를 완제하셔야 가능하며, 새출발기금 신청만으로 해제할 수 없습니다.
+ㅇ 다만, 예외적으로 해당 재산가치* 이상 변제 후 해제 가능하오며, 법적조치 해제를 위한 변제금액은 채무조정 약정 체결 시 산정됩니다.
+* 재산가치 추정 평가액에서 등기되어있는 선순위 동순위 채권액(압류, (근)저당등)의 실체납, 채무 잔액 및 임차보증금 등을 공제한 금액</t>
+  </si>
+  <si>
+    <t>약정 후 완제, 재산가치 이상 변제</t>
+  </si>
+  <si>
+    <t>신청하시면 가압류가 바로 풀립니다</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>매입형, 중개형, 방식, 채무조정 방식, 대출유형, 진행방식</t>
+  </si>
+  <si>
+    <t>새출발기금 채무조정 방식에 대해 설명해주세요.</t>
+  </si>
+  <si>
+    <t>대출 유형에 따라 방식이 다르다. 부실차주의 보증·신용 채무는 매입형, 부실차주의 담보채무와 부실우려차주의 담보·보증·신용 채무는 중개형으로 채무조정이 진행된다.</t>
+  </si>
+  <si>
+    <t>□ 새출발기금은 신청자의 대출 유형에 따라 ①부실차주 보증·신용 채무는 매입형, ②부실차주 담보채무 및 부실우려차주 담보·보증·신용채무는 중개형으로 채무조정이 진행됩니다.</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>카드론, 카드대금, 카드사용대금, 현금서비스, 신용카드, 카드빚</t>
+  </si>
+  <si>
+    <t>카드론 및 카드사용대금, 현금서비스도 지원대상인가요?</t>
+  </si>
+  <si>
+    <t>협약 금융회사가 가진 카드론·카드사용대금·현금서비스도 새출발기금 지원 대상 채권에 해당하면 지원받을 수 있다.</t>
+  </si>
+  <si>
+    <t>□ 협약금융회사가 보유 중인 카드론 및 카드사용대금, 현금서비스에 대해서는 새출발기금 지원대상채권에 해당하는 경우 지원 가능합니다.</t>
+  </si>
+  <si>
+    <t>카드론, 현금서비스, 협약 금융회사</t>
+  </si>
+  <si>
+    <t>카드빚은 지원되지 않습니다</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>도덕적해이, 이의신청, 재심사, 심사결과, 불복, 지원제외</t>
+  </si>
+  <si>
+    <t>도덕적 해이 심사 결과에 대해 이의신청이 가능한가요?</t>
+  </si>
+  <si>
+    <t>도덕적 해이 심사 결과에 이의가 있으면 이의신청할 수 있다. 재심사에서도 지원 제외로 결정되면 추가 심사는 어렵다.</t>
+  </si>
+  <si>
+    <t>□ 도덕적 해이 심사 결과에 이의가 있으신 경우 이의 신청 가능하오나, 재심사에도 지원 제외 결정된 경우, 추가 심사는 어렵습니다.</t>
+  </si>
+  <si>
+    <t>이의신청, 재심사</t>
+  </si>
+  <si>
+    <t>몇 번이고 다시 심사받으실 수 있습니다</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>재산조사, 은닉재산, 약정 후 조사, 무효, 도덕적해이, 사후조사</t>
+  </si>
+  <si>
+    <t>채무조정 약정 체결 이후에도 도덕적 해이 조사가 진행되나요?</t>
+  </si>
+  <si>
+    <t>약정 이후에도 약정자를 대상으로 정기적으로 재산 조사를 해 은닉재산 등을 살핀다. 은닉재산 등이 발견되면 원금조정 등 기존 채무조정이 무효가 되고 채권회수 절차가 진행된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">□ 새출발기금은 채무조정 약정 체결 이후에도 약정자를 대상으로 정기적 재산 조사를 진행하여 은닉재산 등을 조사합니다.
+ㅇ 이에 따라, 은닉재산 등이 발견되는 즉시 원금조정 등 기존 채무조정은 무효 처리되고 채권회수 절차가 진행됩니다.</t>
+  </si>
+  <si>
+    <t>정기적 재산 조사, 채무조정 무효</t>
+  </si>
+  <si>
+    <t>약정하고 나면 더 조사하지 않습니다</t>
+  </si>
+  <si>
     <t>버튼</t>
   </si>
   <si>
@@ -895,7 +1192,7 @@
     <t>자료 출처</t>
   </si>
   <si>
-    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 중 30건 (https://www.newstartfund.or.kr/Faq/List.do, 2026-10-28 확인)</t>
+    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인)</t>
   </si>
   <si>
     <t>홈페이지에 게시된 답변을 그대로 옮긴 칸. 근거 정확도 확인은 이 칸과 대조한다.</t>
@@ -1311,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2973,9 +3270,698 @@
         <v>31</v>
       </c>
     </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2990,10 +3976,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>256</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>257</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3001,7 +3987,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>258</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3009,7 +3995,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3017,7 +4003,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>260</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3025,7 +4011,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>261</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3033,28 +4019,28 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>262</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>263</v>
+        <v>357</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>264</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3069,18 +4055,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>267</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>268</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3088,7 +4074,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3096,7 +4082,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3104,15 +4090,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3120,19 +4106,19 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="393">
   <si>
     <t>번호</t>
   </si>
@@ -160,6 +160,9 @@
 ㅇ 연체일수가 10일 미만이면서,1 폐업 또는 6개월 이상 휴업한자, 2국세 지방세 체납으로 공공기록정보가 등재된 자 등을 의미합니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제6·7호: 부실차주는 1개 이상 채무가 3개월 이상 연체 중인 차주, 부실우려차주는 부실차주가 아니면서 금융회사 분류상 '요주의' 이하 등 장기연체 우려가 있는 차주</t>
+  </si>
+  <si>
     <t>부실차주, 부실우려차주, 연체일수</t>
   </si>
   <si>
@@ -259,6 +262,9 @@
   * 신용회복위원회 서민금융통합지원센터(전국 50개소)</t>
   </si>
   <si>
+    <t>관리업무요강 제11조①: 새출발기금 온라인 플랫폼으로 신청하고, 온라인 이용이 어려우면 상담창구 등으로 신청할 수 있음</t>
+  </si>
+  <si>
     <t>새출발기금.kr, 캠코 상담 창구, 신용회복위원회 방문</t>
   </si>
   <si>
@@ -356,6 +362,9 @@
 □ 신용회복위원회 채무조정, 법원 개인회생, 새출발기금 채무조정 등 신용회복지원제도가 상이하므로 각 제도별 특징을 확인 후 고객님께 유리한 제도를 선택하시기를 당부드립니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제32조 제4·5호: 약정 후 파산·개인회생을 신청하거나 신용회복위원회 채무조정을 신청하면 채무조정 효력이 상실됨</t>
+  </si>
+  <si>
     <t>제도별 특징 비교</t>
   </si>
   <si>
@@ -378,6 +387,9 @@
   </si>
   <si>
     <t>□ 신청량 증가로 2주안에 채무조정(안)을 받아보지 못한 경우가 있을 수 있고, 개인정보(선택적동의정보)를 동의하지 않아 재동의 절차 진행 등으로 시간이 추가 소요되는 경우도 있습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제15조①: 신청을 마치면 신청일 다음날부터 2주일 이내에 채무조정임시안을 제시함</t>
   </si>
   <si>
     <t>신청량 증가, 선택적 동의 재동의</t>
@@ -454,6 +466,9 @@
 □ 새출발기금은 고의적, 반복적 신청을 제한하기 위해 신청 취소일로부터 3개월(90일)간 재신청이 불가능합니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제16조: 신청을 완료한 달의 다음 달 15일까지 취소할 수 있고, 취소하면 취소 신청일부터 3개월간 재신청이 제한됨</t>
+  </si>
+  <si>
     <t>익월 15일, 확정 전, 90일 재신청 제한</t>
   </si>
   <si>
@@ -478,6 +493,9 @@
     <t xml:space="preserve">□ 부실우려차주의 채무조정약정 효력이 미납 등의 사유로 실효되는 경우, 새출발기금이 채권을 매입해 채무조정을 진행하며, 당시에 포함하지 않았던 대출*도 신청할 수 있으니
 * 새출발기금 지원 대상 대출에 한함. (개인자산형성 목적 대출 등은 지원 제외)
 ㅇ 새출발기금 고객센터로 전화주셔서 미신청 채무를 신청하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제19조③: 부실우려차주가 3개월 이상 연체 등으로 약정 효력이 상실되면 매입형 채무조정으로 진행하고 채무부담액은 부실차주 기준으로 산정함</t>
   </si>
   <si>
     <t>실효 후 매입, 미신청 채무 추가</t>
@@ -631,6 +649,9 @@
     <t xml:space="preserve">□ 새출발기금은 신청자의 채무조정 신청 익일에 채권금융회사에 신청 사실을 통지하고 추심 중단을 요청하며, 채권금융회사는 새출발기금 협약에 따라 지원 대상자에 대한 추심을 중단하고 담보물에 대한 강제집행ㆍ임의경매 등을 중지하여야 합니다.
 ㅇ 다만, 이는 새출발기금 협약기관에 한하여 적용되는 내용으로, 제3자에 의해 진행되는 추심 및 강제집행ㆍ임의경매는 중지되지 않습니다.
 ㅇ 또한, 새출발기금 신청 전 매각기일 등이 지정되어 진행되고 있던 강제집행ㆍ임의경매의 경우, 새출발기금 신청만으로 중지할 수 없으므로, 신청자와 금융기관 간 개별 협의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>새출발기금 지원 협약 / 관리업무요강 제13조: 신청을 완료한 다음 영업일 이내에 금융회사에 추심·강제경매·임의경매 등의 중지를 요청함</t>
   </si>
   <si>
     <t>추심 중단, 매각기일, 개별 협의</t>
@@ -664,6 +685,9 @@
 □ 새출발기금 협약기관에서 위의 내용 외 채권 추심이 진행될 경우, 해당 금융기관에 새출발기금 신청 사실을 고지하시고 중단 요청하시기 바라며, 이후에도 협조가 되지 않을 경우 새출발기금으로 문의하시기 바랍니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제13조: 신청을 완료한 다음 영업일 이내에 금융회사에 추심행위 중지를 요청함 / 제47조: 폭행·협박, 반복·야간 전화나 방문 등 불법 추심은 금지</t>
+  </si>
+  <si>
     <t>상계 2주, 신청 사실 고지</t>
   </si>
   <si>
@@ -686,6 +710,9 @@
 ㅇ (매입형 채무조정) 새출발기금 신청부터 채무조정 약정까지 3~4개월 가량 소요, 보증부 채권의 경우 대위변제 절차 등으로 추가 3~4개월 소요
 - 다만, 신청 채무자별 제반심사(도덕적 해이 등), 채권 매입, 상담·약정 체결 등의 진행 경과에 따라 신청과 약정에 시차가 발생
 ㅇ (중개형 채무조정) 중개형 채무조정 신청부터 채무조정 확정까지 평균 2~3개월 가량 소요, 보증부 채권의 경우 대위변제 절차 등으로 추가 3~4개월 소요</t>
+  </si>
+  <si>
+    <t>관리업무요강 제15조①: 신청 후 2주일 이내 임시안 제시 / 제17조②: 확정안 승인 다음날부터 5영업일 이내에 약정(서명)하지 않으면 신청을 취소한 것으로 봄</t>
   </si>
   <si>
     <t>임시안 2주, 매입형 3~4개월, 중개형 2~3개월</t>
@@ -746,6 +773,9 @@
  * 국민취업지원제도(고용노동부), 희망리턴패키지(중소벤처기업부), 한국폴리텍 대학(비학위 직업훈련과정), 신용보증재단 재기교육</t>
   </si>
   <si>
+    <t>관리업무요강 제20조: 사회취약계층은 별표 1 감면율을 적용하되, 재산이 있으면 회수가능액을 뺀 나머지 채무에만 감면율 적용. 약정 후 해당하게 되면 소급 신청 가능(소급 대상에 한함)</t>
+  </si>
+  <si>
     <t>사회취약계층, 중위소득 60%, 순부채 90%</t>
   </si>
   <si>
@@ -769,6 +799,9 @@
 ㅇ 다만, 원금감면율은 교육 이수시간ㆍ난이도 등에 따라 차등 적용되는 것으로, 일괄 10%p를 우대하는 것이 아님을 안내드리며, 해당 제도는 부실차주 중 폐업자에게 적용되는 것으로 부실우려차주나 사업을 영위중인 사업자에게는 적용되지 않음을 참고하여 주시기 바랍니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제20조의2: 2020년 4월 이후 폐업한 부실차주가 지정 취업·재창업 교육을 이수하면 최대 10%p 추가 감면(신청서와 이수 증명서 제출, 상환 중 연체가 있으면 먼저 납부)</t>
+  </si>
+  <si>
     <t>취업·재창업 교육, 최대 10%p</t>
   </si>
   <si>
@@ -795,6 +828,9 @@
   <si>
     <t xml:space="preserve">□ 상환기간이 감면율에 영향을 미치는 관계로, 상환기간 변경은 동일한 감면율이 적용되는 구간 내에서만 가능합니다.
 ㅇ 또한 조기상환도 가능합니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제24조: 상환기간 변경은 1회만, 신청일까지 거치기간이자·연체 분할상환금을 모두 갚아야 함 / 제27조: 조기상환 승인 다음날부터 5영업일 이내에 잔액 전부 상환 / 제27조의2: 무담보 약정 1년·12회차 이상 납부한 부실차주가 일시상환하면 5~10% 추가 감면</t>
   </si>
   <si>
     <t>동일 감면율 구간, 조기상환</t>
@@ -825,6 +861,9 @@
 * 국민취업지원제도(고용노동부), 희망리턴패키지(소상공인시장진흥공단) 등 2025년 프로그램 연계 사항 (공지사항 참고)</t>
   </si>
   <si>
+    <t>관리업무요강 제46조④: 약정 때 등록한 공공정보는 1년(12회차) 성실상환하면 해제 / ⑤: 폐업한 부실차주가 지정 교육을 이수하고 취업·재창업하면 1회에 한해 신청으로 해제 가능</t>
+  </si>
+  <si>
     <t>공공정보, 1년 12회 성실납부</t>
   </si>
   <si>
@@ -845,6 +884,9 @@
   <si>
     <t xml:space="preserve">□ 새출발기금은 채무조정의 도덕적 해이를 방지하기 위해 채무조정 신청자 전원을 대상으로 도덕적 해이 심사를 진행하고 있습니다.
 ㅇ 이를 통해 신청자격을 맞추기 위해 고의 연체한 차주, 고액자산가가 소규모 채무 감면을 위해 신청 하는 경우 등 도덕적 해이가 확인되는 신청자에 대해서는 채무조정 신청을 거절하고 있습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제14조: 행정정보 공동이용망 등으로 채무관계자의 재산 유무를 확인함 / 제32조 제2·3호: 신청 자료가 허위이거나 재산 은닉 등이 발견되면 효력 상실</t>
   </si>
   <si>
     <t>도덕적 해이 심사</t>
@@ -926,6 +968,9 @@
 ㅇ 다만, 개인회생 제도와 새출발기금의 채무조정은 특징과 방식이 상이하므로 고객님의 상황을 고려하여 유리한 제도를 선택하시기를 당부드립니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제32조 제4호: 새출발기금 약정 후에 파산이나 개인회생을 신청하면 채무조정 효력이 상실됨</t>
+  </si>
+  <si>
     <t>개인회생 폐지 후 신청, 유리한 제도 선택</t>
   </si>
   <si>
@@ -990,6 +1035,9 @@
   <si>
     <t xml:space="preserve">□ 불가능합니다. 소진공에서 발급한 소상공인확인서는 착한임대인 세제해택을 위한 것으로, 일반적인 소상공인확인서와 다릅니다.
 * 중소기업현황정보시스템 (sminfo.mss.go.kr)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제12조 제3호: 신청 서류 중 신분증 자리에, 법인 소상공인은 소상공인확인서를 냄</t>
   </si>
   <si>
     <t>중소기업현황정보시스템, 일반 소상공인확인서</t>
@@ -1065,6 +1113,9 @@
 * 재산가치 추정 평가액에서 등기되어있는 선순위 동순위 채권액(압류, (근)저당등)의 실체납, 채무 잔액 및 임차보증금 등을 공제한 금액</t>
   </si>
   <si>
+    <t>관리업무요강 제59조: 새출발기금의 보전조치(가압류 등)는 원칙적으로 완납 때까지 유지. 채무조정 중 해제를 요청하면 재산의 회수가능액 이상 변제 등 요건을 갖출 때 취하 가능</t>
+  </si>
+  <si>
     <t>약정 후 완제, 재산가치 이상 변제</t>
   </si>
   <si>
@@ -1120,6 +1171,9 @@
   </si>
   <si>
     <t>□ 도덕적 해이 심사 결과에 이의가 있으신 경우 이의 신청 가능하오나, 재심사에도 지원 제외 결정된 경우, 추가 심사는 어렵습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제43조: 특수한 사정이 있으면 채무조정심의위원회 심의·의결로 감면율 조정 등을 결정할 수 있음</t>
   </si>
   <si>
     <t>이의신청, 재심사</t>
@@ -1144,6 +1198,9 @@
 ㅇ 이에 따라, 은닉재산 등이 발견되는 즉시 원금조정 등 기존 채무조정은 무효 처리되고 채권회수 절차가 진행됩니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제32조 제3·7호: 재산 도피·은닉이 발견되거나, 신청 때 회수 가능한 재산을 신고하지 않고 약정한 경우 효력 상실 / 제14조: 완제 후 재산조사는 1회</t>
+  </si>
+  <si>
     <t>정기적 재산 조사, 채무조정 무효</t>
   </si>
   <si>
@@ -1217,6 +1274,9 @@
   </si>
   <si>
     <t>민원인 이름·전화번호·고객번호 등 개인정보는 넣지 않는다.</t>
+  </si>
+  <si>
+    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 사용자가 공개 문서임을 확인함(2026-10-29). 원문 대조는 요강 본문으로 한다.</t>
   </si>
 </sst>
 </file>
@@ -1818,10 +1878,10 @@
         <v>45</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>25</v>
@@ -1841,10 +1901,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>19</v>
@@ -1859,25 +1919,25 @@
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>28</v>
@@ -1894,10 +1954,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>19</v>
@@ -1915,19 +1975,19 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>25</v>
@@ -1947,10 +2007,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
@@ -1965,28 +2025,28 @@
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
@@ -2000,10 +2060,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
@@ -2018,31 +2078,31 @@
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>30</v>
@@ -2053,49 +2113,49 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>30</v>
@@ -2106,10 +2166,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>19</v>
@@ -2124,31 +2184,31 @@
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>30</v>
@@ -2159,13 +2219,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -2180,28 +2240,28 @@
         <v>42</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>30</v>
@@ -2212,10 +2272,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>19</v>
@@ -2233,28 +2293,28 @@
         <v>42</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>30</v>
@@ -2265,10 +2325,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -2277,37 +2337,37 @@
         <v>19</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>30</v>
@@ -2318,10 +2378,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -2330,28 +2390,28 @@
         <v>19</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>25</v>
@@ -2360,7 +2420,7 @@
         <v>25</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>30</v>
@@ -2371,13 +2431,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>19</v>
@@ -2389,31 +2449,31 @@
         <v>19</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>30</v>
@@ -2424,10 +2484,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>19</v>
@@ -2436,37 +2496,37 @@
         <v>19</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>30</v>
@@ -2477,10 +2537,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>19</v>
@@ -2489,37 +2549,37 @@
         <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>30</v>
@@ -2530,10 +2590,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -2551,28 +2611,28 @@
         <v>42</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>30</v>
@@ -2583,10 +2643,10 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>19</v>
@@ -2604,28 +2664,28 @@
         <v>42</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>30</v>
@@ -2636,10 +2696,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>19</v>
@@ -2654,31 +2714,31 @@
         <v>19</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>30</v>
@@ -2689,10 +2749,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>19</v>
@@ -2707,31 +2767,31 @@
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>30</v>
@@ -2742,16 +2802,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
@@ -2760,31 +2820,31 @@
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>30</v>
@@ -2795,10 +2855,10 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -2807,7 +2867,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>19</v>
@@ -2816,28 +2876,28 @@
         <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>30</v>
@@ -2848,10 +2908,10 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -2860,7 +2920,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
@@ -2869,28 +2929,28 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>30</v>
@@ -2901,10 +2961,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
@@ -2913,37 +2973,37 @@
         <v>19</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>30</v>
@@ -2954,16 +3014,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>19</v>
@@ -2972,31 +3032,31 @@
         <v>19</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M26" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>30</v>
@@ -3007,10 +3067,10 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
@@ -3025,22 +3085,22 @@
         <v>19</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>25</v>
+        <v>232</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>25</v>
@@ -3049,7 +3109,7 @@
         <v>28</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>30</v>
@@ -3060,49 +3120,49 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>25</v>
+        <v>240</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>30</v>
@@ -3113,10 +3173,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>19</v>
@@ -3125,37 +3185,37 @@
         <v>19</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>30</v>
@@ -3166,49 +3226,49 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>30</v>
@@ -3219,10 +3279,10 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -3231,7 +3291,7 @@
         <v>19</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>19</v>
@@ -3240,19 +3300,19 @@
         <v>42</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>25</v>
+        <v>267</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>25</v>
@@ -3261,7 +3321,7 @@
         <v>25</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>30</v>
@@ -3272,10 +3332,10 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -3290,28 +3350,28 @@
         <v>19</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>29</v>
@@ -3320,15 +3380,15 @@
         <v>30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -3337,7 +3397,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>19</v>
@@ -3346,25 +3406,25 @@
         <v>21</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>29</v>
@@ -3373,15 +3433,15 @@
         <v>30</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -3399,42 +3459,42 @@
         <v>42</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>25</v>
+        <v>292</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -3449,45 +3509,45 @@
         <v>19</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -3505,42 +3565,42 @@
         <v>42</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -3549,51 +3609,51 @@
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>25</v>
+        <v>314</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -3602,28 +3662,28 @@
         <v>19</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>25</v>
@@ -3632,74 +3692,74 @@
         <v>25</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -3717,42 +3777,42 @@
         <v>21</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>25</v>
+        <v>338</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -3767,22 +3827,22 @@
         <v>19</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>25</v>
@@ -3791,21 +3851,21 @@
         <v>25</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -3820,45 +3880,45 @@
         <v>19</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -3867,51 +3927,51 @@
         <v>19</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>25</v>
+        <v>358</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -3920,7 +3980,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>19</v>
@@ -3929,34 +3989,34 @@
         <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>25</v>
+        <v>366</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3976,10 +4036,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3987,7 +4047,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3995,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4003,7 +4063,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4011,7 +4071,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4019,23 +4079,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4046,7 +4106,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4055,18 +4115,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4074,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4082,7 +4142,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,15 +4150,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4106,15 +4166,23 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>372</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="466">
   <si>
     <t>번호</t>
   </si>
@@ -1207,6 +1207,310 @@
     <t>약정하고 나면 더 조사하지 않습니다</t>
   </si>
   <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>상환유예, 유예, 납부유예, 상환연장, 입원, 실직, 휴업, 폐업, 출산, 육아휴직, 중증질환, 잠시 못 내요</t>
+  </si>
+  <si>
+    <t>상환유예</t>
+  </si>
+  <si>
+    <t>[규정] 상환 중에 상환유예를 받을 수 있나요?</t>
+  </si>
+  <si>
+    <t>연체 없이 갚고 있는 동산담보·무담보 채무는 2개월 이상 입원, 실직·휴업·폐업, 4대 중증질환·차상위, 수급자·현역입영·수감, 중증장애인 등 부양, 본인·배우자 출산·육아휴직, 1년 이상 상환 후 기타 사정이 있으면 신청서를 내고 상환을 유예할 수 있다. 사유에 따라 6개월 단위 최장 3년, 사유 해소 때까지, 출산 1년·육아휴직 기간, 기타 사정 2개월이며 총 유예기간은 최장 3년이다. 신청일까지 거치기간이자와 연체된 분할상환금은 모두 갚아야 한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제26조(채무부담액의 상환유예)
+① 채무부담액을 연체 없이 상환하고 있는 채무관계자(동산담보부채권 및 무담보채권의 경우에 한한다)가 다음 각 호의 어느 하나에 해당하는 경우에는 별지 제13호서식의 채무상환 유예(연장) 신청서를 받아 채무부담액의 상환을 유예할 수 있다. 다만, 대리인이 신청할 경우에는 별지 제14호서식의 채무상환 유예(연장) 신청 위임장을 추가로 제출하여야 한다.
+1. 질병 또는 교통사고 등으로 2개월 이상 입원하는 경우
+2. 일시적으로 직장을 잃은 경우 또는 휴업·폐업 등으로 사업을 계속 영위할 수 없는 경우
+3. 4대 중증질환자(암, 심장질환, 뇌혈관질환, 희귀난치성질환), 특별재난지역채무자(특별재난지역 선포일로부터 1년 이내 신청), 「국민기초생활 보장법」 제2조제10호의 차상위계층
+4. 「국민기초생활 보장법」 제2조제2호의 수급자, 미성년자, 현역입영자(직업군인은 제외한다) 및 구속수감자
+5. 장애정도가 심한 중증장애인(종전 1급~3급)이나 4대 중증질환자(암, 심장질환, 뇌혈관질환, 희귀난치성질환)를 부양(동거가족 중 본인 및 배우자와 그 직계 존·비속에 한함)하는 경우(2026.3.25. 본호신설)
+6. 채무관계자 또는 그 배우자가 출산·육아휴직하는 경우(2026.3.25. 본호신설)
+7. 1년(12회차) 이상 상환한 채무관계자가 제1호에서 제6호까지 외의 기타 사정으로 채무변제가 어려울 경우(2026.3.25. 본호신설)
+8. 그 밖에 주무부점의 장이 긴급하게 상환유예가 필요하다고 인정하는 경우
+② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대해서는 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
+③ 제1항제4호에 해당하는 채무관계자에 대하여 채무부담액의 상환유예 사유가 해소될 때까지 상환을 유예할 수 있다.
+④ 제1항 제6호 중 출산의 경우에는 출생일로부터 1년, 육아휴직의 경우에는 휴직기간 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
+⑤ 제1항 제7호에 해당하는 경우에는 상환유예 신청일로부터 2개월 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
+⑥ 채무부담액의 상환유예를 신청하려는 채무관계자는 신청일까지의 거치기간이자, 연체된 분할상환금을 모두 상환하여야 한다.
+⑦ 동산담보부채권의 채무관계자는 상환유예 기간동안 잔여 분할상환금에 대하여 연 2%의 금리를 적용한 이자를 매월 상환기일에 납부하여야 한다.
+⑧ 채무관계자는 상환유예 기간 만료 후에 최초로 도래하는 상환기일부터 잔여 분할상환금을 순차적으로 상환하여야 한다.
+⑨ 제1항 각 호에 해당하는 채무관계자는 동일한 사유 또는 서로 다른 각 호의 사유로 연속하여 채무부담액의 상환을 유예할 수 있으며, 총 상환유예기간은 최장 3년으로 한다.(2026.3.25. 본항신설)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제26조</t>
+  </si>
+  <si>
+    <t>채무상환 유예(연장) 신청서, 최장 3년, 연체 먼저 해소</t>
+  </si>
+  <si>
+    <t>사유 없이도 유예해 드립니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제26조(채무부담액의 상환유예) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>효력상실, 실효, 3개월 연체, 연체, 약정 해지, 못 냈어요, 밀렸어요, 실효 통지</t>
+  </si>
+  <si>
+    <t>[규정] 어떤 경우에 채무조정 효력이 없어지나요?</t>
+  </si>
+  <si>
+    <t>분할상환금(거치기간 이자 포함)을 3개월(3회차) 이상 연체하면 효력이 상실된다. 약정 후 생긴 재난·혼인·사망·입원·실업 같은 특별한 사정이 있으면 6개월 이상 이행하지 않을 때 상실할 수 있다. 신청 자료 허위, 재산 은닉, 파산·개인회생·신복위 채무조정 신청, 제3자의 강제집행, 재산 미신고, 사망·실종, 합의 해제 요청도 상실 사유다. 상실 10영업일 전까지 예정 통지를 보낸다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제32조(채무조정의 효력 상실)
+채무관계자에게 다음 각 호의 어느 하나에 해당하는 사유가 발생한 경우에는 채무조정 약정의 효력이 상실된다. 이 경우 주무부점의 장은 즉시 채권의 회수 절차를 진행하여야 한다.(2024.12.30. 본조개정)
+1. 분할상환금(거치기간동안의 이자를 포함한다)의 상환을 3개월(3회차) 이상 연체한 경우. 다만, 채무관계자가 다음 각 목의 사항과 같은 특별한 사정이 있는 경우에는 채무조정 신청 후 6개월 이상 채무조정에 의한 변제계획을 이행하지 아니하면 채무조정의 효력 상실을 할 수 있다. 단, 그 사정은 채무조정 약정이 체결된 이후에 발생한 사정으로 한정한다.(2024.12.30. 본호개정)
+가. 채무관계자가 「재난 및 안전관리 기본법」 제61조에 따른 특별 지원 대상에 포함되는 경우
+나. 본인 또는 그 직계 존ㆍ비속의 혼인
+다. 본인 또는 그 직계 존ㆍ비속, 배우자 또는 그 직계 존ㆍ비속이 사망한 경우
+라. 본인 또는 그 직계 존·비속, 배우자 또는 그 직계 존·비속이 사고·질병 등으로 수술을 받거나 입원한 경우
+마. 실업(채무자의 사정으로 전직 또는 자영업을 하기 위하여 이직한 경우는 제외), 무급휴직, 폐업(전업하기 위한 경우는 제외)한 경우
+바. 3개월 이상 입원치료가 필요한 질병을 진단받은 경우
+2. 채무조정 신청 당시에 제출한 자료나 진술이 허위인 경우
+3. 허위사실 신고, 재산의 도피 및 은닉, 기타 책임재산 감소행위 등을 한 사실이 발견되는 경우
+4. 「채무자 회생 및 파산에 관한 법률」에 따른 파산신청 또는 (개인)회생절차개시의 신청이 있는 경우
+5. 「서민의 금융생활 지원에 관한 법률」에 따른 신용회복위원회 채무조정 신청이 있는 경우(2024.12.30. 본호신설)
+6. 채무관계자의 채무조정과 관련한 담보물 또는 발견재산에 대하여 제3자로부터 강제집행의 신청이 있는 경우(2024.12.30. 본호개정)
+7. 채무조정 신청 당시에 회수가능성이 있는 재산을 소유하고 있었음에도 불구하고 이를 신고하지 않고 채무조정에 관한 약정이 체결된 경우(2024.12.30. 본호개정)
+8. 채무관계자가 사망하거나 실종선고를 받은 경우(2024.12.30. 본호신설)
+9. 채무조정 합의의 해제를 요청한 경우(2024.12.30. 본호신설)
+제33조(연체 및 채무조정의 효력 상실 등 통지)
+① 채무관계자가 분할상환금을 1회 이상 연체한 경우에는 월 1회 전자우편(E-mail) 또는 문자메세지(SMS 등)로 연체사실을 통지하거나 분할상환금 납입안내장을 채무관계자의 주소에 등기우편으로 통지하여야 한다.
+② 채무관계자에게 제32조 각 호에 따른 채무조정의 효력 상실사유가 발생한 때에는 채무조정의 효력이 상실된다는 사실과 신용정보집중기관에 신용도판단정보가 등록되어 금융거래 시 불이익을 받을 수 있음을 별지 제27의2호서식의 채무조정의 효력 상실 예정통지 및 채무금 변제 최고서로 채무조정의 효력 상실일 10영업일 전까지 통지하여야 한다.(2024.12.30. 본항개정)
+③ 채무관계자가 채무조정의 효력을 상실한 때에는 채무조정의 효력이 상실된 사실과 잔여 채무액을 상환하여야 함을 별지 제27호서식에 따른 채무조정의 효력 상실통지 및 채무금 변제 최고서로 통지하여야 한다.(2024.12.30. 본항개정)
+④ 채무관계자에게 신용회복위원회를 통한 신용회복지원이 실효, 「채무자 회생 및 파산에 관한 법률」에 따른 파산신청 및 (개인)회생절차개시의 신청이 취소 또는 기각 등의 사유가 발생할 때에는 별지 제27호의3서식에 따른 안내서로 통지하여야 한다.(2024.12.30. 본항개정)
+[2024.12.30. 본조개정]</t>
+  </si>
+  <si>
+    <t>관리업무요강 제32조, 제33조</t>
+  </si>
+  <si>
+    <t>3회차 연체, 효력 상실 예정 통지</t>
+  </si>
+  <si>
+    <t>몇 달 밀려도 괜찮습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제32조(채무조정의 효력 상실), 제33조(연체 및 채무조정의 효력 상실 등 통지) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>효력부활, 부활, 되살리기, 다시 살리기, 연체금 납부, 실효 후</t>
+  </si>
+  <si>
+    <t>[규정] 효력이 없어진 채무조정을 되살릴 수 있나요?</t>
+  </si>
+  <si>
+    <t>3개월 이상 연체로 효력이 상실됐으면 상실일부터 6개월이 지나기 전에 연체된 분할상환금 전액과 제비용을 내면 효력이 되살아난다. 신청하면 1회분 분할상환금과 제비용만 내고 부활할 수 있고, 남은 미납금은 잔여기간에 나눠 갚는다. 약정 후 새로 재산을 취득한 부실차주는 부활할 수 없다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제34조(채무조정의 효력 부활)
+① 제32조제1호의 사유로 채무조정의 효력이 상실된 채무관계자가 연체된 분할상환금(거치기간동안의 이자를 포함한다) 전액과 제비용을 납부하는 때에는 채무조정 약정의 효력은 그 때부터 부활된다. 다만, 채무관계자가 신청하는 경우 1회분 분할상환금과 제비용을 납부하여 채무조정의 효력을 부활할 수 있으며, 미납한 분할상환금은 잔여기간에 균등하게 안분하여 상환하여야 한다.(2024.9.11., 2024.12.30. 본항개정)
+② 제1항에 따른 채무조정의 효력 부활은 채무조정의 효력 상실일로부터 6개월이 지나기 전까지 할 수 있다.(2024.12.30. 본항개정)
+③ 제1항 및 제2항에도 불구하고, 채무조정 약정일 이후에 새로이 재산을 취득하여 소유하고 있는 부실차주 및 그 채무관계자의 경우에는 채무조정의 효력을 부활할 수 없다.(2024.12.30. 본항개정)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제34조</t>
+  </si>
+  <si>
+    <t>상실일부터 6개월 이내, 1회분 납부 부활</t>
+  </si>
+  <si>
+    <t>언제든지 부활할 수 있습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제34조(채무조정의 효력 부활) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>재약정, 다시 약정, 실효 후 재약정, 재약정 신청</t>
+  </si>
+  <si>
+    <t>[규정] 효력이 상실된 뒤 다시 약정할 수 있나요?</t>
+  </si>
+  <si>
+    <t>효력이 상실된 채무관계자는 재약정 신청서를 내고 새로 약정할 수 있다. 신청 자료 허위·재산 은닉·파산이나 개인회생 신청으로 상실됐다면 그 사유가 해소된 뒤에 신청한다. 채무부담액은 재약정 신청 시점 기준으로 다시 산정하고, 상환기간은 부실차주는 일반 기준, 부실우려차주는 기존 잔여기간 이내다. 재약정에는 거치기간을 주지 않는다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제35조(채무조정의 재약정)
+① 협약 및 이 요강에 따라 채무조정의 효력이 상실된 채무관계자가 채무조정의 재약정을 하고자 하는 경우에는 채무관계자로부터 별지 제20호서식의 재약정 신청서를 받아 채무조정의 약정을 새로이 체결할 수 있다. 다만, 제32조제2호부터 제4호까지의 사유로 채무조정의 효력이 상실된 경우에는 해당사유가 해소된 이후에 재약정을 신청할 수 있다.
+② 채무조정의 재약정을 할 경우 채무부담액 산정의 기초자료는 재약정 신청 시를 기준으로 하되, 상환기간은 재약정 신청 시에 속한 채무자 유형에 따라 다음 각 호의 기준을 적용한다.
+1. 부실차주 : 제22조에 따른 상환기간
+2. 부실우려차주 : 기존 채무조정의 잔여 상환기간 범위 이내
+③ (2024.9.11. 본항삭제)
+④ 채무조정의 재약정을 할 경우 제21조에 따른 거치기간은 부여하지 않는다. 다만, 제34조에 따른 채무조정의 효력 부활은 할 수 있다.(2024.12.30. 본항개정)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제35조</t>
+  </si>
+  <si>
+    <t>재약정 신청서, 거치기간 없음</t>
+  </si>
+  <si>
+    <t>재약정하면 거치기간을 다시 받으실 수 있습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제35조(채무조정의 재약정) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>거치기간, 거치, 이자만, 원금유예, 원금 나중에, 이자 유예</t>
+  </si>
+  <si>
+    <t>약정</t>
+  </si>
+  <si>
+    <t>[규정] 거치기간(원금 상환 유예)은 얼마나 받을 수 있나요?</t>
+  </si>
+  <si>
+    <t>최초 약정 때 신청하면 1회에 한해 거치기간(이자만 내고 원금 상환을 미루는 기간)을 받을 수 있다. 1개월 단위 최대 1년이며, 사회취약계층 특례대상자·저소득 차주·부동산담보부 채권은 최대 3년까지 가능하다. 부실차주 무담보채무는 거치기간 이자가 없고, 신청하면 거치기간 안에서 최대 1년까지 이자 납부를 미룰 수 있다(미룬 이자는 유예 종료일에 한꺼번에 냄).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제21조(거치기간)
+① 최초의 채무조정 약정 시 채무관계자가 신청할 경우 1회에 한하여 거치기간을 부여할 수 있다.
+② 거치기간은 1개월 단위로 최대 1년(12회차)의 기간 내에서 채무관계자와 협의하여 정한다. 다만 다음 각 호의 어느 하나에 해당하는 경우에는 1개월 단위로 최대 3년(36회차)의 기간을 부여할 수 있다.(2025.9.19. 본항개정)
+1. 별표 1의 사회취약계층 중 특례대상자(2025.9.19. 본호신설)
+2. 저소득 차주(2025.9.19. 본호신설)
+3. 부동산담보부 채권(2025.9.19. 본호신설)
+③ 채무관계자는 거치기간동안 채무유형별 채무부담액에 대하여 제22조제2항에 따른 금리를 적용하여 계산한 이자를 납부하여야 한다. 다만, 부실차주의 동산담보부채무에 대해서는 연 2% 금리를 적용하며, 부실차주의 무담보채무에 대해서는 이자를 부과하지 않는다.(2025.9.19. 본항개정)
+④ 제3항에도 불구하고, 채무관계자가 신청할 경우 거치기간 내에서 최대 1년(12회차)의 이자 납부를 유예할 수 있다. 이 경우 유예한 이자는 유예기간의 종료일에 일시 납부하여야 한다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제21조</t>
+  </si>
+  <si>
+    <t>최초 약정 1회, 최대 1년(특례 3년)</t>
+  </si>
+  <si>
+    <t>거치기간은 언제든 다시 받을 수 있습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제21조(거치기간) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>상환일, 납부일, 상환기일, 날짜 변경, 납부일 변경, 가상계좌, CMS, 자동이체, 분할상환금, 일시상환</t>
+  </si>
+  <si>
+    <t>[규정] 상환일과 납부 방법은 어떻게 되나요?</t>
+  </si>
+  <si>
+    <t>분할상환금 상환일은 매월 5·10·15·20·25일 중에서 고르고, 1회차는 약정일 다음 달(거치기간이 있으면 종료 다음 달)이다. 상환일 변경은 신청서를 내고 1회만 할 수 있고, 연체가 있으면 먼저 해소해야 한다. 납부는 CMS 자동이체(수수료는 새출발기금 부담) 또는 가상계좌(송금수수료는 본인 부담)로 한다. 일시상환은 약정 다음날부터 5영업일 이내에 내지 않으면 효력이 상실된다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제23조(채무부담액의 상환방법)
+① 분할상환금의 상환기일은 매월 5, 10, 15, 20, 25일 중에서 채무관계자가 정한 날로 하되, 해당일이 영업일이 아닌 경우에는 다음 영업일을 상환기일로 한다.
+② 분할상환금의 1회차 상환기일은 채무조정 약정일 다음달에 도래하는 상환기일로한다. 다만, 거치기간이 있는 경우에는 거치기간 종료일의 다음 달에 도래하는 상환기일을 1회차 상환기일로 한다.(2024.12.30. 본항개정)
+③ 분할상환금은 천원 단위로 상환하되, 1만원 이상의 금액으로 한다. 이 경우 천원 미만의 금액은 최종회차에 산입하여 상환한다.
+④ 채무관계자가 채무부담액을 일시상환하는 경우에는 채무조정 약정일의 다음날부터 5영업일 이내에 납부하여야 하고, 이 기간 내에 납부하지 않는 경우에는 채무조정 약정 체결의 효력이 상실된다.
+⑤ 모든 이자의 계산은 한편 넣기로 하며, 원미만은 절사한다.
+⑥ 채무부담액에 포함되지 않은 원금 및 모든 이자는 채무조정 약정 만기일까지 상환을 유예한다.
+제25조(상환기일의 변경)
+분할상환금의 상환기일의 변경은 채무관계자로부터 별지 제12호서식의 분할상환기일 변경 신청서를 받아 1회에 한하여 변경을 허용할 수 있다. 다만, 채무관계자가 분할상환금의 연체가 있거나 상환기일 변경으로 해당 월 분할상환금의 연체가 발생할 경우에는 연체를 해소한 이후 또는 연체를 해소할 수 있는 금액을 상환받은 후에 분할상환기일을 변경하여야 한다.
+제30조(채무부담액 등 회수)
+① 채무부담액 및 제비용 등 상환금은 지정된 납부(가상)계좌로 상환받는다.(2025.9.19. 본항개정)
+② 분할상환금은 CMS이체방식으로 상환받거나 지정된 가상계좌로 상환받을 수 있다.(2025.9.19. 본항신설)
+③ CMS이체방식 이용에 따른 수수료(금융회사 수수료ㆍ금융결제원 중계수수료)는 새출발기금이 부담하며 가상계좌 이용에 따른 송금수수료는 채무관계자가 부담하는 것을 원칙으로 한다.(2025.9.19. 본항신설)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제23조, 제25조, 제30조</t>
+  </si>
+  <si>
+    <t>5·10·15·20·25일, 상환기일 변경 1회, CMS 자동이체</t>
+  </si>
+  <si>
+    <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제23조(채무부담액의 상환방법), 제25조(상환기일의 변경), 제30조(채무부담액 등 회수) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>서류, 신청서류, 제출서류, 필요서류, 준비물, 구비서류, 사업자등록증, 신분증, 동의서, 확약서</t>
+  </si>
+  <si>
+    <t>[규정] 채무조정을 신청할 때 어떤 서류가 필요한가요?</t>
+  </si>
+  <si>
+    <t>채무승인 및 조정 확약서(일시상환용 또는 분할상환용), 사업자등록증, 신분증(법인 소상공인은 소상공인확인서, 특수형태근로종사자·프리랜서는 긴급고용안정지원금 입출금거래내역서), 개인(신용)정보 동의서 2종, 행정정보 공동이용 사전동의서, 분할상환이면 CMS 출금이체 신청서, 대상확인 및 채무조정신청서, 공공 마이데이터 동의서를 받거나 확인한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제12조(채무조정의 신청서류)
+채무관계자가 채무조정을 신청할 경우에는 채무관계자로부터 다음 각 호에 해당하는 서류를 수령 또는 확인하여야 한다.
+1. 채무승인 및 조정 확약서(일시상환용)(별지 제5호서식) 또는 채무승인 및 조정 확약서(분할상환용)(별지 제6호서식)
+2. 사업자등록증
+3. 신분증(법인 소상공인의 경우에는 소상공인확인서, 특수형태근로종사자 및 프리랜서의 경우에는 긴급고용안정지원금 입출금거래내역서)
+4. 개인(신용)정보 수집·이용·제공 동의서(별지 제7호서식)
+5. 개인(신용)정보 수집·이용·제공·조회 동의서(별지 제8호서식)
+6. 행정정보 공동이용 사전동의서(별지 제9호서식)
+7. (분할상환용) CMS 출금이체 신청서(별지 제38호서식)(2025.9.19. 본호신설)
+8. 새출발기금 대상확인 및 채무조정신청서(별지 제40호서식)(2026.3.25. 본호신설)
+9. 공공 마이데이터 처리를 위한 개인정보 수집·이용·제공 동의서(별지 제41호서식)(2026.3.25. 본호신설)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제12조</t>
+  </si>
+  <si>
+    <t>채무승인 및 조정 확약서, 사업자등록증, 행정정보 공동이용 동의</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) (2026.3.25. 시행)</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>순자산, 재산 많으면, 자산, 6.5억, 지원 제외, 대리인, 위임장, 대리 신청, 대신 신청</t>
+  </si>
+  <si>
+    <t>[규정] 재산이 많아도 신청할 수 있나요? (순자산 기준·대리 신청)</t>
+  </si>
+  <si>
+    <t>온라인 플랫폼으로 신청하고, 어려우면 상담창구 등으로 신청한다. 주채무자의 순자산(자산-부채)이 6.5억원을 넘으면 지원 대상에서 제외되지만, 1회 이상 채무조정 약정을 맺은 이력이 있으면 지원 대상이다. 대리인이 신청하면 위임장을 받고 대리권을 확인한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제11조(채무조정의 신청)
+① 채무조정의 신청은 대상채권의 채무관계자가 새출발기금의 온라인 플랫폼을 통하여 신청한다. 다만, 채무관계자가 온라인 플랫폼을 이용하여 신청하기 어려운 경우에는 새출발기금 상담창구 등을 통하여 신청할 수 있다.
+② 주채무자의 순자산(자산-부채)규모가 6.5억원을 초과하는 경우에는 채무조정 지원 대상에서 제외한다. 다만, 1회 이상 채무조정 약정을 체결한 이력이 있는 채무관계자의 경우에는 채무조정 지원 대상으로 한다.
+③ 채무관계자가 대리인을 통하여 채무조정을 신청하고자 할 경우에는 채무조정 신청 위임장(별지 제1호서식 또는 별지 제2호서식)을 수령하고 대리권이 있는지 여부를 확인하여야 한다.
+④ 채무관계자가 아닌 제3자가 채무부담액의 전부 또는 일부에 대하여 대위변제를 신청하는 경우에는 별지 제3호서식의 대위변제에 대한 승낙서를 받은 후 변제받을 수 있다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 대위변제에 대한 승낙서 제출을 생략할 수 있다.
+1. 채무관계자가 아닌 제3자가 구상권을 행사하지 않기로 동의하여 별지 제4호서식의 대위변제 신청서를 받은 경우
+2. 변제할 정당한 이익이 있는 자인 경우
+⑤ 제4항에 따라 채무관계자가 아닌 제3자가 대위변제할 경우에는 채무관계자의 채무조정기준에 따라 처리한다.
+⑥ (2024.9.11. 본항삭제)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제11조</t>
+  </si>
+  <si>
+    <t>순자산 6.5억원, 채무조정 신청 위임장</t>
+  </si>
+  <si>
+    <t>재산과 상관없이 누구나 됩니다</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) (2026.3.25. 시행)</t>
+  </si>
+  <si>
     <t>버튼</t>
   </si>
   <si>
@@ -1249,7 +1553,7 @@
     <t>자료 출처</t>
   </si>
   <si>
-    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인)</t>
+    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인) / 044~051은 「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행) 조문 기반 자료로, 제목 앞에 [규정]을 붙이고 "FAQ 원문" 칸에 조문을 그대로 옮겼다(2026-10-29).</t>
   </si>
   <si>
     <t>홈페이지에 게시된 답변을 그대로 옮긴 칸. 근거 정확도 확인은 이 칸과 대조한다.</t>
@@ -1668,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -4019,6 +4323,430 @@
         <v>278</v>
       </c>
     </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -4036,10 +4764,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>369</v>
+        <v>442</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>370</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4047,7 +4775,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>371</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4055,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4063,7 +4791,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4071,7 +4799,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>374</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4079,23 +4807,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>375</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>377</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>379</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -4115,18 +4843,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>380</v>
+        <v>453</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>381</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>455</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4134,7 +4862,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4142,7 +4870,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4150,15 +4878,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>386</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>387</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>388</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4166,15 +4894,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>389</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>390</v>
+        <v>463</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>391</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4910,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>392</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -1251,7 +1251,7 @@
     <t>사유 없이도 유예해 드립니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제26조(채무부담액의 상환유예) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제26조(채무부담액의 상환유예) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>045</t>
@@ -1300,7 +1300,7 @@
     <t>몇 달 밀려도 괜찮습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제32조(채무조정의 효력 상실), 제33조(연체 및 채무조정의 효력 상실 등 통지) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제32조(채무조정의 효력 상실), 제33조(연체 및 채무조정의 효력 상실 등 통지) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>046</t>
@@ -1330,7 +1330,7 @@
     <t>언제든지 부활할 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제34조(채무조정의 효력 부활) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제34조(채무조정의 효력 부활) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>047</t>
@@ -1363,7 +1363,7 @@
     <t>재약정하면 거치기간을 다시 받으실 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제35조(채무조정의 재약정) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제35조(채무조정의 재약정) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>048</t>
@@ -1400,7 +1400,7 @@
     <t>거치기간은 언제든 다시 받을 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제21조(거치기간) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제21조(거치기간) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>049</t>
@@ -1439,7 +1439,7 @@
     <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제23조(채무부담액의 상환방법), 제25조(상환기일의 변경), 제30조(채무부담액 등 회수) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제23조(채무부담액의 상환방법), 제25조(상환기일의 변경), 제30조(채무부담액 등 회수) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>050</t>
@@ -1473,7 +1473,7 @@
     <t>채무승인 및 조정 확약서, 사업자등록증, 행정정보 공동이용 동의</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>051</t>
@@ -1508,7 +1508,7 @@
     <t>재산과 상관없이 누구나 됩니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) (2026.3.25. 시행)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>버튼</t>
@@ -1580,7 +1580,7 @@
     <t>민원인 이름·전화번호·고객번호 등 개인정보는 넣지 않는다.</t>
   </si>
   <si>
-    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 사용자가 공개 문서임을 확인함(2026-10-29). 원문 대조는 요강 본문으로 한다.</t>
+    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 공개 위치: 캠코 홈페이지 정보공개 &gt; 법무자료 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100). 2026-10-29 확인 시 게시본은 2026.6.29. 일부개정·시행본이라, 바뀐 조항이 있으면 다시 맞춰야 한다.</t>
   </si>
 </sst>
 </file>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="483">
   <si>
     <t>번호</t>
   </si>
@@ -93,7 +93,7 @@
   * 새출발기금 미협약기관 대출, 개인 자산형성 목적의 대출 등 정책 취지에 맞지 않는 대출 등은 지원 대상이 아님</t>
   </si>
   <si>
-    <t>-</t>
+    <t>관리업무요강 제2조 제4호: 채무조정은 상환능력 등을 고려해 채무 감면, 상환기간 연장, 분할상환 등으로 채무 내용을 바꿔 채무부담 완화와 재기를 지원하는 것</t>
   </si>
   <si>
     <t>채무조정 프로그램, 추심 중단, 상환기간 연장</t>
@@ -131,6 +131,9 @@
 ㅇ 소상공인 대출 지원 정책은 ‘소상공인정책자금(https://ols.semas.or.kr/)’ 사이트 등을 통하여 확인하실 수 있습니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제4호: 채무조정은 이미 있는 채무의 내용(감면·기간 연장·분할상환)을 바꾸는 것</t>
+  </si>
+  <si>
     <t>수수료 없음, 사칭 주의</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
     <t>부실차주, 부실우려차주, 연체일수</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>004</t>
   </si>
   <si>
@@ -209,6 +215,9 @@
 ㅇ 또한 정상영업회복까지 충분한 시간적 여유를 제공해 드리기 위해 무담보 10년, 담보 20년 등으로 타 제도(법원 개인회생 최장 5년, 신복위 무담보 8년, 담보 20년) 대비 더욱 충분한 상환기간을 지원하고 있습니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제32조 제4·5호: 새출발기금 약정 후 파산·개인회생이나 신용회복위원회 채무조정을 신청하면 새출발기금 채무조정 효력이 상실됨</t>
+  </si>
+  <si>
     <t>소상공인 전용, 무담보 10년, 담보 20년</t>
   </si>
   <si>
@@ -232,7 +241,7 @@
 ㅇ 새출발기금 미협약기관 대출의 경우 법원 회생 및 신용회복위원회 개인워크아웃 등 타 채무조정 제도를 이용하여 주시기 바랍니다.</t>
   </si>
   <si>
-    <t>새출발기금 지원 협약</t>
+    <t>새출발기금 지원 협약 / 관리업무요강 제2조 제5호: 채권금융회사는 협약에 가입하고 대상차주에 대한 채권을 가진(또는 새출발기금에 넘긴) 금융회사·보증기관</t>
   </si>
   <si>
     <t>협약기관, 미협약기관, 타 채무조정 제도</t>
@@ -290,6 +299,9 @@
  ㅇ부실차주의 신용ㆍ보증대출은 새출발기금(한국자산관리공사 운영)을 통한 매입형 채무조정으로, 부실우려차주의 대출 및 부실차주의 담보대출은 신용회복위원회를 통한 중개형 채무조정으로 지원하고 있습니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제12호: 자산관리자는 새출발기금으로부터 관리·운용 업무를 위탁받은 한국자산관리공사 / 제11조①: 온라인 플랫폼 신청, 어려우면 상담창구 등</t>
+  </si>
+  <si>
     <t>매입형, 중개형</t>
   </si>
   <si>
@@ -310,6 +322,9 @@
   <si>
     <t xml:space="preserve">□ 새출발기금은 고의적, 반복적 채무조정 신청으로 인한 도덕적 해이를 방지하기 위해 신청 횟수를 1회로 제한하고 있습니다.
 ㅇ 다만, 부실우려차주가 약정했던 채무조정이 미납의 사유로 실효되는 경우, 해당 채권을 새출발기금이 매입해 채무조정을 지원하며, 최초에 신청하지 않았던 대출도 추가 신청할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제16조②: 신청을 취소하면 취소 신청일부터 3개월간 재신청이 제한됨</t>
   </si>
   <si>
     <t>1회 제한, 미납 실효 시 매입</t>
@@ -336,6 +351,9 @@
     <t xml:space="preserve">□ 새출발기금의 지원대상은 부실 또는 부실우려 개인사업자 또는 소상공인으로 3개월 이상 대출이 연체된 부실차주 뿐만 아니라 연체 3개월 미만으로 근시일 내에 장기연체에 빠질 우려가 큰 부실우려차주를 포함합니다.
 ㅇ 따라서 연체가 없는 경우에도 부실우려차주 요건*에 해당되는 경우 새출발기금 신청이 가능합니다.
 * 폐업자, 6개월 이상 휴업자/국세·지방세·관세 체납으로 신용정보관리대상에 등재된 차주/신용평점 하위차주 또는 고의성 없이 상당기간 연체가 발생한 차주 등</t>
+  </si>
+  <si>
+    <t>관리업무요강 제2조 제6·7호: 부실차주는 1개 이상 채무가 3개월 이상 연체 중인 차주, 부실우려차주는 부실차주가 아니면서 '요주의' 이하 등 장기연체 우려가 있는 차주</t>
   </si>
   <si>
     <t>부실우려차주 요건</t>
@@ -417,6 +435,9 @@
 ㅇ 채권인수 후 채무조정 본 약정 체결 시에는 신청자를 대상으로 정밀한 재산조사 절차가 진행될 예정이므로, 오류입력분에 대해서는 본 약정 체결 시 보완하시면 됩니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제17조①: 약정할 때 신청서 기재사항과 채무부담액 산정 기초자료(나이·소득·재산 등)가 일치하는지 확인 / 제32조 제2호: 신청 자료나 진술이 허위면 효력 상실</t>
+  </si>
+  <si>
     <t>임시안, 본 약정 때 보완</t>
   </si>
   <si>
@@ -437,6 +458,9 @@
   <si>
     <t xml:space="preserve">□ 금융기관 대출을 3개월 이상 연체 중이나 전산상 등록된 연체정보가 없어 부실차주 신청이 불가한 경우,
 ㅇ 새출발기금 홈페이지 이의신청을 통해 부채증명원 등 증빙자료를 첨부하여 주시면, 검토 후 지원 가능 여부를 안내드리겠습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제15조①: 채무조정임시안은 한국신용정보원에서 제공한 채무액을 기초로 작성함</t>
   </si>
   <si>
     <t>이의신청, 부채증명원</t>
@@ -521,6 +545,9 @@
 ㅇ 지원 대상에 해당하지 않는 분께서는 법원 회생, 신용회복위원회 개인워크아웃 등 타 채무조정 제도를 이용하여 채무조정을 지원받을 수 있습니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제1·2호: 대상차주는 새출발기금 지원 대상인 협약상 차주, 주채무자는 대상차주(합명·합자회사는 대표 무한책임사원 포함)</t>
+  </si>
+  <si>
     <t>개인사업자, 법인 소상공인</t>
   </si>
   <si>
@@ -575,6 +602,9 @@
   * 단, 법인 소상공인의 대표자가 보유한 가계대출은 지원 제외
 ㅇ 다만, 지원 한도(총채무액 15억원, 담보10억원, 무담보 5억원) 이상 대출을 보유하였거나, 새출발기금 미협약기관의 대출(대부업 등) 등은 지원 대상에 해당하지 않으며,
 ㅇ 6개월 이내 신규 발생 대출(해당 대출이 전체 대출 총액의 30%이하인 경우에는 지원 가능), 사업 목적이 아닌 개인 자산형성 목적의 대출 등 새출발기금 정책 취지에 맞지 않는 대출 및 기타 처분에 제한이 있는 대출 등은 지원에서 제외됩니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제2조 제26호: 대상채권은 협약 금융회사 채권 중 새출발기금 지원 대상이 되는 원금·이자·가지급금·수수료·제비용</t>
   </si>
   <si>
     <t>사업자대출, 가계대출, 6개월 내 신규대출 30%</t>
@@ -600,6 +630,9 @@
  * (연체 30일 이전) min(채무조정 전 금리, 9%)
    (연체 30일 이후) min(채무조정 전 금리, 3.9~4.7%)
 ※ 새출발기금을 신청하더라도 이미 등록되어 있는 금융기관 연체정보에 따라 신규 대출 및 카드 이용ㆍ발급 등 정상 금융생활이 제한될 수 있습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제18조②: 약정은 채무관계자 기준으로, 대상채권 계좌별로 채무부담액을 따로 산정한 뒤 합산해 한꺼번에 체결함</t>
   </si>
   <si>
     <t>부실차주 일괄 신청, 부실우려 선택 신청</t>
@@ -746,6 +779,9 @@
 ㅇ 특히, 부실 차주의 경우에도 담보 대출은 원금감면 지원 대상이 아닙니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제19조①: 부실우려차주는 원금 감면 없이 무담보채권 연체이자 전액 등을 감면 / ②: 부실차주는 별표 3 기준으로 채무부담액(감면 포함)을 산정</t>
+  </si>
+  <si>
     <t>순부채, 무담보 대출</t>
   </si>
   <si>
@@ -912,6 +948,9 @@
 ㅇ 새출발기금을 통한 지원이 어려우실 경우, 타 채무조정 제도(신복위 개인워크아웃 및 법원 회생 등)를 이용하여 주시기 바랍니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제5호: 채무조정 대상은 협약에 가입한 채권금융회사의 채권</t>
+  </si>
+  <si>
     <t>금융기관 조회, 협약 가입 금융기관</t>
   </si>
   <si>
@@ -943,6 +982,9 @@
 ※ 새출발기금 성실상환자 재기지원 사업은 신청 상황에 따라 조기 마감 및 사업 종료될 수 있으며, 특히, 보증 및 대출지원의 경우 지원기관 기준에 따라 최종 지원 여부가 결정됨을 참고하시기 바랍니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제17조③: 약정할 때 재기지원 사업(취업알선, 상품안내 등)을 안내할 수 있음</t>
+  </si>
+  <si>
     <t>성실상환자 재기지원 사업, 웹플랫폼 공지</t>
   </si>
   <si>
@@ -1063,6 +1105,9 @@
   <si>
     <t xml:space="preserve">□ 채무내역 조회시 대출정보와 대출 중 연체된 건의 연체정보가 함께 조회됩니다.
 ㅇ 채무조정 진행 과정에서 채권금융회사와 대출에 대한 확인 절차를 거치고 있으므로 채무조정 약정시에는 채무조정 대상 채무를 명확히 확인하실 수 있습니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제15조②: 금융회사에서 채권 인수가 끝나면 매입전산자료·원인서류(대출약정서 등)를 확인해 채무조정확정안을 제시함</t>
   </si>
   <si>
     <t>대출정보와 연체정보 함께 조회, 약정 시 확인</t>
@@ -1137,6 +1182,9 @@
     <t>□ 새출발기금은 신청자의 대출 유형에 따라 ①부실차주 보증·신용 채무는 매입형, ②부실차주 담보채무 및 부실우려차주 담보·보증·신용채무는 중개형으로 채무조정이 진행됩니다.</t>
   </si>
   <si>
+    <t>관리업무요강 제2조 제6호, 제19조③: 중개형 채무조정 효력이 상실된 부실우려차주 등은 매입형 채무조정으로 진행하고, 채무부담액은 부실차주 기준으로 산정함</t>
+  </si>
+  <si>
     <t>041</t>
   </si>
   <si>
@@ -1150,6 +1198,9 @@
   </si>
   <si>
     <t>□ 협약금융회사가 보유 중인 카드론 및 카드사용대금, 현금서비스에 대해서는 새출발기금 지원대상채권에 해당하는 경우 지원 가능합니다.</t>
+  </si>
+  <si>
+    <t>관리업무요강 제2조 제26호: 대상채권은 협약 금융회사 채권 중 새출발기금 지원 대상이 되는 채권(원금·이자·수수료 등)</t>
   </si>
   <si>
     <t>카드론, 현금서비스, 협약 금융회사</t>
@@ -2129,16 +2180,16 @@
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>29</v>
@@ -2152,10 +2203,10 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>19</v>
@@ -2170,25 +2221,25 @@
         <v>19</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>28</v>
@@ -2205,10 +2256,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>19</v>
@@ -2223,25 +2274,25 @@
         <v>19</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>28</v>
@@ -2258,10 +2309,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>19</v>
@@ -2279,22 +2330,22 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>28</v>
@@ -2311,10 +2362,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
@@ -2329,28 +2380,28 @@
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
@@ -2364,10 +2415,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
@@ -2382,31 +2433,31 @@
         <v>19</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>30</v>
@@ -2417,10 +2468,10 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>19</v>
@@ -2435,31 +2486,31 @@
         <v>19</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>30</v>
@@ -2470,10 +2521,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>19</v>
@@ -2488,31 +2539,31 @@
         <v>19</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>30</v>
@@ -2523,13 +2574,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -2541,31 +2592,31 @@
         <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>30</v>
@@ -2576,10 +2627,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>19</v>
@@ -2594,31 +2645,31 @@
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>30</v>
@@ -2629,10 +2680,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -2641,37 +2692,37 @@
         <v>19</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>30</v>
@@ -2682,10 +2733,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -2694,37 +2745,37 @@
         <v>19</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>30</v>
@@ -2735,13 +2786,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>19</v>
@@ -2753,31 +2804,31 @@
         <v>19</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>30</v>
@@ -2788,10 +2839,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>19</v>
@@ -2800,37 +2851,37 @@
         <v>19</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>30</v>
@@ -2841,10 +2892,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>19</v>
@@ -2853,37 +2904,37 @@
         <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>30</v>
@@ -2894,10 +2945,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -2912,31 +2963,31 @@
         <v>19</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>30</v>
@@ -2947,10 +2998,10 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>19</v>
@@ -2965,31 +3016,31 @@
         <v>19</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>30</v>
@@ -3000,10 +3051,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>19</v>
@@ -3018,31 +3069,31 @@
         <v>19</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>30</v>
@@ -3053,10 +3104,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>19</v>
@@ -3071,31 +3122,31 @@
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>30</v>
@@ -3106,16 +3157,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
@@ -3124,31 +3175,31 @@
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>30</v>
@@ -3159,10 +3210,10 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -3171,7 +3222,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>19</v>
@@ -3180,28 +3231,28 @@
         <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>30</v>
@@ -3212,10 +3263,10 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -3224,7 +3275,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
@@ -3233,28 +3284,28 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>30</v>
@@ -3265,10 +3316,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
@@ -3277,37 +3328,37 @@
         <v>19</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>30</v>
@@ -3318,16 +3369,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>19</v>
@@ -3336,31 +3387,31 @@
         <v>19</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>25</v>
+        <v>236</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>30</v>
@@ -3371,10 +3422,10 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
@@ -3389,31 +3440,31 @@
         <v>19</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>30</v>
@@ -3424,49 +3475,49 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>30</v>
@@ -3477,10 +3528,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>19</v>
@@ -3489,37 +3540,37 @@
         <v>19</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>30</v>
@@ -3530,49 +3581,49 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>30</v>
@@ -3583,10 +3634,10 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -3595,37 +3646,37 @@
         <v>19</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>30</v>
@@ -3636,10 +3687,10 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -3654,28 +3705,28 @@
         <v>19</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>25</v>
+        <v>287</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>29</v>
@@ -3684,15 +3735,15 @@
         <v>30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -3701,7 +3752,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>19</v>
@@ -3710,25 +3761,25 @@
         <v>21</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>29</v>
@@ -3737,15 +3788,15 @@
         <v>30</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -3760,45 +3811,45 @@
         <v>19</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q34" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -3813,45 +3864,45 @@
         <v>19</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -3866,45 +3917,45 @@
         <v>19</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -3913,51 +3964,51 @@
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -3966,104 +4017,104 @@
         <v>19</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>25</v>
+        <v>337</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -4081,42 +4132,42 @@
         <v>21</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -4131,45 +4182,45 @@
         <v>19</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>25</v>
+        <v>361</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -4184,45 +4235,45 @@
         <v>19</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>25</v>
+        <v>367</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -4231,51 +4282,51 @@
         <v>19</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -4284,7 +4335,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>19</v>
@@ -4293,42 +4344,42 @@
         <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -4337,51 +4388,51 @@
         <v>19</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -4390,7 +4441,7 @@
         <v>19</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>19</v>
@@ -4399,42 +4450,42 @@
         <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -4443,7 +4494,7 @@
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>19</v>
@@ -4452,42 +4503,42 @@
         <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -4496,7 +4547,7 @@
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>19</v>
@@ -4505,42 +4556,42 @@
         <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -4549,51 +4600,51 @@
         <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -4602,51 +4653,51 @@
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -4655,51 +4706,51 @@
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -4714,37 +4765,37 @@
         <v>19</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4764,10 +4815,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4775,7 +4826,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4783,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4791,7 +4842,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4799,7 +4850,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4807,23 +4858,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -4843,18 +4894,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4862,7 +4913,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4870,7 +4921,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4878,15 +4929,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4894,15 +4945,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4910,7 +4961,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="추천DB" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="버튼선택지" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="안내" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="요강조문" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="717">
   <si>
     <t>번호</t>
   </si>
@@ -1632,6 +1633,1054 @@
   </si>
   <si>
     <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 공개 위치: 캠코 홈페이지 정보공개 &gt; 법무자료 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100). 2026-10-29 확인 시 게시본은 2026.6.29. 일부개정·시행본이라, 바뀐 조항이 있으면 다시 맞춰야 한다.</t>
+  </si>
+  <si>
+    <t>요강조문</t>
+  </si>
+  <si>
+    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본) 본문 조문 73개를 원문 그대로 옮긴 시트. 추천DB "관련 규정" 칸의 조문 번호로 찾아 카드에 전문을 보여 준다.</t>
+  </si>
+  <si>
+    <t>조문</t>
+  </si>
+  <si>
+    <t>제목</t>
+  </si>
+  <si>
+    <t>장</t>
+  </si>
+  <si>
+    <t>전문</t>
+  </si>
+  <si>
+    <t>제1조</t>
+  </si>
+  <si>
+    <t>목적</t>
+  </si>
+  <si>
+    <t>제1장 총칙</t>
+  </si>
+  <si>
+    <t>이 요강은 소상공인자영업자새출발기금 주식회사로부터 위탁받은 수탁채권에 대하여 「소상공인·자영업자 새출발기금 지원 협약」, 「소상공인자영업자새출발기금 운영 기준」 등에 따라 해당채권의 관리·운용·처분 및 기타 업무수행을 위한 세부사항, 절차 및 방법을 규정함을 목적으로 한다.</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 (2026.3.25. 시행본) — 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+  </si>
+  <si>
+    <t>제2조</t>
+  </si>
+  <si>
+    <t>정의</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 요강에서 사용하는 용어의 뜻은 다음과 같다. 다만, 이 요강에서 정의되지 않은 용어의 정의는 「소상공인·자영업자 새출발기금 지원 협약」(이하 “협약”이라 한다)에 따른다.
+1. “대상차주”란 소상공인자영업자새출발기금 주식회사(이하 “새출발기금”이라 한다)의 지원 대상에 해당하는 협약 제2조제9호에 해당하는 자를 말한다.
+2. “주채무자”란 대상차주와 합명·합자회사(법률상 이에 준하는 회사를 포함한다)의 무한책임사원 중 대표자를 말한다.
+3. “채무관계자”란 주채무자, 연대보증인, 물상보증인, 어음의 발행인ㆍ배서인과 그 각각의 상속인을 말한다.
+4. “채무조정”이란 채무관계자의 상환능력 또는 채권의 회수가능성을 고려하여 채무의 감면, 상환기간의 연장 및 분할상환 등을 통해 채무의 내용을 변경함으로써 채무관계자의 채무부담 완화 및 신용회복과 경제적 재기를 지원하는 것을 말한다.(2024.12.30. 본호개정)
+5. “채권금융회사”란 협약에 가입하고, 대상차주에 대하여 채권을 보유하고 있거나 새출발기금에 대상차주에 대한 채권을 양도한 금융회사 또는 보증기관 등을 말한다.
+6. “부실차주”란 채무조정 신청일 현재 대상차주가 채권금융회사에 대하여 부담하는 1개 이상의 채무에서 3개월 이상 연체가 발생하여 계속되고 있는 채무자(중개형 채무조정의 효력이 상실된 채무자 중 매입형 채무조정을 신청한 채무자 또는 새출발기금이 매입한 채무자 포함)를 말한다.(2024.12.30. 본호개정)
+7. “부실우려차주”란 채무조정 신청일 현재 채권금융회사의 자산건전성 분류 상 ‘요주의’ 이하로 평가하는 채권의 채무자 등 장기연체 발생 확률이 높은 것으로 인정되는 대상차주 중 부실차주에 해당하지 않는 자로서 「소상공인자영업자새출발기금 운영 기준」에서 정하는 자를 말한다.
+8. “사회취약계층”이란 부실차주에 해당하는 채무관계자로서 별표 1의 사회취약계층 감면표에서 정하는 사람을 말한다.
+9. “거치기간”이란 채무관계자가 신청한 일정기간동안 이자만 납부하고 원금상환을 유예하는 기간을 말한다.
+10. “채무부담액”이란 채무관계자의 소유재산 유무, 상환능력 등을 고려하여 산정된 채무조정 후에 채무관계자가 상환하여야 하는 금액을 말한다.
+11. “영업일”이란 대한민국 내에서 은행이 영업을 하는 날(토요일 및 일부 은행이나 어느 은행의 일부 점포만 영업을 하는 날은 제외한다)을 말한다.
+12. “자산관리자”란 새출발기금 지원 사업의 관리ㆍ운용, 기타 사무 등의 업무 및 자산의 관리ㆍ운용, 처분 등의 업무를 새출발기금으로부터 위탁받은 한국자산관리공사를 말한다.
+13. “보조자산관리자”란 새출발기금 또는 자산관리자로부터 직접 추심 등에 관한 업무를 위임 또는 위탁받아 수행하는 채권금융회사, 채권추심회사를 말한다.
+14. “양도자산확정일”이란 새출발기금이 양수할 채권을 확정하는 기준이 되는 날로써 채권금융회사와의 양수도계약 체결일이 속한 달의 전 월 마지막 영업일을 말한다. 다만, 협약 또는 계약당사자와의 협의가 있는 경우에는 그 협의에 따른다.(2026.3.25. 단서신설)
+15. “채무조정확정안 승인일”이란 채무조정 신청인으로부터 채무조정 신청을 받아 적정여부를 검토한 후 작성한 채무조정확정안에 대해 전결권자의 승인을 받은 날을 말한다.
+16. “채무조정 약정일”이란 자산관리자가 작성한 채무조정확정안에 대하여 채무조정 신청인이 인증서·자필서명 등을 통해 채무조정확정안의 합의 및 그 이행을 확약한 날을 말한다.
+17. “약정금리”란 채무관계자가 채권금융회사와 약정한 금리를 말하며, 이를 적용하여 계산한 이자를 “약정이자”라 한다.
+18. “연체금리”란 채무관계자가 채권금융회사에 대한 채무를 연체하였을 경우 약정금리에 가산하는 금리를 말하며, 이를 적용하여 계산한 이자를 “연체이자”라 한다.
+19. “조정금리”란 새출발기금의 채무조정 시에 적용하는 금리로써 새출발기금 이사회에서 별도로 정한 금리를 말한다.
+20. “기발생이자”란 각 채권금융회사와 새출발기금 간 양수도한 채권에 대하여 양도자산확정일까지 해당 채권금융회사로부터 이미 발생한 약정이자 및 연체이자를 말한다.
+21. “경과이자”란 양도자산확정일 다음날부터 채무조정확정안 승인일까지 각 채권금융회사 약정금리를 적용하여 계산한 이자를 말한다.
+22. “거치기간이자”란 채무조정확정안 승인일 다음날부터 거치기간동안 채무부담액에 대하여 부과하는 이자를 말한다.
+23. “발생이자”란 채무조정확정안 승인일(거치기간이 있는 경우에는 거치기간 종료일로 한다) 다음날부터 상환기간에 따라 잔여 채무부담액에 대하여 부과하는 이자를 말한다.
+24. “가지급금”이란 채권의 보전처분 및 권리행사를 위해 양도자산확정일 이전에 채권금융회사에서 지출한 비용의 총액으로 경매신청비용, 가압류·가처분 및 강제집행비용, 시효중단 목적의 소송비용, 담보물 보전·관리비용(화재보험료, 관리용역비 등을 포함한다), 법무사 비용 및 변호사 선임비용 등을 말한다.
+25. “제비용”이란 양도자산확정일 이후 채권금융회사 또는 새출발기금이 지출한 경매비용(법적조치 취하 비용을 포함한다)과 소송(지급명령을 포함한다)비용 중 채무관계자와 직접 관련된 비용을 말한다. 다만, 주채무자의 경우에는 관련 비용 전액을 말한다.
+26. “대상채권”이란 채무관계자가 채무조정을 받기 이전에 새출발기금이 해당 채무관계자에 대하여 가지고 있거나 협약을 체결한 채권금융회사가 채무관계자에 대하여 가지는 채권 중 새출발기금의 지원 대상이 되는 채권의 원금, 그에 부수하는 이자(기발생이자, 경과이자 등을 말한다), 가지급금, 각종 수수료 및 제비용 등의 채권을 말하며, 채무관계자의 입장에서 “대상채무”라 한다.
+27. “회차”란 채무관계자가 채무부담액을 상환하는 기간을 월 단위로 구분한 순서를 말한다.
+28. “분할상환금”이란 대상채권의 계좌별로 채무관계자마다 개별적으로 산정된 채무부담액을 분할상환기간동안 회차별 변제하여야 하는 금액을 말한다.
+29. “담보부채권“이란 채권금융회사가 담보권 등을 행사하여 회수할 수 있는 채권을 말한다.
+30. “부동산담보부채권“이란 담보부채권 중에서 부동산을 목적물로 한 저당권 또는 근저당권 등을 행사하여 회수할 수 있는 채권을 말한다.
+31. “동산담보부채권”이란 담보부채권 중에서 「동산·채권 등의 담보에 관한 법률」에 따라 동산담보물에 담보권이 설정되어 등기된 동산담보권 또는 동산근담보권으로 담보되는 채권을 말한다.
+32. “무담보채권”이란 채권금융회사가 담보 없이 신용 등으로 대출을 취급한 채권과 담보부채권의 담보물 정리 후 잔여 채권을 말한다.
+33. “회수가능재산”이란 새출발기금이 대상채권의 채무관계자로부터 회수할 수 있는 재산을 말한다.
+34. “유효담보가액” 또는 “회수가능액”이란 별표 2의 “유효담보가액 및 회수가능액 산정기준”에 따라 산정한 금액을 말한다.
+35. “재약정”이란 채무조정의 효력이 상실된 채무관계자와 채무조정의 약정을 새로이 맺는 것을 말한다.
+36. “신용도판단정보”란 한국신용정보원의 「일반신용정보관리규약」에 따른 연체정보·대위변제정보·대지급정보 등을 말한다.
+37. “주택”이란 「주택법」 제2조제1호에 따른 주택, 같은 법 제2조제4호에 따른 준주택 및 같은 법 제2조제6호에 따른 주거의 용도로만 쓰이는 면적이 개별 건축물 연면적의 50% 이상인 건축물을 말한다.
+38. “사물인터넷디바이스(IOT)”란 담보물의 관리를 위해 동산에 부착하는 전자적 식별장치로 데이터 송·수신 등 자체적인 통신기능이 있는 것을 말한다.
+39. “매입전산자료”란 채권금융회사가 제공한 전산상의 대상채권 주채무자정보, 채무관계자정보, 대출계좌정보, 법원사건정보, 신용정보 등을 말한다.
+40. “주무부점”이란 「업무분장세칙」에 따라 새출발기금 관련 채권관리업무를 총괄하여 수행하는 부점을 말한다.(2024.12.30. 본호개정)
+41. “업무총괄부점”이란 「업무분장세칙」에 따라 새출발기금 운영을 총괄하여 수행하는 부점을 말한다.(2024.12.30. 본호개정)
+42. “채권추심”이란 채무관계자에 대한 소재파악 및 재산조사, 인수채권에 대한 변제 요구, 채무관계자로부터 변제 수령 등 채권의 만족을 얻기 위한 일체의 행위를 말한다.(2024.12.30. 본호신설)
+43. “개인금융채권”이란 「개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률」(이하 “개인채무자보호법”이라 한다) 제2조제1호의 채권을 말한다.(2024.12.30. 본호신설)
+44. “개인금융채무자”란 채무관계자 중 개인채무자보호법 제2조제3호에서 정하는 사람을 말한다.(2024.12.30. 본호신설)
+45. “저소득 차주“란 새출발기금 신청(새출발기금 웹플랫폼 또는 신용회복위원회를 통해 신청한 것을 말한다) 당시 총채무액 1억원 이하이면서 소득이 신용회복위원회의 신용회복지원협약 등에서 정한 부양가족수에 따른 최저생계비의 100분의 150 이하(중위소득 100분의 60 이하)인 부실 차주를 말한다.(2025.9.19. 본호신설)
+46. “CMS(Cash Management Service)이체 방식“이란 채무자가 지정한 금융회사 등의 계좌에서 분할상환금을 출금하여 회사가 지정한 계좌로 입금하는 방식을 말한다.(2025.9.19. 본호신설)</t>
+  </si>
+  <si>
+    <t>제3조</t>
+  </si>
+  <si>
+    <t>적용범위</t>
+  </si>
+  <si>
+    <t>이 요강은 새출발기금으로부터 위탁받은 수탁채권의 관리·운용·처분 및 기타 업무수행 등에 대하여 적용한다.</t>
+  </si>
+  <si>
+    <t>제4조</t>
+  </si>
+  <si>
+    <t>다른 법령 등과의 관계</t>
+  </si>
+  <si>
+    <t>새출발기금으로부터 위탁받은 수탁채권의 관리·운용·처분 및 기타 업무수행 등에 대하여 관련 법령, 감독기관의 지침·예규, 업무 및 자산관리위탁계약서, 새출발기금의 정관, 「소상공인자영업자새출발기금 운영 기준」 및 협약에 따로 정한 것을 제외하고는 이 요강이 정하는 바에 따른다.</t>
+  </si>
+  <si>
+    <t>제5조</t>
+  </si>
+  <si>
+    <t>요강외 취급</t>
+  </si>
+  <si>
+    <t>이 요강에서 정하지 아니한 사항은 업무처리를 하기 전에 요강외 취급사항임을 명시하여 부사장의 승인을 얻어야 한다.</t>
+  </si>
+  <si>
+    <t>제5조의2</t>
+  </si>
+  <si>
+    <t>기한의 이익 상실예정의 통지</t>
+  </si>
+  <si>
+    <t>제2장 연체 관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 새출발기금이 매입한 원금 3,000만원 미만의 개인금융채권이 연체로 인해 기한의 이익이 상실되는 경우에는 기한의 이익 상실 예정일의 10영업일 전까지 다음 각 호의 사항이 포함된 별지 제34호서식 기한의 이익 상실 예정통지서로 개인금융채무자에게 통지하여야 한다.
+1. 기한의 이익 상실 예정일
+2. 기한의 이익 상실 원인
+3. 기한의 이익 상실 효과
+4. 채무조정의 요건과 요청 절차ㆍ방법
+5. 채무조정 요청 시 기한의 이익이 상실되지 않는다는 내용 등
+② 제1항에 따른 통지가 기한의 이익 상실 예정일의 10영업일 전까지 채무관계자에게 도달하지 아니한 경우에 기한의 이익 상실일은 그 통지가 도달한 날부터 10영업일이 지난 날로 한다.
+③ 제1항에 따른 통지가 2회 이상 반송되거나 개인금융채무자의 주소 등 연락처를 통상적인 방법으로 확인할 수 없는 경우에는 새출발기금 인터넷 홈페이지에 기한의 이익 상실 사실을 게재하는 방법으로 그 통지를 갈음할 수 있으며, 이 경우 게재일로부터 10영업일이 지난 날을 기한의 이익 상실일로 본다.
+④ 제1항부터 제3항까지에도 불구하고 채무관계자가 다음 각 호의 구분에 따른 날까지 채무조정을 요청하는 경우에는 그 채무조정의 절차가 끝나기 전까지 기한의 이익이 상실되지 않는다. 다만, 다른 채권자가 개인금융채무자에 대하여 강제집행을 법원에 신청하는 경우에는 신청한 날에 기한의 이익이 상실된 것으로 본다.
+1. 제1항에 따른 통지가 기한의 이익 상실 예정일의 10영업일 전까지 개인금융채무자에게 도달한 경우: 기한의 이익 상실 예정일 전일
+2. 제2항에 해당하는 경우: 제1항에 따른 통지가 도달한 날부터 10영업일이 되는 날
+3. 제3항에 해당하는 경우: 새출발기금의 인터넷 홈페이지에 게재 등을 한 날부터 10영업일이 되는 날
+[2024.12.30. 본조신설]</t>
+  </si>
+  <si>
+    <t>제5조의3</t>
+  </si>
+  <si>
+    <t>연체이자의 제한 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">새출발기금이 매입한 원금 5,000만원 미만 개인금융채권에 대해서는 별표 9 소액 개인금융채권 이자 부과기준에 따라 이자를 면제 또는 부과한다.(2024.12.30. 본조신설, 2025.5.29. 본조개정)
+[2025.5.29. 제목개정]</t>
+  </si>
+  <si>
+    <t>제6조</t>
+  </si>
+  <si>
+    <t>담보물 보전 및 관리</t>
+  </si>
+  <si>
+    <t>제3장 담보물의 보전·관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 담보물의 보전 및 관리는 「경비업법」에 따라 경비업의 허가를 받은 법인(이하 “경비회사”라 한다)과 관리용역계약을 체결하여 관리한다. 다만, 관리용역계약 체결이 곤란하거나 그 밖의 사유로 필요하다고 인정되는 경우에는 담보물을 관리하는 부점장의 승인을 얻어 달리 정할 수 있다.
+② 담보물을 관리함에 있어 담보물의 가치, 성질, 이동가능성 등을 고려하여 사물인터넷디바이스(IOT) 전문업체를 이용하여 경비하거나 담보물을 창고 업체에 위탁하여 보관할 수 있다.
+③ 담보물 보전 및 관리를 위하여 필요한 경우에는 해당 담보물에 새출발기금이 보유한 채권의 담보물임을 나타내는 표지를 부착할 수 있다.
+④ 양도담보물의 관리와 처분은 별표 5 새출발기금 양도담보물 관리ㆍ처분 기준에 따르고, 기계기구 경비는 별표 6 기계기구 경비용역 실시기준에 따른다.(2024.9.11., 2024.12.30. 본항개정)
+⑤ 제4항에도 불구하고 담보물 중 공장의 기계기구 보전관리는 「기계기구 유지보수·개보수 및 분리매각요강」에서 정하는 바에 따른다.(2024.9.11. 본항개정)
+⑥ 제1항부터 제5항까지 규정된 사항 외에 담보물 보전 및 경비관리업무의 세부절차 및 방법 등은 「경비관리업무처리요강」에서 정한 바에 따른다.(2024.9.11. 본항신설)</t>
+  </si>
+  <si>
+    <t>제6조의2</t>
+  </si>
+  <si>
+    <t>담보물 점검</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 담보물건에 대한 점검방법은 다음과 같다. 다만, 경비회사 등에서 관리하는 경우에는 이상유무보고서로 갈음할 수 있다.
+&lt;table border="1" cellspacing="0" cellpadding="4" style="border-collapse:collapse"&gt;
+&lt;tr&gt;
+&lt;td&gt;
+&lt;p&gt;종          류&lt;/p&gt;
+&lt;/td&gt;
+&lt;td&gt;
+&lt;p&gt;점검 주기&lt;/p&gt;
+&lt;/td&gt;
+&lt;td&gt;
+&lt;p&gt;점검횟수&lt;/p&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;
+&lt;p&gt;건물. 공장&lt;/p&gt;
+&lt;/td&gt;
+&lt;td&gt;
+&lt;p&gt;6개월&lt;/p&gt;
+&lt;/td&gt;
+&lt;td rowspan="2"&gt;
+&lt;p&gt;1회 이상&lt;/p&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td&gt;
+&lt;p&gt;기계기구 등 동산&lt;/p&gt;
+&lt;/td&gt;
+&lt;td&gt;
+&lt;p&gt;3개월&lt;/p&gt;
+&lt;/td&gt;
+&lt;/tr&gt;
+&lt;/table&gt;
+② 도난, 멸실, 훼손, 변질 또는 무단점유 등의 우려가 있을 때에는 제1항에도 불구하고 수시로 점검하여야 한다.
+③ 제1항에도 불구하고 사고발생의 우려가 없을 것으로 예상되거나 점검을 실시하기 곤란한 사유가 발생한 경우에는 정기점검을 생략하거나 점검기간을 연장할 수 있다.
+④ 등록원부를 통해 관리되는 동산 담보물건에 대한 점검은 생략할 수 있다.
+[2024.9.11. 본조신설]</t>
+  </si>
+  <si>
+    <t>제7조</t>
+  </si>
+  <si>
+    <t>담보물 멸실·훼손 등에 따른 책임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 담보물이 채무관계자의 고의 또는 과실로 멸실·훼손되거나 그 밖의 사유로 담보가치가 감소되었을 때에는 그 채무관계자에게 채권액 전부 또는 일부를 상환하게 하거나 추가로 담보를 제공하게 하여야 한다.
+② 담보물 도난, 분실 등의 사고가 발생한 경우에는 채무관계자 또는 경비회사 등 사고를 일으킨 자에게 원상복구를 내용증명 등으로 촉구하여야 한다.</t>
+  </si>
+  <si>
+    <t>제8조</t>
+  </si>
+  <si>
+    <t>보험계약 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 멸실·훼손의 염려가 있는 담보물은 새출발기금의 명의로 화재보험 등 필요한 보험에 가입하여야 한다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 담보물을 관리하는 부점장의 승인을 얻어 보험가입을 생략할 수 있다.
+1. 원금채권액(신용보증서, 금융기관지급보증서는 제외한 금액을 말한다)이 토지가용담보가액(토지감정가격에서 선순위 저당권으로 담보된 금액을 공제한 금액을 말한다) 이하인 경우
+2. 원금채권액이 3,000만원 이하인 담보물 중 토지가 포함된 주택
+3. 아파트, 주상복합건물, 오피스텔 등 법령에 따라 공동주택 관리체계가 구성되어 있거나 화재보험이 의무적으로 가입되어 있는 공동주택 또는 집합건물(단, 소규모 공동주택 등 공동주택 관리체계가 미흡하여 재해발생에 대한 보험 가입이 필요하다고 판단한 경우에는 제외한다)(2024.9.11. 본호신설)
+② 제1항의 보험계약은 채무의 상환이 종료되거나 담보물에 대한 처분절차가 종료될 때까지 계속하여야 하며, 보험료는 새출발기금이 부담한다.
+③ 보험의 목적인 담보물이 멸실·훼손되었을 때에는 지체 없이 보험회사에 통지하고 보험금의 지급을 청구하여 채무의 상환에 충당하여야 한다.</t>
+  </si>
+  <si>
+    <t>제9조</t>
+  </si>
+  <si>
+    <t>보험금액의 책정</t>
+  </si>
+  <si>
+    <t>제8조제1항에 따라 보험에 가입하는 경우의 보험금액은 원금채권액의 120%에서 토지가용담보가액을 공제한 금액 이상으로 하되, 보험에 가입할 담보물 감정가격의 100%를 초과할 수 없다.(2024.9.11. 본조개정)</t>
+  </si>
+  <si>
+    <t>제10조</t>
+  </si>
+  <si>
+    <t>보험계약의 해지</t>
+  </si>
+  <si>
+    <t>담보물이 제3자에게 매각되었을 경우 매수인이 매수대금을 완납한 때에 보험계약을 해지하여야 한다.</t>
+  </si>
+  <si>
+    <t>제11조</t>
+  </si>
+  <si>
+    <t>채무조정의 신청</t>
+  </si>
+  <si>
+    <t>제4장 채무조정의 신청 및 약정 체결</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무조정의 신청은 대상채권의 채무관계자가 새출발기금의 온라인 플랫폼을 통하여 신청한다. 다만, 채무관계자가 온라인 플랫폼을 이용하여 신청하기 어려운 경우에는 새출발기금 상담창구 등을 통하여 신청할 수 있다.
+② 주채무자의 순자산(자산-부채)규모가 6.5억원을 초과하는 경우에는 채무조정 지원 대상에서 제외한다. 다만, 1회 이상 채무조정 약정을 체결한 이력이 있는 채무관계자의 경우에는 채무조정 지원 대상으로 한다.
+③ 채무관계자가 대리인을 통하여 채무조정을 신청하고자 할 경우에는 채무조정 신청 위임장(별지 제1호서식 또는 별지 제2호서식)을 수령하고 대리권이 있는지 여부를 확인하여야 한다.
+④ 채무관계자가 아닌 제3자가 채무부담액의 전부 또는 일부에 대하여 대위변제를 신청하는 경우에는 별지 제3호서식의 대위변제에 대한 승낙서를 받은 후 변제받을 수 있다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 대위변제에 대한 승낙서 제출을 생략할 수 있다.
+1. 채무관계자가 아닌 제3자가 구상권을 행사하지 않기로 동의하여 별지 제4호서식의 대위변제 신청서를 받은 경우
+2. 변제할 정당한 이익이 있는 자인 경우
+⑤ 제4항에 따라 채무관계자가 아닌 제3자가 대위변제할 경우에는 채무관계자의 채무조정기준에 따라 처리한다.
+⑥ (2024.9.11. 본항삭제)</t>
+  </si>
+  <si>
+    <t>제11조의2</t>
+  </si>
+  <si>
+    <t>채무조정의 안내</t>
+  </si>
+  <si>
+    <t>채무관계자로부터 채무조정의 요청을 받은 때에는 별표 7의 “새출발기금 채무조정 내부기준”에 따라 업무를 처리하여야 한다.(2024.12.30. 본조신설)</t>
+  </si>
+  <si>
+    <t>제12조</t>
+  </si>
+  <si>
+    <t>채무조정의 신청서류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채무관계자가 채무조정을 신청할 경우에는 채무관계자로부터 다음 각 호에 해당하는 서류를 수령 또는 확인하여야 한다.
+1. 채무승인 및 조정 확약서(일시상환용)(별지 제5호서식) 또는 채무승인 및 조정 확약서(분할상환용)(별지 제6호서식)
+2. 사업자등록증
+3. 신분증(법인 소상공인의 경우에는 소상공인확인서, 특수형태근로종사자 및 프리랜서의 경우에는 긴급고용안정지원금 입출금거래내역서)
+4. 개인(신용)정보 수집·이용·제공 동의서(별지 제7호서식)
+5. 개인(신용)정보 수집·이용·제공·조회 동의서(별지 제8호서식)
+6. 행정정보 공동이용 사전동의서(별지 제9호서식)
+7. (분할상환용) CMS 출금이체 신청서(별지 제38호서식)(2025.9.19. 본호신설)
+8. 새출발기금 대상확인 및 채무조정신청서(별지 제40호서식)(2026.3.25. 본호신설)
+9. 공공 마이데이터 처리를 위한 개인정보 수집·이용·제공 동의서(별지 제41호서식)(2026.3.25. 본호신설)</t>
+  </si>
+  <si>
+    <t>제13조</t>
+  </si>
+  <si>
+    <t>신청의 효력</t>
+  </si>
+  <si>
+    <t>업무총괄부점의 장은 대상채권의 채무관계자가 채무조정 신청을 완료한 날의 다음 영업일 이내에 채권금융회사에게 채무관계자에 대한 추심행위, 강제경매 및 담보물에 대한 임의경매 등의 중지를 요청하여야 한다.(2024.12.30., 2026.1.20. 본조개정)</t>
+  </si>
+  <si>
+    <t>제14조</t>
+  </si>
+  <si>
+    <t>재산조사</t>
+  </si>
+  <si>
+    <t>주무부점의 장은 행정정보 공동이용망 등을 통하여 채무관계자의 소유재산 유무를 확인하여야 한다. 다만, 채무관계자가 채무부담액을 완제한 이후의 재산조사는 1회에 한한다.</t>
+  </si>
+  <si>
+    <t>제15조</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 채무조정의 신청을 완료한 경우에는 한국신용정보원에서 제공한 채무액을 기초로 작성한 채무조정임시안을 주무부점의 소관업무 담당 팀장의 승인을 얻어 채무조정의 신청일의 다음날로부터 2주일 이내에 신청인에게 제시하여야 한다.
+② 채권금융회사로부터 대상채권의 인수가 완료된 경우 매입전산자료, 원인서류(대출약정서, 대위변제증서 등을 포함한다) 등을 확인하여 채무조정확정안을 「위임전결규정」 별표의 Ⅲ-1-라-(1)에 따른 전결권자의 승인을 얻어 신청인에게 제시하여야 한다.
+③ 제2항에 따른 채무조정확정안의 승인권자는 채무관계자의 소유재산 여부, 소득수준, 채무자의 연령, 상환기간 등을 종합적으로 검토하여 채무조정확정안의 승인 여부를 결정하여야 한다. 다만, 담보부채권의 경우에는 검토를 생략할 수 있다.
+④ 채권금융회사의 요청에 의해 매입한 대상채권의 경우에는 해당채권의 채무관계자에게 우편 또는 문자메시지 등을 통해 채무상환을 안내하며, 채무관계자가 채무조정 신청 시에는 제2항에 따라 채무조정확정안을 신청인에게 제시하여야 한다.</t>
+  </si>
+  <si>
+    <t>제16조</t>
+  </si>
+  <si>
+    <t>채무조정 신청의 취소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자는 채무조정의 신청을 완료한 날이 속한 달의 다음 달 15일까지 채무조정 신청의 취소를 할 수 있다.
+② 제1항에 따라 채무조정 신청을 취소한 채무관계자는 취소 신청일부터 3개월까지 채무조정의 재신청이 제한된다.</t>
+  </si>
+  <si>
+    <t>제17조</t>
+  </si>
+  <si>
+    <t>채무조정 약정의 체결</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무조정 약정을 체결할 때에는 신청자가 전자서명 또는 자필로 기재하여야 하는 모든 신청서, 약정서 등의 기재사항이 빠짐없이 기재되었는지 여부 및 채무부담액 산정의 기초자료(나이, 소득, 재산, 유효담보가액 등을 말한다. 이하 같다)와의 일치여부를 확인하여야 한다.
+② 채무관계자는 채무조정확정안 승인일의 다음날부터 5영업일 이내에 「전자서명법」 제8조에 따라 운영기준 준수사실의 인정을 받은 전자서명인증사업자로부터 발급받은 인증서 또는 자필서명 등의 방법으로 채무조정확정안에 대한 합의 및 그 이행을 확약하여야 하며, 해당 기간이 도과된 경우에는 채무조정 신청을 취소한 것으로 본다.
+③ 주무부점의 장은 채무조정확정안에 대한 합의 및 그 이행을 확약 시에 채무관계자로부터 별지 제10호서식의 개인(신용)정보 수집·이용·제공 동의서(상품서비스 안내 등)를 제출받고 재기지원 사업(취업알선 및 상품안내 등)에 대한 안내를 할 수 있다.</t>
+  </si>
+  <si>
+    <t>제17조의2</t>
+  </si>
+  <si>
+    <t>미약정자의 임의변제</t>
+  </si>
+  <si>
+    <t>새출발기금이 대상채권을 매입한 후 채무관계자가 채무를 상환하지 않거나 채무조정지원 대상이 아니어서 채무조정을 진행할 수 없는 경우에는 양도자산확정일로부터 임의변제일 또는 법적조치 등을 통한 회수일까지 채권금융회사의 약정금리를 적용하여 채무부담액을 산정하여, 채무관계자에게 변제를 요청할 수 있다. 다만, 원금이 3,000만원 미만으로 개인채무자보호법 제9조에 따라 장래이자채권이 면제된 개인금융채무자에 대해서는 양도자산확정일 이후 이자는 면제한다.(2024.9.11. 본조신설, 2024.12.30. 단서신설)</t>
+  </si>
+  <si>
+    <t>제18조</t>
+  </si>
+  <si>
+    <t>채무조정 방법</t>
+  </si>
+  <si>
+    <t>제5장 채무조정의 내용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무조정을 신청한 채무관계자는 일시상환 방식 또는 분할상환 방식 중에서 상환 방식을 선택 할 수 있다. 다만, 채무부담액이 10만원 이하인 경우에는 일시상환 방식으로 하여야 한다.(2024.12.30. 본항개정)
+② 채무조정의 약정은 채무관계자를 기준으로 체결하되, 대상채권 계좌별로 채무부담액을 개별적으로 산정한 후 이를 합산하여 채무관계자와 일괄 약정한다.
+③ 일괄 약정을 체결할 경우 납부(가상)계좌는 대상차주 단위로 부여한다. 다만, 부실차주가 담보부채무 및 무담보채무를 동시에 채무조정 신청하는 경우에는 채무별로 개별 약정하고, 납부(가상)계좌를 각각 부여할 수 있다.</t>
+  </si>
+  <si>
+    <t>제19조</t>
+  </si>
+  <si>
+    <t>채무부담액의 산정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 부실우려차주 및 그 채무관계자는 원금, 기발생이자, 경과이자, 가지급금을 합산하여 채무부담액으로 산정하되, 기발생이자는 채무유형에 따라 다음 각 호의 기준을 적용한다. 단, 최초약정에 한하여 경과이자를 제외한 금액으로 채무부담액을 산정한다.(2024.9.11. 단서신설)
+1. 무담보채권 : 각 채권금융회사의 연체이자를 전액 감면
+2. 담보부채권 : 채무부담액에서 가지급금을 제외한 금액이 유효담보가액을 초과하는 경우 초과하는 범위에서 각 채권금융회사의 연체이자를 감면
+② 부실차주 및 그 채무관계자의 채무부담액은 별표 3의 부실차주의 채무유형별 채무부담액 산정기준에 따라 산정한다.
+③ 제1항의 부실우려차주 및 그 채무관계자가 3개월 이상 연체 등으로 채무조정약정의 효력이 상실되거나, 협약 제16조 제1항의 신용회복지원협약에서 정하는 사유에 따라 중개형 채무조정약정의 효력이 상실되는 경우 해당 부실우려차주에 대하여 협약 제10조 내지 제13조에서 정한 매입형 채무조정을 실시하며, 채무부담액은 별표 3 부실차주의 채무유형별 채무부담액 산정기준에 따라 산정한다.(2024.9.11. 본항신설)
+④ 본 조 차주에 대한 채무부담액 산정 시 제비용 전액을 채무부담액에 포함한다. 다만, 제비용 중 소송비용은 해당 채무관계자의 소송비용에 채무감면율을 적용한 금액을 채무부담액으로 한다.(2024.9.11. 본항신설, 2024.12.30. 본항개정)
+⑤ 제5조의3에 따라 장래 이자채권을 면제한 개인금융채권에 대해서는 채무조정 시 채무부담액에 경과이자를 부과하지 않는다.(2025.5.29. 본항신설)</t>
+  </si>
+  <si>
+    <t>제20조</t>
+  </si>
+  <si>
+    <t>사회취약계층 감면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 사회취약계층이 채무조정을 신청하는 경우에는 해당기준 부합여부의 확인 후에 별표 1의 사회취약계층 감면표에서 정하는 채무감면율을 적용한다. 다만, 사회취약계층이 재산을 소유한 경우에는 대상채무액에서 회수가능액을 차감한 후에 잔여 대상채무액에 대하여만 감면율을 적용한다.(2025.5.29. 본항개정)
+② 부실차주가 채무조정 약정 이후 사회취약계층(별표 1 소급적용 대상에 한정한다)에 해당하게 된 경우에는 별지 제39호서식 사회취약계층 감면율 소급 신청서를 제출받아 제1항에 따라 감면율을 소급하여 적용할 수 있다.(2025.5.29. 본항신설, 2026.1.20. 본항개정)</t>
+  </si>
+  <si>
+    <t>제20조의2</t>
+  </si>
+  <si>
+    <t>폐업한 부실차주 추가 감면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 2020년 4월 이후 폐업한 부실차주(이하 “폐업부실차주”라 한다)가 새출발기금에서 지정한 취업․재창업 교육을 이수한 사실이 있는 경우 별표 3 부실차주의 채무유형별 채무부담액 산정기준상 Ⅱ. 3. 채무감면율 산정기준에 따라 산정된 채무감면율에 최대 10%p까지 추가 감면율을 적용할 수 있다.
+② 제1항에서 “새출발기금에서 지정한 취업ㆍ재창업 교육”이란 고용노동부가 주관하는 국민취업지원제도 내 취업교육 프로그램 또는 중소벤처기업부가 주관하는 희망리턴패키지 내 재창업 사업화 지원 교육 프로그램, 재취업 지원 교육 프로그램 등을 말하며, 새출발기금 신청기간 종료 전까지의 고용노동부, 중소벤처기업부 등 정부 부처의 취업ㆍ재창업 교육 프로그램을 포함한다.
+③ 폐업부실차주가 제2항의 취업ㆍ재창업 교육을 이수하고 추가 감면을 신청하는 경우 별지 제24호서식에 따른 추가 감면 신청서와 교육 이수 사실을 증명하는 서류를 제출하여야 한다.
+④ 추가 감면 신청일 이전에 채무조정 약정을 체결하고 상환 중인 폐업부실차주가 제3항에 따른 추가 감면을 신청할 경우 기존 체결한 채무조정 약정에서 산정된 채무감면율에 최대 10%p까지 추가 감면율을 적용할 수 있다. 다만, 추가 감면율을 적용하여 재산정한 채무조정금액이 이미 변제한 분할상환금의 합계보다 적을 경우 그 차액은 반환하지 아니한다.
+⑤ 제4항의 추가 감면 신청일 이전에 채무조정 약정을 체결하고 상환 중인 폐업부실차주가 분할상환금을 연체 중인 경우에는 연체된 분할상환금을 모두 납부하여야 제3항에 따른 추가감면을 신청할 수 있다.
+[2024.9.11. 본조신설]</t>
+  </si>
+  <si>
+    <t>제21조</t>
+  </si>
+  <si>
+    <t>거치기간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 최초의 채무조정 약정 시 채무관계자가 신청할 경우 1회에 한하여 거치기간을 부여할 수 있다.
+② 거치기간은 1개월 단위로 최대 1년(12회차)의 기간 내에서 채무관계자와 협의하여 정한다. 다만 다음 각 호의 어느 하나에 해당하는 경우에는 1개월 단위로 최대 3년(36회차)의 기간을 부여할 수 있다.(2025.9.19. 본항개정)
+1. 별표 1의 사회취약계층 중 특례대상자(2025.9.19. 본호신설)
+2. 저소득 차주(2025.9.19. 본호신설)
+3. 부동산담보부 채권(2025.9.19. 본호신설)
+③ 채무관계자는 거치기간동안 채무유형별 채무부담액에 대하여 제22조제2항에 따른 금리를 적용하여 계산한 이자를 납부하여야 한다. 다만, 부실차주의 동산담보부채무에 대해서는 연 2% 금리를 적용하며, 부실차주의 무담보채무에 대해서는 이자를 부과하지 않는다.(2025.9.19. 본항개정)
+④ 제3항에도 불구하고, 채무관계자가 신청할 경우 거치기간 내에서 최대 1년(12회차)의 이자 납부를 유예할 수 있다. 이 경우 유예한 이자는 유예기간의 종료일에 일시 납부하여야 한다.</t>
+  </si>
+  <si>
+    <t>제22조</t>
+  </si>
+  <si>
+    <t>상환기간 및 발생이자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무부담액의 상환기간은 채무 유형에 따라 다음 각 호의 기간을 적용한다.
+1. 무담보채권 또는 동산담보부채권 : 1개월 단위로 최대 10년(120회차) 이내. 다만, 별표 1의 사회취약계층 중 특례대상자 및 저소득 차주에 대하여는 1개월 단위로 최대 20년(240회차) 이내로 한다.(2025.9.19. 본호개정)
+2. 부동산담보부채권 : 1개월 단위로 최대 20년(240회차) 이내(2025.9.19. 본호개정)
+② 부실우려차주 및 그 채무관계자는 상환기간동안 연체기간(채권금융회사 최초연체일로부터 새출발기금 채무조정 신청을 완료한 날까지를 말한다)에 따라 다음 각 호의 기준을 적용한 발생이자를 납부하여야 한다. 다만, 부실우려차주의 대위변제된 구상채권의 조정금리는 3.9%를 적용한다.(2025.9.19. 단서신설)
+1. 연체 30일 이하 : 채권금융회사 약정금리를 그대로 적용하되, 9% 초과 금리에 대해서만 9%로 조정한 이자율 적용. 다만, 사회취약계층 중 특례대상자에 대해서는 제2항제2호에 따른 금리를 적용한다.(2025.9.19. 단서신설)
+2. 연체 30일 초과 : 별표 4의 채무유형별 분할상환기간에 따른 조정금리 기준에 따른 이자율을 적용하되, 약정금리가 조정금리보다 낮은 경우에는 약정금리를 적용
+③ 부실차주 및 그 채무관계자는 상환기간동안 발생이자를 부과하지 않는다. 다만, 부동산 담보부채권에 대해서는 별표 4의 채무유형별 분할상환기간에 따른 조정금리 기준을 적용하여 발생이자를 계산하되, 약정금리가 조정금리보다 낮은 경우에는 약정금리를 적용한다.
+④ 상환기간이 10년을 초과하는 부동산 담보부채권에 대해서는 최대 2회(11년차, 16년차)에 한하여 채무조정 약정일 대비 한국은행 기준금리의 변동분을 반영하여 조정금리를 변경할 수 있다.
+⑤ 거치기간 및 상환유예 기간은 상환기간에 포함하지 않는다.
+⑥ 제2항 및 제3항에도 불구하고 매입전산자료 상 약정금리가 없는 채권에 대해서는 별표 4의 채무유형별 분할상환기간에 따른 조정금리 기준 중 4.7%를 적용한다.(2025.5.29. 본항신설)
+⑦ 제2항에도 불구하고 부실우려차주의 무담보채무에 대해 상환기간 1년 경과할 때마다 최초 적용 이자율의 10%씩 4년간 인하한다. 이 때 최저금리는 3.25%로 한다. (2026.3.25. 본항신설)</t>
+  </si>
+  <si>
+    <t>제23조</t>
+  </si>
+  <si>
+    <t>채무부담액의 상환방법</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 분할상환금의 상환기일은 매월 5, 10, 15, 20, 25일 중에서 채무관계자가 정한 날로 하되, 해당일이 영업일이 아닌 경우에는 다음 영업일을 상환기일로 한다.
+② 분할상환금의 1회차 상환기일은 채무조정 약정일 다음달에 도래하는 상환기일로한다. 다만, 거치기간이 있는 경우에는 거치기간 종료일의 다음 달에 도래하는 상환기일을 1회차 상환기일로 한다.(2024.12.30. 본항개정)
+③ 분할상환금은 천원 단위로 상환하되, 1만원 이상의 금액으로 한다. 이 경우 천원 미만의 금액은 최종회차에 산입하여 상환한다.
+④ 채무관계자가 채무부담액을 일시상환하는 경우에는 채무조정 약정일의 다음날부터 5영업일 이내에 납부하여야 하고, 이 기간 내에 납부하지 않는 경우에는 채무조정 약정 체결의 효력이 상실된다.
+⑤ 모든 이자의 계산은 한편 넣기로 하며, 원미만은 절사한다.
+⑥ 채무부담액에 포함되지 않은 원금 및 모든 이자는 채무조정 약정 만기일까지 상환을 유예한다.</t>
+  </si>
+  <si>
+    <t>제24조</t>
+  </si>
+  <si>
+    <t>상환기간의 변경</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 상환기간(거치기간을 포함한다. 이하 이 조에서 같다)의 변경을 신청하는 경우에는 별지 제11호서식 분할상환 약정기간 변경 신청서를 받아 1회에 한하여 허용할 수 있다.
+② 제1항에 따라 상환기간을 변경하려는 채무관계자는 신청일까지 거치기간이자, 연체된 분할상환금을 모두 상환하여야 한다.(2026.3.25. 본항개정)
+③ 상환기간, 그에 따른 채무부담액 및 조정금리 외에 채무관계자가 최초로 채무조정 약정을 체결할 때의 채무부담액 산정의 기초자료는 변경할 수 없다.
+④ 이미 상환이 진행된 기간은 변경이 가능한 상환기간 산정의 범위에서 제외하며, 상환기간의 변경에 따라 다시 산정한 채무부담액에 대하여 이미 납부한 상환금을 제외한 잔액을 대상으로 상환계획을 수립하여야 한다.
+⑤ 상환기간의 변경에 따라 조정금리가 달라지는 경우에는 이미 납부한 분할상환금에 대한 발생이자와 바뀐 조정금리로 계산된 발생이자의 차액은 상환기간 변경 후 처음으로 도래하는 상환기일에 반영한다.</t>
+  </si>
+  <si>
+    <t>제25조</t>
+  </si>
+  <si>
+    <t>상환기일의 변경</t>
+  </si>
+  <si>
+    <t>분할상환금의 상환기일의 변경은 채무관계자로부터 별지 제12호서식의 분할상환기일 변경 신청서를 받아 1회에 한하여 변경을 허용할 수 있다. 다만, 채무관계자가 분할상환금의 연체가 있거나 상환기일 변경으로 해당 월 분할상환금의 연체가 발생할 경우에는 연체를 해소한 이후 또는 연체를 해소할 수 있는 금액을 상환받은 후에 분할상환기일을 변경하여야 한다.</t>
+  </si>
+  <si>
+    <t>제26조</t>
+  </si>
+  <si>
+    <t>채무부담액의 상환유예</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무부담액을 연체 없이 상환하고 있는 채무관계자(동산담보부채권 및 무담보채권의 경우에 한한다)가 다음 각 호의 어느 하나에 해당하는 경우에는 별지 제13호서식의 채무상환 유예(연장) 신청서를 받아 채무부담액의 상환을 유예할 수 있다. 다만, 대리인이 신청할 경우에는 별지 제14호서식의 채무상환 유예(연장) 신청 위임장을 추가로 제출하여야 한다.
+1. 질병 또는 교통사고 등으로 2개월 이상 입원하는 경우
+2. 일시적으로 직장을 잃은 경우 또는 휴업·폐업 등으로 사업을 계속 영위할 수 없는 경우
+3. 4대 중증질환자(암, 심장질환, 뇌혈관질환, 희귀난치성질환), 특별재난지역채무자(특별재난지역 선포일로부터 1년 이내 신청), 「국민기초생활 보장법」 제2조제10호의 차상위계층
+4. 「국민기초생활 보장법」 제2조제2호의 수급자, 미성년자, 현역입영자(직업군인은 제외한다) 및 구속수감자
+5. 장애정도가 심한 중증장애인(종전 1급~3급)이나 4대 중증질환자(암, 심장질환, 뇌혈관질환, 희귀난치성질환)를 부양(동거가족 중 본인 및 배우자와 그 직계 존·비속에 한함)하는 경우(2026.3.25. 본호신설)
+6. 채무관계자 또는 그 배우자가 출산·육아휴직하는 경우(2026.3.25. 본호신설)
+7. 1년(12회차) 이상 상환한 채무관계자가 제1호에서 제6호까지 외의 기타 사정으로 채무변제가 어려울 경우(2026.3.25. 본호신설)
+8. 그 밖에 주무부점의 장이 긴급하게 상환유예가 필요하다고 인정하는 경우
+② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대해서는 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
+③ 제1항제4호에 해당하는 채무관계자에 대하여 채무부담액의 상환유예 사유가 해소될 때까지 상환을 유예할 수 있다.
+④ 제1항 제6호 중 출산의 경우에는 출생일로부터 1년, 육아휴직의 경우에는 휴직기간 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
+⑤ 제1항 제7호에 해당하는 경우에는 상환유예 신청일로부터 2개월 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
+⑥ 채무부담액의 상환유예를 신청하려는 채무관계자는 신청일까지의 거치기간이자, 연체된 분할상환금을 모두 상환하여야 한다.
+⑦ 동산담보부채권의 채무관계자는 상환유예 기간동안 잔여 분할상환금에 대하여 연 2%의 금리를 적용한 이자를 매월 상환기일에 납부하여야 한다.
+⑧ 채무관계자는 상환유예 기간 만료 후에 최초로 도래하는 상환기일부터 잔여 분할상환금을 순차적으로 상환하여야 한다.
+⑨ 제1항 각 호에 해당하는 채무관계자는 동일한 사유 또는 서로 다른 각 호의 사유로 연속하여 채무부담액의 상환을 유예할 수 있으며, 총 상환유예기간은 최장 3년으로 한다.(2026.3.25. 본항신설)</t>
+  </si>
+  <si>
+    <t>제27조</t>
+  </si>
+  <si>
+    <t>채무부담액의 조기상환</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 분할상환 중인 채무관계자가 개별 약정의 잔여 채무부담액 일시 상환을 신청하는 경우에는 별지 제15호서식 조기상환신청서를 받고 이를 승인할 수 있다.(2026.3.25. 본항개정)
+② 조기상환을 신청한 채무관계자는 조기상환 승인일 다음날부터 5영업일 이내에 잔여 채무부담액 전부를 상환하여야 한다.
+③ 부실우려차주 및 그 채무관계자 또는 부동산 담보부채무를 부담하는 부실차주 및 그 채무관계자는 제22조 제2항 및 제3항에 따라 잔여 채무부담액 및 조기상환일 전일까지의 발생이자를 포함하여 상환하여야 한다.(2025.5.29. 본항신설)</t>
+  </si>
+  <si>
+    <t>제27조의2</t>
+  </si>
+  <si>
+    <t>조기상환자 추가감면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 무담보 채무조정 약정 체결 후 1년 이상 경과하고 분할상환금을 12회차 이상 납부한 부실차주가 일시 상환을 신청한 경우 변제계획 이행기간에 따라 잔여 채무부담액에 대하여 최대 10%~최소 5% 추가 감면 인센티브를 부여할 수 있다. 다만, 채무관계자가 분할상환금을 연체하고 있는 경우에는 연체된 분할상환금 및 연체이자를 전액 상환하는 경우에 한하여 조기상환을 신청할 수 있다.
+1. 변제계획을 1년(12회) 이상 2년(24회) 미만 이행한 경우 : 10%
+2. 변제계획을 2년(24회) 이상 3년(36회) 미만 이행한 경우 : 8%
+3. 변제계획을 3년(36회) 이상 4년(48회) 미만 이행한 경우 : 6%
+4. 변제계획을 4년(48회) 이상 이행한 경우 : 5%
+② 제1항의 변제계획 이행기간 산정에 있어 제21조에 따른 거치기간 및 제26조에 따른 상환유예기간 등은 제외한다.
+③ 제1항 각 호의 변제계획 이행기간 및 그에 따른 추가감면율은  채무관계자가 체결한 개별 약정별로 산정하고, 추가감면율을 개별 약정별로 각각 적용하여 잔여 채무부담액을 산정한다.
+[2026.3.25. 본조신설]</t>
+  </si>
+  <si>
+    <t>제28조</t>
+  </si>
+  <si>
+    <t>채무부담액의 완납</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채무관계자가 채무부담액을 완납한 경우에는 제23조제6항에 따라 상환을 유예하여 채무부담액에 포함되지 않은 원금 및 모든 이자와 약정 전 발생한 제비용은 다음 각 호에 따라 처리한다.(2024.12.30. 본조개정)
+1. 주채무자가 채무부담액을 완납한 경우 : 채무관계자 전원에 대하여 잔여 채권을 감면
+2. 채무관계자 전원이 재산이 없고 주채무자 이외의 채무관계자가 주채무자의 채무부담액 이상을 상환한 경우 : 채무관계자 전원에 대하여 잔여 채권을 감면
+3. 보증인이 자신의 채무부담액만을 완납한 경우 : 다른 채무관계자의 대상채권에 포함</t>
+  </si>
+  <si>
+    <t>제29조</t>
+  </si>
+  <si>
+    <t>대상채권의 추가 매입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 새출발기금이 채무관계자와 채무조정의 약정을 체결한 이후 그 채무관계자의 대상채권을 추가로 매입하는 경우에는 채무관계자로부터 별지 제16호서식의 채무조정 대상채무 추가 신청서를 제출받아 추가로 매입하는 대상채권의 채무조정 약정을 할 수 있다. 이 경우 채무부담액 산정의 기초자료는 최초의 채무조정 약정과 동일하게 적용한다.
+② 추가로 매입한 대상채권의 채무조정을 약정할 경우 최초의 채무조정 약정에 따라 이미 상환이 진행된 기간(회차)은 추가로 매입한 대상채권의 거치기간 및 상환기간 산정의 범위에서 제외한다.
+③ 주무부점의 장은 채무관계자에게 추가된 대상채권의 분할상환계획을 안내하여야 한다.</t>
+  </si>
+  <si>
+    <t>제30조</t>
+  </si>
+  <si>
+    <t>채무부담액 등 회수</t>
+  </si>
+  <si>
+    <t>제6장 채무조정의 사후관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무부담액 및 제비용 등 상환금은 지정된 납부(가상)계좌로 상환받는다.(2025.9.19. 본항개정)
+② 분할상환금은 CMS이체방식으로 상환받거나 지정된 가상계좌로 상환받을 수 있다.(2025.9.19. 본항신설)
+③ CMS이체방식 이용에 따른 수수료(금융회사 수수료ㆍ금융결제원 중계수수료)는 새출발기금이 부담하며 가상계좌 이용에 따른 송금수수료는 채무관계자가 부담하는 것을 원칙으로 한다.(2025.9.19. 본항신설)</t>
+  </si>
+  <si>
+    <t>제31조</t>
+  </si>
+  <si>
+    <t>변제충당순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 납부한 분할상환금은 대상채권의 계좌별로 회차별 상환예정금액 비율을 기준으로 안분하여 충당한다. 이 경우 상환기일이 도래하지 않은 채무는 충당대상에서 제외한다.
+② 채무관계자가 채무조정의 효력을 상실하지 아니한 때의 채권별 변제충당은 원금, 가지급금, 이자 순으로 하여 상환하는 회차별로 순차적으로 충당한다.(2024.12.30. 본항개정)
+③ 법원의 강제집행을 통한 배당금 등 그 밖의 방법을 통하여 수령한 금액은 해당 채무관계자와 관련된 가지급금, 원금, 이자 순으로 충당한다.</t>
+  </si>
+  <si>
+    <t>제32조</t>
+  </si>
+  <si>
+    <t>채무조정의 효력 상실</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채무관계자에게 다음 각 호의 어느 하나에 해당하는 사유가 발생한 경우에는 채무조정 약정의 효력이 상실된다. 이 경우 주무부점의 장은 즉시 채권의 회수 절차를 진행하여야 한다.(2024.12.30. 본조개정)
+1. 분할상환금(거치기간동안의 이자를 포함한다)의 상환을 3개월(3회차) 이상 연체한 경우. 다만, 채무관계자가 다음 각 목의 사항과 같은 특별한 사정이 있는 경우에는 채무조정 신청 후 6개월 이상 채무조정에 의한 변제계획을 이행하지 아니하면 채무조정의 효력 상실을 할 수 있다. 단, 그 사정은 채무조정 약정이 체결된 이후에 발생한 사정으로 한정한다.(2024.12.30. 본호개정)
+가. 채무관계자가 「재난 및 안전관리 기본법」 제61조에 따른 특별 지원 대상에 포함되는 경우
+나. 본인 또는 그 직계 존ㆍ비속의 혼인
+다. 본인 또는 그 직계 존ㆍ비속, 배우자 또는 그 직계 존ㆍ비속이 사망한 경우
+라. 본인 또는 그 직계 존·비속, 배우자 또는 그 직계 존·비속이 사고·질병 등으로 수술을 받거나 입원한 경우
+마. 실업(채무자의 사정으로 전직 또는 자영업을 하기 위하여 이직한 경우는 제외), 무급휴직, 폐업(전업하기 위한 경우는 제외)한 경우
+바. 3개월 이상 입원치료가 필요한 질병을 진단받은 경우
+2. 채무조정 신청 당시에 제출한 자료나 진술이 허위인 경우
+3. 허위사실 신고, 재산의 도피 및 은닉, 기타 책임재산 감소행위 등을 한 사실이 발견되는 경우
+4. 「채무자 회생 및 파산에 관한 법률」에 따른 파산신청 또는 (개인)회생절차개시의 신청이 있는 경우
+5. 「서민의 금융생활 지원에 관한 법률」에 따른 신용회복위원회 채무조정 신청이 있는 경우(2024.12.30. 본호신설)
+6. 채무관계자의 채무조정과 관련한 담보물 또는 발견재산에 대하여 제3자로부터 강제집행의 신청이 있는 경우(2024.12.30. 본호개정)
+7. 채무조정 신청 당시에 회수가능성이 있는 재산을 소유하고 있었음에도 불구하고 이를 신고하지 않고 채무조정에 관한 약정이 체결된 경우(2024.12.30. 본호개정)
+8. 채무관계자가 사망하거나 실종선고를 받은 경우(2024.12.30. 본호신설)
+9. 채무조정 합의의 해제를 요청한 경우(2024.12.30. 본호신설)</t>
+  </si>
+  <si>
+    <t>제33조</t>
+  </si>
+  <si>
+    <t>연체 및 채무조정의 효력 상실 등 통지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 분할상환금을 1회 이상 연체한 경우에는 월 1회 전자우편(E-mail) 또는 문자메세지(SMS 등)로 연체사실을 통지하거나 분할상환금 납입안내장을 채무관계자의 주소에 등기우편으로 통지하여야 한다.
+② 채무관계자에게 제32조 각 호에 따른 채무조정의 효력 상실사유가 발생한 때에는 채무조정의 효력이 상실된다는 사실과 신용정보집중기관에 신용도판단정보가 등록되어 금융거래 시 불이익을 받을 수 있음을 별지 제27의2호서식의 채무조정의 효력 상실 예정통지 및 채무금 변제 최고서로 채무조정의 효력 상실일 10영업일 전까지 통지하여야 한다.(2024.12.30. 본항개정)
+③ 채무관계자가 채무조정의 효력을 상실한 때에는 채무조정의 효력이 상실된 사실과 잔여 채무액을 상환하여야 함을 별지 제27호서식에 따른 채무조정의 효력 상실통지 및 채무금 변제 최고서로 통지하여야 한다.(2024.12.30. 본항개정)
+④ 채무관계자에게 신용회복위원회를 통한 신용회복지원이 실효, 「채무자 회생 및 파산에 관한 법률」에 따른 파산신청 및 (개인)회생절차개시의 신청이 취소 또는 기각 등의 사유가 발생할 때에는 별지 제27호의3서식에 따른 안내서로 통지하여야 한다.(2024.12.30. 본항개정)
+[2024.12.30. 본조개정]</t>
+  </si>
+  <si>
+    <t>제34조</t>
+  </si>
+  <si>
+    <t>채무조정의 효력 부활</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 제32조제1호의 사유로 채무조정의 효력이 상실된 채무관계자가 연체된 분할상환금(거치기간동안의 이자를 포함한다) 전액과 제비용을 납부하는 때에는 채무조정 약정의 효력은 그 때부터 부활된다. 다만, 채무관계자가 신청하는 경우 1회분 분할상환금과 제비용을 납부하여 채무조정의 효력을 부활할 수 있으며, 미납한 분할상환금은 잔여기간에 균등하게 안분하여 상환하여야 한다.(2024.9.11., 2024.12.30. 본항개정)
+② 제1항에 따른 채무조정의 효력 부활은 채무조정의 효력 상실일로부터 6개월이 지나기 전까지 할 수 있다.(2024.12.30. 본항개정)
+③ 제1항 및 제2항에도 불구하고, 채무조정 약정일 이후에 새로이 재산을 취득하여 소유하고 있는 부실차주 및 그 채무관계자의 경우에는 채무조정의 효력을 부활할 수 없다.(2024.12.30. 본항개정)</t>
+  </si>
+  <si>
+    <t>제35조</t>
+  </si>
+  <si>
+    <t>채무조정의 재약정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 협약 및 이 요강에 따라 채무조정의 효력이 상실된 채무관계자가 채무조정의 재약정을 하고자 하는 경우에는 채무관계자로부터 별지 제20호서식의 재약정 신청서를 받아 채무조정의 약정을 새로이 체결할 수 있다. 다만, 제32조제2호부터 제4호까지의 사유로 채무조정의 효력이 상실된 경우에는 해당사유가 해소된 이후에 재약정을 신청할 수 있다.
+② 채무조정의 재약정을 할 경우 채무부담액 산정의 기초자료는 재약정 신청 시를 기준으로 하되, 상환기간은 재약정 신청 시에 속한 채무자 유형에 따라 다음 각 호의 기준을 적용한다.
+1. 부실차주 : 제22조에 따른 상환기간
+2. 부실우려차주 : 기존 채무조정의 잔여 상환기간 범위 이내
+③ (2024.9.11. 본항삭제)
+④ 채무조정의 재약정을 할 경우 제21조에 따른 거치기간은 부여하지 않는다. 다만, 제34조에 따른 채무조정의 효력 부활은 할 수 있다.(2024.12.30. 본항개정)</t>
+  </si>
+  <si>
+    <t>제36조</t>
+  </si>
+  <si>
+    <t>담보권 실행</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 담보부채권의 담보권 실행에 곤란한 사유가 있다고 판단하는 경우를 제외하고는 신속ㆍ정확하게 「민사집행법」에 따라 담보권을 실행하여야 한다. 다만, 재산가액, 물건 소재지 낙찰률, 선순위채권 등을 고려하였을 때 예상배당액이 매입대금보다 적은 경우에는 그러하지 아니한다.(2024.9.11. 단서신설, 2024.12.30., 2025.9.19. 본항개정)
+② 제1항에 따른 담보권 실행을 위한 경매신청 시에는 경매신청 전에 별지 제28호서식 ‘경매예정 통지서’를 채무자 및 담보물 소유자에게 부동산의 등기사항증명서에 기재되어 있는 주소(주민등록등본에 기재된 주소와 다른 경우에는 주민등록등본에 기재된 주소를 포함한다)로 통지하여야 한다.(2024.12.30. 본항개정)
+③ 담보권 실행을 위한 경매신청서에는 제2항의 통지서 사본과 채무자 또는 담보물 소유자의 주민등록초본을 첨부하여야 한다.
+④ 제1항 단서의 담보권 실행 분석을 위하여 별지 제25호 서식을 작성할 수 있으며 필요한 재산가액 산정은 별표2를 따르되, 기타 낙찰률 등은 「인수채권담보물건유입요강」의 산정방식을 준용한다.(2024.9.11. 본항신설)</t>
+  </si>
+  <si>
+    <t>제36조의2</t>
+  </si>
+  <si>
+    <t>주택경매예정사실의 통지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 전입 신고하고 실제 거주하고 있는 「주택법」에 따른 주택으로서 금융위원회가 정하여 고시하는 기준 따른 가격이 6억원 이하인 주택을 법원에 경매 신청하려는 경우에는 별지 제29호서식 ‘주택경매 예정사실 통지서’에 다음 각 호의 사항을 포함하여 경매신청 예정일의 10영업일 전까지 채무관계자에게 등기우편이나 교부의 방법으로 통지하여야 한다, 다만, 채무관계자가 동의하는 경우에는 정보통신망 이용 등 「전자문서 및 전자거래기본법」 제2조제10호의 공인전자문서중계자를 통한 전자문서로 할 수 있다.
+1. 경매신청 대상 주택
+2. 경매신청 예정일
+3. 채무조정의 요건과 요청 절차ㆍ방법
+4. 그 밖에 주택의 경매에 필요한 사항으로서 개인채무자보호법 시행령 제7조제3항으로 정하는 사항
+② 제1항제2호의 경매신청 예정일은 연체가 발생한 날로부터 6개월이 경과한 날을 말한다.
+③ 제1항에 따른 통지가 같은 항 제2호의 경매신청 예정일의 10영업일 전까지 채무관계자에게 도달하지 아니한 경우에는 그 통지가 도달한 날부터 10영업일 지난 날 이후에 주택의 경매를 신청할 수 있다.
+④ 제1항에 따른 주택경매예정사실의 통지를 받은 채무관계자가 제1항제2호의 경매신청 예정일 전에 경매절차의 시작을 희망하는 의사표시를 한 경우에는 경매신청 예정일 전이라도 경매를 신청할 수 있다.
+⑤ 제1항에 따른 통지가 2회 이상 반송되거나 채무관계자의 주소 등 연락처를 통상적인 방법으로 확인할 수 없는 경우에는 새출발기금 인터넷 홈페이지에 경매예정사실을 게재하는 방법으로 그 통지를 갈음할 수 있다.
+⑥ 제5항에 따라 인터넷 홈페이지에 게재한 경우 게재일로부터 10영업일이 지난 날 이후에 주택의 경매를 신청할 수 있다.
+⑦ 제1항부터 제6항까지에도 불구하고 채무관계자가 다음 각 호의 구분에 따른 날까지 채무조정을 요청하는 경우에는 그 채무조정의 절차가 끝나기 전까지 경매를 신청해서는 아니 된다. 다만, 다른 채권자가 해당 주택에 대하여 강제집행을 법원에 신청하는 경우 또는 별표7 새출발기금 채무조정 내부기준에 따른 채무조정 거절 사유가 발생한 경우에는 경매를 신청할 수 있다.
+1. 제1항에 해당하는 경우: 같은 항 제2호의 경매신청 예정일 전일
+2. 제3항에 해당하는 경우: 제1항에 따른 통지가 도달한 날부터 10영업일이 되는 날
+3. 제5항에 해당하는 경우: 새출발기금 인터넷 홈페이지에 게재 등을 한 날부터 10영업일이 되는 날
+[2024.12.30. 본조신설]</t>
+  </si>
+  <si>
+    <t>제37조</t>
+  </si>
+  <si>
+    <t>담보부채권에 대한 지원 특례</t>
+  </si>
+  <si>
+    <t>담보부채권의 채무조정 약정이 최초로 실효되는 경우에는 제36조에도 불구하고 6개월 간 추심 및 담보권의 실행을 유예한다. 이 경우 추심 유예의 기준일은 최초의 채무조정 약정이 실효되는 날을 기준으로 기산한다.</t>
+  </si>
+  <si>
+    <t>제38조</t>
+  </si>
+  <si>
+    <t>매각기일의 연기 신청</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 새출발기금이 직접 신청한 경매 사건의 채무관계자가 별지 제36호서식 매각기일 연기 동의 신청서를 제출하는 경우에는 별표 4 채무유형별 분할상환기간에 따른 조정금리 기준 채무에 따른 담보부채무의 조정금리를 적용한 60일분의 이자와 제비용(경매비용은 제외한다)을 상환받고 매각기일의 연기에 동의할 수 있다. 다만, 채권금융회사의 약정금리가 담보부채무의 조정금리보다 낮은 경우에는 채권금융회사의 약정금리를 적용한다.(2025.5.29. 본항개정)
+② 경매의 연기가 시급하거나 채무조정 신청인이 신청하는 경우에는 경매연기에 필요한 서류를 채무조정 신청인에게 교부하고 수령증을 제출받아야 한다.
+③ 제1항에 따른 매각기일의 연기 동의는 2회에 한한다.</t>
+  </si>
+  <si>
+    <t>제39조</t>
+  </si>
+  <si>
+    <t>경매개시결정 후의 조치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 경매개시결정이 된 때에는 다음 각 호의 사항을 확인하여야 한다.
+1. 신청내용과 경매개시결정 내용의 일치 여부
+2. 등기사항증명서상 경매개시결정 기입등기 여부
+3. 채무자에 대한 경매개시결정문 송달 여부. 다만, 주민등록상의 주소와 등기사항증명서상의 주소가 다른 경우에는 양쪽 주소에 모두 송달하였는지 여부를 확인하여야 한다.
+② 경매개시결정 내용이 신청내용과 다른 경우 및 경매개시결정문의 송달상 하자를 발견한 경우에는 즉시 경정신청이나 추가 송달의 요청 등 적절한 조치를 하여야 한다.</t>
+  </si>
+  <si>
+    <t>제40조</t>
+  </si>
+  <si>
+    <t>수계신고 및 채권계산서의 제출</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 대상채권과 관련하여 경매가 진행되는 경우 채권 및 근저당권 양도·양수 절차를 종료한 즉시 수계신고를 하여 채권자로서의 지위를 승계하여야 한다.
+② 주무부점의 장은 새출발기금에서 신청 또는 수계한 경매사건의 배당요구종기일까지 배당요구 또는 채권계산서를 관할법원에 제출하여야 한다.</t>
+  </si>
+  <si>
+    <t>제41조</t>
+  </si>
+  <si>
+    <t>경매사건 대책 수립</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 매각기일통지서를 접수하였을 때에는 제39조제1항제3호 단서에 준하여 경매절차상 이해관계인에 대한 기일통지서의 송달여부를 확인하고, 담보물별 최저매각가격, 부동산의 현상(現狀), 점유관계, 임차금 또는 보증금의 수액(數額), 선순위채권, 조세공과금 등을 조사하여 별지 제26호 서식에 따라 경매사건 대책을 수립한다.(2024.9.11. 본항개정)
+② 주무부점의 장은 임차인 및 유치권자 등의 권리신고로 저가 낙찰 등 배당금의 감소가 예상되는 경우에는 소송을 제기할 수 있다.
+③ 경매 진행과 관련한 법원의 보정명령, 상대방의 이의신청 및 즉시항고 등에 대하여는 신속히 대처하여야 한다.
+④ (2024.9.11. 본항삭제)
+[2024.9.11. 본조개정]</t>
+  </si>
+  <si>
+    <t>제42조</t>
+  </si>
+  <si>
+    <t>경매신청의 취하</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 채무부담액을 전액 납부하거나 채무조정약정을 체결한 경우에는 담보물에 대한 경매신청을 취하할 수 있다. 다만, 채무조정의 재약정으로 경매신청을 취하하는 경우에는 제59조의2를 준용한다. (2024.9.11. 본항개정)
+② 주무부점의 장은 다음 각 호의 어느 하나에 해당하는 경우에는 경매신청의 실익여부를 판단하여 경매신청을 취하할 수 있다.
+1. 경매개시결정 후에 경매신청 물건이 법원의 감정평가 등에 따라 멸실이 확인되었을 경우(해당 물건에 한한다)
+2. 경매신청 물건의 가격하락, 선순위채권의 과다 등으로 경매속행의 실익이 없는 경우(2025.9.19. 본호개정)
+③ 경매신청의 취하가 시급하거나 채무조정 신청인이 요청하는 경우에는 경매취하에 필요한 서류를 채무조정 신청인에게 교부하고 영수증을 제출받아야 한다.</t>
+  </si>
+  <si>
+    <t>제43조</t>
+  </si>
+  <si>
+    <t>채무조정심의위원회 심의</t>
+  </si>
+  <si>
+    <t>채무조정 신청인의 특수한 상황 등을 고려하여  「채무조정심의위원회 운영요강」에 따른 채무조정심의위원회의 심의·의결을 거쳐 채무감면율 조정, 발견재산 회수대상 제외, 성실상환 채무관계자 채무부담액 잔액 감면, 채무상환 유예 승인 등을 결정할 수 있다.</t>
+  </si>
+  <si>
+    <t>제44조</t>
+  </si>
+  <si>
+    <t>채무조정 약정서류 등의 관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무조정 약정서류 등은 전자문서화(DIPS)한 뒤 「기록물관리세칙」에 따른 기록관(이하 “기록관”이라 한다)으로 이관하여 관리하도록 한다.(2024.12.30. 본항개정)
+② 추심이 위임된 채권의 약정서류는 채무조정 약정일 이후에 보조자산관리자가 전산에 등록을 하여 주무부점의 장에게 이관하고, 주무부점의 장은 전산등록 여부 및 약정서류의 이상 유무를 확인 후에 기록관으로 이관한다.</t>
+  </si>
+  <si>
+    <t>제45조</t>
+  </si>
+  <si>
+    <t>채무관련 약정서류 등의 교부</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 대상채권이 전부 회수된 경우 채무관계자 또는 대위변제자가 채무조정 약정서류 등에 대하여 반환을 요구할 때에는 주무부점의 장은 수령증을 받은 후에 채무관계자 또는 대위변제자에게 교부할 수 있다.
+② 대상채권이 전부 또는 일부가 회수되고 채무관계자 또는 대위변제자의 요청이 있는 경우에는 별지 제21호서식의 채무완제증서 또는 별지 제22호서식의 상환내역확인서를 교부할 수 있다.</t>
+  </si>
+  <si>
+    <t>제46조</t>
+  </si>
+  <si>
+    <t>부실차주 신용정보의 기록 및 활용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 부실차주가 채무조정의 약정을 체결하는 경우 주무부점의 장은 이미 등록되어 있는 부실차주의 신용도판단정보를 해제하고, 공공정보를 등록한다.
+② 채무조정 약정 후 제32조제1호 및 제5호에 따라 채무조정의 효력 상실사유가 발생한 때에는 채무조정의 효력 상실일 다음날부터 5영업일 이내에 제1항에 따라 채무조정의 약정 체결 시에 해제한 채무에 대한 신용도판단정보를 재등록하고, 채무조정 약정 체결 시 등록된 신용도판단정보가 없었던 채무에 대해서는 등록사유 발생일을 소급하여 재등록한다. 이 경우 등록한 공공정보는 해제한다.(2024.12.30. 본항개정)
+③ 채무조정 승인내용을 불이행하거나 채무조정의 효력 상실로 제2항에 따라 신용도판단정보를 등록할 경우 7영업일 전까지 다음 각 호의 사항을 채무관계자에게 통지하여야 한다.(2024.12.30. 본항개정)
+1. 신용정보집중기관에 신용도판단정보가 등록되어 금융거래상 불이익을 받을 수 있다는 사실
+2. 신규 채무조정 또는 기존 채무조정의 부활을 요청할 수 있다는 사실
+④ 제1항에 따라 등록된 공공정보는 1년(12회차) 간 성실상환 시에는 해제한다. 이 경우 성실상환의 기산점은 분할상환기간에 따른 거치기간 이자 또는 원리금을 처음으로 상환하는 시점을 말한다.(2024.9.11., 2024.12.30. 본항개정)
+⑤ 폐업한 부실차주가 채무조정 약정을 체결하고 다음 각 호의 어느 하나에 해당하는 경우에는 별지 제35호서식 공공정보 해제 신청서를 받아 1회에 한하여 등록된 공공정보를 해제할 수 있다.(2025.5.29. 본항신설)
+1. 국민취업지원제도와 희망리턴패키지 특화취업(심화)을 모두 이수하고 취업을 한 경우
+2. 희망리턴패키지 재기사업화(재창업)를 이수하고 재창업 한 경우</t>
+  </si>
+  <si>
+    <t>제47조</t>
+  </si>
+  <si>
+    <t>불법 채권추심 행위의 금지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채권을 추심하는 경우 다음 각 호의 방법을 사용하여서는 아니 된다.
+1. 폭행 또는 협박을 가하거나 위계 또는 위력을 사용하는 방법
+2. 채무관계자 또는 그의 관계인(채무관계자와 동거하거나 생계를 같이하는 사람, 채무관계자의 친족, 채무자가 근무하는 장소에 함께 근무를 하는 사람을 말한다. 이하 이 조에서 같다)에게 채무에 관한 사실 또는 허위사실을 알리는 방법
+3. 엽서에 의한 채무변제 요구 등 채무관계자 외의 사람이 채무사실을 알 수 있게 하는 방법
+4. 다음과 같은 행위로 채무관계자 또는 그의 관계인에게 공포심과 불안감을 유발하여 사생활 또는 업무의 평온을 심히 해치는 방법
+가. 정당한 사유 없이 반복적으로 또는 야간에 전화하는 등 말이나 글, 음향 또는 영상, 물건을 채무관계자 또는 그의 관계인에게 도달하게 하는 행위
+나. 정당한 사유 없이 반복적으로 또는 야간에 채무관계자 또는 그의 관계인을 방문하는 행위
+다. 채무관계자에게 금전의 차입이나 그 밖에 이와 유사한 방법으로 채무의 변제자금을 조달할 것을 강요하는 행위
+라. 채무관계자의 관계인에게 채무관계자를 대신하여 채무를 변제할 것을 강요하는 행위</t>
+  </si>
+  <si>
+    <t>제48조</t>
+  </si>
+  <si>
+    <t>준용</t>
+  </si>
+  <si>
+    <t>이 장에서 정하지 않은 채무조정의 사후관리에 필요한 세부사항은 「인수채권정리업무규정」을 준용한다.</t>
+  </si>
+  <si>
+    <t>제49조</t>
+  </si>
+  <si>
+    <t>소송업무 등 수행</t>
+  </si>
+  <si>
+    <t>제7장 소송업무 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자에 대한 소송업무 등 법적조치의 수행 및 관리는 주무부점의 장이 수행한다. (2024.12.30. 본항개정, 2025.9.19. 단서삭제)
+② 소송업무는 「고문변호사 운용요강」에 따른 고문변호사(이하 “고문변호사”라 한다)에게 위임하여 수행하거나 직원이 직접 수행하는 것을 원칙으로 한다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 담당 상임이사·본부장의 승인을 얻어 고문변호사 외의 변호사(법무법인, 법무조합을 포함한다)에게 의뢰할 수 있다.
+1. 새출발기금 또는 자산관리자에 중대한 영향을 미칠 수 있는 경우
+2. 확립된 판례가 없거나 향후 분쟁이 예상되는 경우
+3. 그 밖에 담당 상임이사·본부장이 승인하는 경우
+③ 고문변호사에게 위임하여 소송을 수행하는 경우 변호사의 보수는 「고문변호사 운용요강」 별표 3의 변호사 보수지급 기준에 따라 지급한다.</t>
+  </si>
+  <si>
+    <t>제50조</t>
+  </si>
+  <si>
+    <t>시효소송수행 기준</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 대상채권의 시효중단을 위하여 시효완성 예정일 3개월 전에 시효관리대상채권의 선정 및 시효중단조치의 착수여부를 결정하여야 하며, 시효완성 예정일 1개월 전까지는 시효중단 조치를 하여야 한다.
+② 제1항에도 불구하고 시효관리대상채권 중 채권액에 비해 시효소송의 비용이 과다하거나 회수가능성이 적은 채권은 시효중단조치를 유보할 수 있다.</t>
+  </si>
+  <si>
+    <t>제51조</t>
+  </si>
+  <si>
+    <t>시효관리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 「소멸시효 관리규정」을 준용하여 시효를 관리하되, 비용이 최소화되는 방향으로 관리하여야 한다.(2026.3.25. 본항개정)
+② 제1항에도 불구하고 채권회수에 효율적이라고 판단되는 경우에는 다르게 적용할 수 있다.</t>
+  </si>
+  <si>
+    <t>제52조</t>
+  </si>
+  <si>
+    <t>시효점검</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 효율적인 시효관리를 위하여 수시로 채권의 시효기간 만료일을 점검하여야 한다.
+② 시효는 채권별·채무관계자별로 전산자료와 채권원인서류(문서 및 전자문서화(DIPS)된 서류를 포함한다)를 대조하여 점검한다.</t>
+  </si>
+  <si>
+    <t>제53조</t>
+  </si>
+  <si>
+    <t>시효중단조치 제외대상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 시효가 도래한 대상채권의 채무관계자가 다음 각 호의 어느 하나에 해당되어 채권회수의 실익이 없는 것으로 인정되는 경우에는 시효중단조치를 하지 아니할 수 있다.
+1. 주채무자가 60세 이상으로 원금잔액이 5백만원 이하이고, 보증인이 없는 경우
+2. 주채무자가 60세 이상으로 원금잔액이 5백만원 이하이고, 보증인이 있는 경우로써 보증인이 사망한 후 피상속인 소유의 회수실익이 있는 발견재산이 없는 경우
+3. 보증인이 없는 주채무자가 사망한 경우로써 피상속인 소유의 회수실익이 있는 발견재산이 없는 경우
+4. 보증인이 있는 주채무자가 사망한 경우로써 피상속인 및 보증인 소유의 회수실익이 있는 발견재산이 없는 경우
+5. 보증인이 사망한 경우로써 피상속인 소유의 회수실익 있는 발견재산이 없는 경우
+6. 채무관계자의 총 채무원금 잔액이 2백만원 이하인 경우(2024.12.30. 본호개정)
+6의2. 무담보채무 중 시효가 1년 내 도래하는 모든 개별 채무의 원금 및 가지급금 잔액의 합계가 1백만원 미만인 경우 해당 채무(2025.5.29. 본호신설, 2025.9.19. 본호개정)
+6의3. 무담보채무 중 해당 개별 채무의 원금 및 가지급금 잔액이 0인 경우(2025.5.29. 본호신설, 2025.9.19. 본호개정)
+7. 「국민기초생활 보장법」 제2조제2호에 따른 수급자 중 생계급여, 주거급여, 의료급여, 교육급여 수급자
+8. 「국민기초생활 보장법」제2조제10호에 따른 차상위계층이고, 회수가능재산이 없는 경우
+9. 「장애인연금법」 제2조제3호에 따른 장애인연금의 수급권자
+10. 주채무자가 70세 이상이고, 회수가능재산이 없는 경우
+11. 채권원인서류의 부존재 등 기타 사유로 소송의 진행이 불가능한 경우
+12. 그 밖에 시효연장 실익이 없다고 판단되는 경우
+② 제1항에도 불구하고 제1항제8호의 경우에는 수급자 자격을 상실할 경우에는 시효중단조치를 하여야 한다. 다만, 채권금융회사에서 신청하여 진행 중인 소송은 다음 각 호의 기준에 따른다.
+1. 시효연장을 위한 대여금 청구소송 등은 소송승계 참가를 포기
+2. 배당금(공탁금) 및 추심금 수령을 위한 본안소송 등은 소송승계 참가
+③ 제1항에도 불구하고 채권회수의 실익이 있는 것으로 판단되는 경우에는 시효중단조치를 할 수 있다.</t>
+  </si>
+  <si>
+    <t>제54조</t>
+  </si>
+  <si>
+    <t>지급명령신청</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 시효관리대상채권 중 지급명령을 신청하는 것이 적절하다고 판단되는 경우에는 지급명령을 신청할 수 있다.
+② 지급명령의 신청은 업무량, 비용 등을 고려하여 고문변호사에게 위임할 수 있다.
+③ 지급명령 결정률 제고를 위해 채무관계자의 주소 확인을 보조자산관리자, 고문변호사 및 「지정법무사 운용요강」에 따른 지정법무사(이하 “지정법무사”라 한다)에게 요청할 수 있으며, 이와 관련한 비용은 새출발기금의 부담으로 한다. (2026.3.25. 본항개정)</t>
+  </si>
+  <si>
+    <t>제55조</t>
+  </si>
+  <si>
+    <t>시효소송제기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 시효관리대상채권 중 지급명령의 신청을 하지 않았거나 지급명령을 신청하였으나 송달불능 또는 이의신청이 있는 채권은 시효중단을 위한 소송을 제기하여야 한다.
+② 제1항에도 불구하고 채무관계자에게 회수가능재산이 없고, 월평균소득이 「국민기초생활 보장법」 제2조제11호에 따른 기준 중위소득의 100분의60 이하임이 확인된 경우 시효중단을 위한 소송은 양도자산확정일 이후 1회에 한한다.</t>
+  </si>
+  <si>
+    <t>제56조</t>
+  </si>
+  <si>
+    <t>발견재산에 대한 조치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자 소유의 발견재산에 대하여 집행권원이 있는 경우에는 강제집행의 방법으로 채권을 회수하여야 한다.
+② 강제집행의 청구금액은 발견재산의 시가에서 선순위 채권액을 차감한 금액으로 책정한다. 다만, 제3자와의 권리관계 경합으로 채권액 대비 안분배당 등이 예상되는 경우에는 총 채권액 범위에서 추가로 청구하여 최대한 채권을 회수할 수 있도록 하여야 한다.
+③ 채무관계자 소유의 발견재산에 대하여 집행권원이 없는 경우에는 가압류·가처분 등의 보전조치를 하여야 한다. 다만, 담보권 설정 등 채무관계자의 발견재산에 대해 채무부담액 또는 회수가능액 이상의 실익 있는 대체 담보 제공이 있을 경우 가압류ㆍ가처분 등 보전조치를 생략할 수 있다.(2024.9.11. 단서신설)</t>
+  </si>
+  <si>
+    <t>제57조</t>
+  </si>
+  <si>
+    <t>법무사 위임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 주무부점의 장은 업무량 등을 고려하여 가압류·가처분 등의 신청업무 및 배당·공탁금의 회수업무를 지정법무사에게 위임할 수 있다.(2025.9.19. 본항개정)
+② 제1항에 따라 가압류·가처분 등의 신청업무 및 배당·공탁금의 회수업무를 지정법무사에게 위임하는 경우에는 「지정법무사 운용요강」제17조, 제20조 및 제21조를 준용한다. 다만, 배당·공탁금의 회수업무를 비지정법무사에게 위임하는 경우에는 별지 제23호서식의 확약서를 받아야 한다.(2026.3.25. 본항개정)</t>
+  </si>
+  <si>
+    <t>제58조</t>
+  </si>
+  <si>
+    <t>강제집행의 특례</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자가 채무조정 약정 체결 후에 정상적으로 분할상환금을 납부하는 경우에는 채무관계자에 대한 급여채권의 보전조치는 유예할 수 있다.
+② 채무관계자의 주거용 건물의 전세(임차)보증금이 「주택임대차보호법 시행령」 제10조제1항 각 호의 구분에 따른 금액 이하인 경우에는 전세(임차)보증금 반환채권에 대하여 강제집행을 실시하지 않을 수 있다.
+③ 채무관계자의 상업용 건물의 전세(임차)보증금이 「상가건물임대차보호법 시행령」 제7조제1항 각 호의 구분에 따른 금액 이하인 경우에는 전세(임차)보증금 반환채권에 대하여 강제집행을 실시하지 않을 수 있다.</t>
+  </si>
+  <si>
+    <t>제59조</t>
+  </si>
+  <si>
+    <t>보전조치의 취하</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 보전조치는 채무부담액이 완납될  때까지 취하하지 아니한다.(2025.9.19. 본항개정)
+② 제1항에도 불구하고 채무관계자가 채무조정 중에 보전조치의 해제를 요청하는 경우에는 다음 각 호의 구분에 따라 보전조치를 취하할 수 있다.(2025.9.19. 본항신설)
+1. 보전조치 대상 재산의 회수가능성이 있는 경우(2025.9.19. 본호신설)
+가. 부동산 등 유형재산에 대한 가압류·가처분 : 해당 재산의 회수가능액(제2호가목 단서의 승용자동차를 제외한 차량의 경우 감정평가액 또는 시가를 회수가능액으로 산정한다) 이상을 변제하는 경우
+나. 채권에 대한 (가)압류 : 제3채무자 적립금액과 법원공탁금액의 회수가능액의 합계금액 또는 해당 재산의 회수가능액을 변제하는 경우. 다만, 회수가능액의 합계금액 또는 해당 재산의 회수가능액이 500만원 이하인 경우 변제없이 취하하고, 500만원을 초과하는 경우 회수가능액 합계금액에서 500만원을 차감한 금액을 변제(2026.3.25. 본목개정)
+다. 이미 보전조치된 발견재산이 아닌 새로운 발견재산에 대한 담보권 설정 등 채무부담액 또는 회수가능액 이상의 실익 있는 대체 담보 제공이 있는 경우
+2. 보전조치 대상 재산의 회수가능성이 없는 경우(2025.9.19. 본호신설)
+가. 부동산 등 유형재산에 대한 가압류·가처분 : 채무관계자가 채무부담액의 10% 이상을 변제하는 경우. 다만, 해당 재산이 멸실 등으로 채권보전조치를 할 수 없거나 「재산조사업무요강」 [별표4]에 따라 재산평가액 산정에서 제외되는 자동차의 경우 변제 없이 취하(2026.3.25. 본목개정)
+나. 채권에 대한 (가)압류 : 「민사집행법 시행령」 제7조에 따른 압류금지 예금 등의 금액범위 이하인 경우 변제없이 취하
+③ 제1항에도 불구하고 근저당권 설정등기는 채무부담액과 회수가능액을 비교하여 적은 금액이 변제된 경우에는 말소할 수 있고, 경매가 진행 중인 경우에는 강제집행 비용과 회수가능액의 합계금액이 일시 변제되는 경우에는 경매를 취하할 수 있다.(2025.9.19. 본항개정)
+④ (2024.9.11. 본항삭제)
+[2024.9.11. 본조개정]</t>
+  </si>
+  <si>
+    <t>제59조의2</t>
+  </si>
+  <si>
+    <t>강제집행의 취하</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 강제집행 절차가 진행 중인 채무관계자가 분할상환을 요청하는 경우 다음 각 호의 어느 하나에 해당하는 조치를 하고 강제집행을 취하할 수 있다.
+1. 강제집행비용과 회수가능액의 합계금액을 일시에 변제한 경우
+2. 채권금융회사가 신청한 강제집행의 경우 채무관계자가 제17조에 따라 채무조정 약정을 체결하고, 압류의 순위보전여부 등을 검토하여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 근저당권 설정금액이 5백만원 미만인 경우에는 근저당권 설정을 아니 할 수 있다.(2026.3.25. 본호개정)
+3. 새출발기금이 신청한 강제집행의 경우 압류의 순위보전 여부 등을 검토하여 강제집행비용과 채무부담액의 10% 이상을 상환받은 후 잔여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 근저당권 설정금액이 5백만원 미만인 경우에는 근저당권 설정을 아니할수 있다.(2026.3.25. 본호신설)
+② 제1항에 따라 저당권을 설정 또는 해지하는 경우 그에 필요한 비용은 새출발기금의 부담으로 한다. 다만, 채무관계자가 채무조정약정에 따른 채무조정의 효력을 상실하는 경우에는 채무관계자에게 비용을 청구하여야 한다.(2024.12.30. 본항개정)
+[2024.9.11. 본조신설]</t>
+  </si>
+  <si>
+    <t>제60조</t>
+  </si>
+  <si>
+    <t>추심행위 유보</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 새출발기금 지원 채무자의 원활한 정상경제활동 복귀 지원을 위해 새출발기금이 채권금융회사의 요청에 의해 매입한 대상채권에 대하여는 양도자산확정일로부터 1년 동안 일체의 추심행위(담보권 실행을 포함한다)를 유보할 수 있다. 다만, 추심행위 유보 기간에도 시효관리 등을 위한 소송과 권리 확보가 필요한 경우에는 채권보전조치를 하여야 한다.(2024.9.11. 본항개정)
+② (2025.5.29. 본항삭제)</t>
+  </si>
+  <si>
+    <t>제61조</t>
+  </si>
+  <si>
+    <t>채권추심내부기준</t>
+  </si>
+  <si>
+    <t>제8장 채권의 추심</t>
+  </si>
+  <si>
+    <t>개인채무자보호법 제20조에 따라 새출발기금이 보유하고 있는 채권을 추심하는 경우 별표 8 “새출발기금 채권추심내부기준”에 따라 업무를 처리하여야 한다.</t>
+  </si>
+  <si>
+    <t>제62조</t>
+  </si>
+  <si>
+    <t>채권추심의 착수통지 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채무관계자에 대해 채권추심에 착수하려는 경우에는 다음 각 호의 사항이 포함된 별지 제31호서식의 추심의 착수 통지서를 서면(전자문서를 포함한다)으로 추심 착수 예정일의 3영업일 전까지 채무관계자에게 통지하여야 한다.
+1. 채권자, 채무금액, 연체금액 및 연체기간 등 추심대상 채권에 관한 사항
+2. 추심 착수 예정일
+3. 채권추심자의 성명ㆍ명칭 및 연락처
+4. 연락ㆍ독촉 등 수행하려는 추심업무의 방법
+5. 불법추심이나 소멸시효 완성채권의 추심에 대한 대응요령 등 채무관계자의 방어권 행사 방법
+6. 입금계좌번호, 예금주명 등 입금계좌 관련 사항
+7. 「채권의 공정한 추심에 관한 법률」 제8조의2에 따른 대리인 선임 관련 사항
+8. 불법추심이나 소멸시효 완성채권의 추심에 대한 대응요령에 관한 정보를 확인할 수 있는 방법에 관한 사항
+② 새출발기금이 채무자의 신청에 의해 매입한 대상채권에 대하여는 채무관계자가 6개월 이상 채무조정 약정을 체결하지 않을 경우 제1항에 따른 채권추심의 착수통지 후 채무관계자에 대해 채권추심을 착수할 수 있다.(2025.5.29. 본항신설)
+③ 제2항에 따라 채권추심을 착수한 채무관계자에 대해서는 회수가능액 있는 재산에 대한 조사, 채권보전조치, 경매 신청 등을 할 수 있다.(2025.5.29. 본항신설)
+[2025.5.29. 제목개정]</t>
+  </si>
+  <si>
+    <t>제63조</t>
+  </si>
+  <si>
+    <t>추심업무등의 위탁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 채권추심업무를 위탁하려는 경우의 절차 및 업무처리 기준은 자산관리자의「인수ㆍ위탁채권 사무위탁요강」에 따른다.
+② 제1항에 따라 채권추심 업무 등을 위탁하려는 경우에는 다음 각 호의 사항이 포함된 별지 사무위탁예정 통지서를 위탁 예정일의 5영업일 전까지 채무관계자에게 통지하여야 한다.
+1. 입금계좌번호, 예금주명 등 입금계좌 관련 사항
+2. 「채권의 공정한 추심에 관한 법률」 제8조의2에 따른 대리인 선임 관련 사항
+3. 위탁대상 채권의 소멸시효 완성 여부
+4. 추심연락의 횟수 제한 및 추심연락유형의 제한 등 요청 방법
+③ 제2항에 따른 통지는 서면(「전자문서 및 전자거래 기본법」 제2조제10호의 공인전자문서중계자를 통한 전자문서를 포함한다)의 방법으로 한다.</t>
+  </si>
+  <si>
+    <t>제64조</t>
+  </si>
+  <si>
+    <t>보조자산관리자 위임</t>
+  </si>
+  <si>
+    <t>제9장 보칙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주무부점의 장은 필요한 경우에는 새출발기금 이사회의 승인을 받아 보조자산관리자에게 대상채권의 추심 등에 관한 업무를 위임할 수 있다.
+[2024.12.30. 본조개정]</t>
   </si>
 </sst>
 </file>
@@ -1675,13 +2724,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4885,7 +5938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4964,8 +6017,1738 @@
         <v>482</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>483</v>
+      </c>
+      <c r="B10" t="s">
+        <v>484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="100" style="3" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="E2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="E3" t="s">
+        <v>493</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C4" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="E4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E5" t="s">
+        <v>493</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B6" t="s">
+        <v>504</v>
+      </c>
+      <c r="C6" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>506</v>
+      </c>
+      <c r="B7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>510</v>
+      </c>
+      <c r="B8" t="s">
+        <v>511</v>
+      </c>
+      <c r="C8" t="s">
+        <v>508</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E8" t="s">
+        <v>493</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+      <c r="C9" t="s">
+        <v>515</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E9" t="s">
+        <v>493</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>517</v>
+      </c>
+      <c r="B10" t="s">
+        <v>518</v>
+      </c>
+      <c r="C10" t="s">
+        <v>515</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E10" t="s">
+        <v>493</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>520</v>
+      </c>
+      <c r="B11" t="s">
+        <v>521</v>
+      </c>
+      <c r="C11" t="s">
+        <v>515</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E11" t="s">
+        <v>493</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>523</v>
+      </c>
+      <c r="B12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E12" t="s">
+        <v>493</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>526</v>
+      </c>
+      <c r="B13" t="s">
+        <v>527</v>
+      </c>
+      <c r="C13" t="s">
+        <v>515</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E13" t="s">
+        <v>493</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>529</v>
+      </c>
+      <c r="B14" t="s">
+        <v>530</v>
+      </c>
+      <c r="C14" t="s">
+        <v>515</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E14" t="s">
+        <v>493</v>
+      </c>
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>532</v>
+      </c>
+      <c r="B15" t="s">
+        <v>533</v>
+      </c>
+      <c r="C15" t="s">
+        <v>534</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E15" t="s">
+        <v>493</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>536</v>
+      </c>
+      <c r="B16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C16" t="s">
+        <v>534</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E16" t="s">
+        <v>493</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B17" t="s">
+        <v>540</v>
+      </c>
+      <c r="C17" t="s">
+        <v>534</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E17" t="s">
+        <v>493</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>542</v>
+      </c>
+      <c r="B18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C18" t="s">
+        <v>534</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E18" t="s">
+        <v>493</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>545</v>
+      </c>
+      <c r="B19" t="s">
+        <v>546</v>
+      </c>
+      <c r="C19" t="s">
+        <v>534</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="E19" t="s">
+        <v>493</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>548</v>
+      </c>
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>534</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E20" t="s">
+        <v>493</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>550</v>
+      </c>
+      <c r="B21" t="s">
+        <v>551</v>
+      </c>
+      <c r="C21" t="s">
+        <v>534</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E21" t="s">
+        <v>493</v>
+      </c>
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>553</v>
+      </c>
+      <c r="B22" t="s">
+        <v>554</v>
+      </c>
+      <c r="C22" t="s">
+        <v>534</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>556</v>
+      </c>
+      <c r="B23" t="s">
+        <v>557</v>
+      </c>
+      <c r="C23" t="s">
+        <v>534</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E23" t="s">
+        <v>493</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>559</v>
+      </c>
+      <c r="B24" t="s">
+        <v>560</v>
+      </c>
+      <c r="C24" t="s">
+        <v>561</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="E24" t="s">
+        <v>493</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>563</v>
+      </c>
+      <c r="B25" t="s">
+        <v>564</v>
+      </c>
+      <c r="C25" t="s">
+        <v>561</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="E25" t="s">
+        <v>493</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>566</v>
+      </c>
+      <c r="B26" t="s">
+        <v>567</v>
+      </c>
+      <c r="C26" t="s">
+        <v>561</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E26" t="s">
+        <v>493</v>
+      </c>
+      <c r="F26" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>569</v>
+      </c>
+      <c r="B27" t="s">
+        <v>570</v>
+      </c>
+      <c r="C27" t="s">
+        <v>561</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E27" t="s">
+        <v>493</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>572</v>
+      </c>
+      <c r="B28" t="s">
+        <v>573</v>
+      </c>
+      <c r="C28" t="s">
+        <v>561</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E28" t="s">
+        <v>493</v>
+      </c>
+      <c r="F28" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>575</v>
+      </c>
+      <c r="B29" t="s">
+        <v>576</v>
+      </c>
+      <c r="C29" t="s">
+        <v>561</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E29" t="s">
+        <v>493</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>578</v>
+      </c>
+      <c r="B30" t="s">
+        <v>579</v>
+      </c>
+      <c r="C30" t="s">
+        <v>561</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="E30" t="s">
+        <v>493</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B31" t="s">
+        <v>582</v>
+      </c>
+      <c r="C31" t="s">
+        <v>561</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="E31" t="s">
+        <v>493</v>
+      </c>
+      <c r="F31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>584</v>
+      </c>
+      <c r="B32" t="s">
+        <v>585</v>
+      </c>
+      <c r="C32" t="s">
+        <v>561</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="E32" t="s">
+        <v>493</v>
+      </c>
+      <c r="F32" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>587</v>
+      </c>
+      <c r="B33" t="s">
+        <v>588</v>
+      </c>
+      <c r="C33" t="s">
+        <v>561</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E33" t="s">
+        <v>493</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>590</v>
+      </c>
+      <c r="B34" t="s">
+        <v>591</v>
+      </c>
+      <c r="C34" t="s">
+        <v>561</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E34" t="s">
+        <v>493</v>
+      </c>
+      <c r="F34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>593</v>
+      </c>
+      <c r="B35" t="s">
+        <v>594</v>
+      </c>
+      <c r="C35" t="s">
+        <v>561</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E35" t="s">
+        <v>493</v>
+      </c>
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>596</v>
+      </c>
+      <c r="B36" t="s">
+        <v>597</v>
+      </c>
+      <c r="C36" t="s">
+        <v>561</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E36" t="s">
+        <v>493</v>
+      </c>
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>599</v>
+      </c>
+      <c r="B37" t="s">
+        <v>600</v>
+      </c>
+      <c r="C37" t="s">
+        <v>561</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E37" t="s">
+        <v>493</v>
+      </c>
+      <c r="F37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>602</v>
+      </c>
+      <c r="B38" t="s">
+        <v>603</v>
+      </c>
+      <c r="C38" t="s">
+        <v>604</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E38" t="s">
+        <v>493</v>
+      </c>
+      <c r="F38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>606</v>
+      </c>
+      <c r="B39" t="s">
+        <v>607</v>
+      </c>
+      <c r="C39" t="s">
+        <v>604</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E39" t="s">
+        <v>493</v>
+      </c>
+      <c r="F39" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>609</v>
+      </c>
+      <c r="B40" t="s">
+        <v>610</v>
+      </c>
+      <c r="C40" t="s">
+        <v>604</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E40" t="s">
+        <v>493</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>612</v>
+      </c>
+      <c r="B41" t="s">
+        <v>613</v>
+      </c>
+      <c r="C41" t="s">
+        <v>604</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E41" t="s">
+        <v>493</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>615</v>
+      </c>
+      <c r="B42" t="s">
+        <v>616</v>
+      </c>
+      <c r="C42" t="s">
+        <v>604</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E42" t="s">
+        <v>493</v>
+      </c>
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>618</v>
+      </c>
+      <c r="B43" t="s">
+        <v>619</v>
+      </c>
+      <c r="C43" t="s">
+        <v>604</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E43" t="s">
+        <v>493</v>
+      </c>
+      <c r="F43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>621</v>
+      </c>
+      <c r="B44" t="s">
+        <v>622</v>
+      </c>
+      <c r="C44" t="s">
+        <v>604</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="E44" t="s">
+        <v>493</v>
+      </c>
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>624</v>
+      </c>
+      <c r="B45" t="s">
+        <v>625</v>
+      </c>
+      <c r="C45" t="s">
+        <v>604</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="E45" t="s">
+        <v>493</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>627</v>
+      </c>
+      <c r="B46" t="s">
+        <v>628</v>
+      </c>
+      <c r="C46" t="s">
+        <v>604</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E46" t="s">
+        <v>493</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>630</v>
+      </c>
+      <c r="B47" t="s">
+        <v>631</v>
+      </c>
+      <c r="C47" t="s">
+        <v>604</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="E47" t="s">
+        <v>493</v>
+      </c>
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>633</v>
+      </c>
+      <c r="B48" t="s">
+        <v>634</v>
+      </c>
+      <c r="C48" t="s">
+        <v>604</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E48" t="s">
+        <v>493</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>636</v>
+      </c>
+      <c r="B49" t="s">
+        <v>637</v>
+      </c>
+      <c r="C49" t="s">
+        <v>604</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="E49" t="s">
+        <v>493</v>
+      </c>
+      <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>639</v>
+      </c>
+      <c r="B50" t="s">
+        <v>640</v>
+      </c>
+      <c r="C50" t="s">
+        <v>604</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="E50" t="s">
+        <v>493</v>
+      </c>
+      <c r="F50" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>642</v>
+      </c>
+      <c r="B51" t="s">
+        <v>643</v>
+      </c>
+      <c r="C51" t="s">
+        <v>604</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E51" t="s">
+        <v>493</v>
+      </c>
+      <c r="F51" t="s">
+        <v>30</v>
+      </c>
+      <c r="G51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>645</v>
+      </c>
+      <c r="B52" t="s">
+        <v>646</v>
+      </c>
+      <c r="C52" t="s">
+        <v>604</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="E52" t="s">
+        <v>493</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>648</v>
+      </c>
+      <c r="B53" t="s">
+        <v>649</v>
+      </c>
+      <c r="C53" t="s">
+        <v>604</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="E53" t="s">
+        <v>493</v>
+      </c>
+      <c r="F53" t="s">
+        <v>30</v>
+      </c>
+      <c r="G53" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>651</v>
+      </c>
+      <c r="B54" t="s">
+        <v>652</v>
+      </c>
+      <c r="C54" t="s">
+        <v>604</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E54" t="s">
+        <v>493</v>
+      </c>
+      <c r="F54" t="s">
+        <v>30</v>
+      </c>
+      <c r="G54" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>654</v>
+      </c>
+      <c r="B55" t="s">
+        <v>655</v>
+      </c>
+      <c r="C55" t="s">
+        <v>604</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="E55" t="s">
+        <v>493</v>
+      </c>
+      <c r="F55" t="s">
+        <v>30</v>
+      </c>
+      <c r="G55" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>657</v>
+      </c>
+      <c r="B56" t="s">
+        <v>658</v>
+      </c>
+      <c r="C56" t="s">
+        <v>604</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="E56" t="s">
+        <v>493</v>
+      </c>
+      <c r="F56" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>660</v>
+      </c>
+      <c r="B57" t="s">
+        <v>661</v>
+      </c>
+      <c r="C57" t="s">
+        <v>604</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E57" t="s">
+        <v>493</v>
+      </c>
+      <c r="F57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>663</v>
+      </c>
+      <c r="B58" t="s">
+        <v>664</v>
+      </c>
+      <c r="C58" t="s">
+        <v>665</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="E58" t="s">
+        <v>493</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>667</v>
+      </c>
+      <c r="B59" t="s">
+        <v>668</v>
+      </c>
+      <c r="C59" t="s">
+        <v>665</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E59" t="s">
+        <v>493</v>
+      </c>
+      <c r="F59" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>670</v>
+      </c>
+      <c r="B60" t="s">
+        <v>671</v>
+      </c>
+      <c r="C60" t="s">
+        <v>665</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E60" t="s">
+        <v>493</v>
+      </c>
+      <c r="F60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>673</v>
+      </c>
+      <c r="B61" t="s">
+        <v>674</v>
+      </c>
+      <c r="C61" t="s">
+        <v>665</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E61" t="s">
+        <v>493</v>
+      </c>
+      <c r="F61" t="s">
+        <v>30</v>
+      </c>
+      <c r="G61" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>676</v>
+      </c>
+      <c r="B62" t="s">
+        <v>677</v>
+      </c>
+      <c r="C62" t="s">
+        <v>665</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="E62" t="s">
+        <v>493</v>
+      </c>
+      <c r="F62" t="s">
+        <v>30</v>
+      </c>
+      <c r="G62" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>679</v>
+      </c>
+      <c r="B63" t="s">
+        <v>680</v>
+      </c>
+      <c r="C63" t="s">
+        <v>665</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="E63" t="s">
+        <v>493</v>
+      </c>
+      <c r="F63" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>682</v>
+      </c>
+      <c r="B64" t="s">
+        <v>683</v>
+      </c>
+      <c r="C64" t="s">
+        <v>665</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E64" t="s">
+        <v>493</v>
+      </c>
+      <c r="F64" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>685</v>
+      </c>
+      <c r="B65" t="s">
+        <v>686</v>
+      </c>
+      <c r="C65" t="s">
+        <v>665</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E65" t="s">
+        <v>493</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>688</v>
+      </c>
+      <c r="B66" t="s">
+        <v>689</v>
+      </c>
+      <c r="C66" t="s">
+        <v>665</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="E66" t="s">
+        <v>493</v>
+      </c>
+      <c r="F66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>691</v>
+      </c>
+      <c r="B67" t="s">
+        <v>692</v>
+      </c>
+      <c r="C67" t="s">
+        <v>665</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="E67" t="s">
+        <v>493</v>
+      </c>
+      <c r="F67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G67" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>694</v>
+      </c>
+      <c r="B68" t="s">
+        <v>695</v>
+      </c>
+      <c r="C68" t="s">
+        <v>665</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="E68" t="s">
+        <v>493</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>697</v>
+      </c>
+      <c r="B69" t="s">
+        <v>698</v>
+      </c>
+      <c r="C69" t="s">
+        <v>665</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="E69" t="s">
+        <v>493</v>
+      </c>
+      <c r="F69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>700</v>
+      </c>
+      <c r="B70" t="s">
+        <v>701</v>
+      </c>
+      <c r="C70" t="s">
+        <v>665</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E70" t="s">
+        <v>493</v>
+      </c>
+      <c r="F70" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>703</v>
+      </c>
+      <c r="B71" t="s">
+        <v>704</v>
+      </c>
+      <c r="C71" t="s">
+        <v>705</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="E71" t="s">
+        <v>493</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>707</v>
+      </c>
+      <c r="B72" t="s">
+        <v>708</v>
+      </c>
+      <c r="C72" t="s">
+        <v>705</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E72" t="s">
+        <v>493</v>
+      </c>
+      <c r="F72" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>710</v>
+      </c>
+      <c r="B73" t="s">
+        <v>711</v>
+      </c>
+      <c r="C73" t="s">
+        <v>705</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E73" t="s">
+        <v>493</v>
+      </c>
+      <c r="F73" t="s">
+        <v>30</v>
+      </c>
+      <c r="G73" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>713</v>
+      </c>
+      <c r="B74" t="s">
+        <v>714</v>
+      </c>
+      <c r="C74" t="s">
+        <v>715</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="E74" t="s">
+        <v>493</v>
+      </c>
+      <c r="F74" t="s">
+        <v>30</v>
+      </c>
+      <c r="G74" t="s">
+        <v>291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="719">
   <si>
     <t>번호</t>
   </si>
@@ -49,7 +49,7 @@
     <t>관련 규정</t>
   </si>
   <si>
-    <t>추천 단어</t>
+    <t>추천 문장</t>
   </si>
   <si>
     <t>하면 안 되는 말</t>
@@ -97,7 +97,9 @@
     <t>관리업무요강 제2조 제4호: 채무조정은 상환능력 등을 고려해 채무 감면, 상환기간 연장, 분할상환 등으로 채무 내용을 바꿔 채무부담 완화와 재기를 지원하는 것</t>
   </si>
   <si>
-    <t>채무조정 프로그램, 추심 중단, 상환기간 연장</t>
+    <t xml:space="preserve">빚 부담을 줄여 주는 채무조정 제도입니다.
+신청하면 추심이 중단됩니다.
+새로 대출해 주는 제도는 아닙니다.</t>
   </si>
   <si>
     <t>새로 대출을 받으실 수 있습니다</t>
@@ -135,7 +137,9 @@
     <t>관리업무요강 제2조 제4호: 채무조정은 이미 있는 채무의 내용(감면·기간 연장·분할상환)을 바꾸는 것</t>
   </si>
   <si>
-    <t>수수료 없음, 사칭 주의</t>
+    <t xml:space="preserve">새출발기금은 대출 상품이 아닙니다.
+채무조정 약정 수수료는 없습니다.
+기금 사칭 보이스피싱에 주의하세요.</t>
   </si>
   <si>
     <t>수수료를 내시면 빨리 처리됩니다</t>
@@ -167,7 +171,9 @@
     <t>관리업무요강 제2조 제6·7호: 부실차주는 1개 이상 채무가 3개월 이상 연체 중인 차주, 부실우려차주는 부실차주가 아니면서 금융회사 분류상 '요주의' 이하 등 장기연체 우려가 있는 차주</t>
   </si>
   <si>
-    <t>부실차주, 부실우려차주, 연체일수</t>
+    <t xml:space="preserve">3개월 이상 연체면 부실차주입니다.(제2조)
+연체 10~89일이면 부실우려차주입니다.
+폐업·휴업도 부실우려차주일 수 있어요.</t>
   </si>
   <si>
     <t>-</t>
@@ -193,7 +199,9 @@
 ㅇ 또한 채무조정 약정 후 부실차주에 대하여는 연체정보를 삭제하고 공공정보를 등록(1년간 성실상환 시 해제)함을 안내드립니다.</t>
   </si>
   <si>
-    <t>예·적금 상계, 한도 감축, 공공정보 등록</t>
+    <t xml:space="preserve">신청 후 예·적금이 상계될 수 있어요.
+카드 이용이 정지될 수 있습니다.
+1년 성실상환하면 공공정보가 해제돼요.</t>
   </si>
   <si>
     <t>신청하셔도 아무 불이익이 없습니다</t>
@@ -219,7 +227,9 @@
     <t>관리업무요강 제32조 제4·5호: 새출발기금 약정 후 파산·개인회생이나 신용회복위원회 채무조정을 신청하면 새출발기금 채무조정 효력이 상실됨</t>
   </si>
   <si>
-    <t>소상공인 전용, 무담보 10년, 담보 20년</t>
+    <t xml:space="preserve">소상공인·자영업자 전용 제도입니다.
+무담보 10년, 담보 20년까지 갚아요.
+약정 후 회생 신청 시 효력 상실(제32조)</t>
   </si>
   <si>
     <t>006</t>
@@ -245,7 +255,8 @@
     <t>새출발기금 지원 협약 / 관리업무요강 제2조 제5호: 채권금융회사는 협약에 가입하고 대상차주에 대한 채권을 가진(또는 새출발기금에 넘긴) 금융회사·보증기관</t>
   </si>
   <si>
-    <t>협약기관, 미협약기관, 타 채무조정 제도</t>
+    <t xml:space="preserve">협약 금융기관 대출만 지원됩니다.
+미협약 대출은 다른 제도를 안내해요.</t>
   </si>
   <si>
     <t>모든 금융기관 대출이 다 됩니다</t>
@@ -275,7 +286,9 @@
     <t>관리업무요강 제11조①: 새출발기금 온라인 플랫폼으로 신청하고, 온라인 이용이 어려우면 상담창구 등으로 신청할 수 있음</t>
   </si>
   <si>
-    <t>새출발기금.kr, 캠코 상담 창구, 신용회복위원회 방문</t>
+    <t xml:space="preserve">새출발기금.kr에서 온라인 신청합니다.
+어려우시면 캠코 상담창구도 됩니다.
+담보대출은 신복위 방문 접수입니다.</t>
   </si>
   <si>
     <t>캠코 상담 창구 / 신용회복위원회 서민금융통합지원센터</t>
@@ -303,7 +316,8 @@
     <t>관리업무요강 제2조 제12호: 자산관리자는 새출발기금으로부터 관리·운용 업무를 위탁받은 한국자산관리공사 / 제11조①: 온라인 플랫폼 신청, 어려우면 상담창구 등</t>
   </si>
   <si>
-    <t>매입형, 중개형</t>
+    <t xml:space="preserve">신용·보증대출은 캠코 매입형입니다.
+담보대출은 신복위 중개형입니다.</t>
   </si>
   <si>
     <t>캠코(매입형) / 신용회복위원회(중개형)</t>
@@ -328,7 +342,8 @@
     <t>관리업무요강 제16조②: 신청을 취소하면 취소 신청일부터 3개월간 재신청이 제한됨</t>
   </si>
   <si>
-    <t>1회 제한, 미납 실효 시 매입</t>
+    <t xml:space="preserve">채무조정 신청은 1회로 제한됩니다.
+취소하면 3개월 재신청 불가(제16조)</t>
   </si>
   <si>
     <t>언제든 다시 신청하시면 됩니다</t>
@@ -357,7 +372,8 @@
     <t>관리업무요강 제2조 제6·7호: 부실차주는 1개 이상 채무가 3개월 이상 연체 중인 차주, 부실우려차주는 부실차주가 아니면서 '요주의' 이하 등 장기연체 우려가 있는 차주</t>
   </si>
   <si>
-    <t>부실우려차주 요건</t>
+    <t xml:space="preserve">연체가 없어도 신청할 수 있습니다.
+폐업·휴업·세금 체납이면 해당돼요.</t>
   </si>
   <si>
     <t>연체가 없으면 신청하실 수 없습니다</t>
@@ -384,7 +400,8 @@
     <t>관리업무요강 제32조 제4·5호: 약정 후 파산·개인회생을 신청하거나 신용회복위원회 채무조정을 신청하면 채무조정 효력이 상실됨</t>
   </si>
   <si>
-    <t>제도별 특징 비교</t>
+    <t xml:space="preserve">회생·신복위 상환 중이면 신청 불가예요.
+신청 단계면 취소 후 신청할 수 있어요.</t>
   </si>
   <si>
     <t>신용회복위원회, 법원</t>
@@ -411,7 +428,8 @@
     <t>관리업무요강 제15조①: 신청을 마치면 신청일 다음날부터 2주일 이내에 채무조정임시안을 제시함</t>
   </si>
   <si>
-    <t>신청량 증가, 선택적 동의 재동의</t>
+    <t xml:space="preserve">신청이 몰리면 2주를 넘길 수 있어요.
+선택 동의를 다시 하셔야 할 수 있어요.</t>
   </si>
   <si>
     <t>2주 안에 무조건 나옵니다</t>
@@ -439,7 +457,8 @@
     <t>관리업무요강 제17조①: 약정할 때 신청서 기재사항과 채무부담액 산정 기초자료(나이·소득·재산 등)가 일치하는지 확인 / 제32조 제2호: 신청 자료나 진술이 허위면 효력 상실</t>
   </si>
   <si>
-    <t>임시안, 본 약정 때 보완</t>
+    <t xml:space="preserve">2주 안에 받는 안은 임시안입니다.
+잘못 입력한 건 본 약정 때 고치면 돼요.</t>
   </si>
   <si>
     <t>014</t>
@@ -464,7 +483,8 @@
     <t>관리업무요강 제15조①: 채무조정임시안은 한국신용정보원에서 제공한 채무액을 기초로 작성함</t>
   </si>
   <si>
-    <t>이의신청, 부채증명원</t>
+    <t xml:space="preserve">홈페이지 이의신청으로 접수해 주세요.
+부채증명원 등 증빙을 첨부해 주세요.</t>
   </si>
   <si>
     <t>새출발기금 홈페이지 이의신청</t>
@@ -494,7 +514,9 @@
     <t>관리업무요강 제16조: 신청을 완료한 달의 다음 달 15일까지 취소할 수 있고, 취소하면 취소 신청일부터 3개월간 재신청이 제한됨</t>
   </si>
   <si>
-    <t>익월 15일, 확정 전, 90일 재신청 제한</t>
+    <t xml:space="preserve">매입형은 다음 달 15일까지 취소돼요.
+중개형은 확정 전까지 취소할 수 있어요.
+취소하면 3개월 재신청 불가(제16조)</t>
   </si>
   <si>
     <t>취소하고 바로 다시 신청하시면 됩니다</t>
@@ -523,7 +545,9 @@
     <t>관리업무요강 제19조③: 부실우려차주가 3개월 이상 연체 등으로 약정 효력이 상실되면 매입형 채무조정으로 진행하고 채무부담액은 부실차주 기준으로 산정함</t>
   </si>
   <si>
-    <t>실효 후 매입, 미신청 채무 추가</t>
+    <t xml:space="preserve">실효되면 기금이 채권을 매입합니다.
+빠진 대출도 추가로 신청할 수 있어요.
+고객센터로 미신청 채무를 신청하세요.</t>
   </si>
   <si>
     <t>새출발기금 고객센터 1660-1378</t>
@@ -549,7 +573,8 @@
     <t>관리업무요강 제2조 제1·2호: 대상차주는 새출발기금 지원 대상인 협약상 차주, 주채무자는 대상차주(합명·합자회사는 대표 무한책임사원 포함)</t>
   </si>
   <si>
-    <t>개인사업자, 법인 소상공인</t>
+    <t xml:space="preserve">개인사업자와 법인 소상공인이 대상입니다.
+폐업한 법인은 지원되지 않습니다.</t>
   </si>
   <si>
     <t>폐업한 법인도 신청하실 수 있습니다</t>
@@ -578,7 +603,8 @@
     <t>소상공인 정책자금 융자 제외대상 업종</t>
   </si>
   <si>
-    <t>제외 업종</t>
+    <t xml:space="preserve">정책자금 제외 업종은 지원이 어려워요.
+부동산임대·금융·전문직 등이 해당돼요.</t>
   </si>
   <si>
     <t>모든 업종이 다 됩니다</t>
@@ -608,7 +634,8 @@
     <t>관리업무요강 제2조 제26호: 대상채권은 협약 금융회사 채권 중 새출발기금 지원 대상이 되는 원금·이자·가지급금·수수료·제비용</t>
   </si>
   <si>
-    <t>사업자대출, 가계대출, 6개월 내 신규대출 30%</t>
+    <t xml:space="preserve">사업자대출과 가계대출 모두 됩니다.
+6개월 내 신규대출은 제외될 수 있어요.</t>
   </si>
   <si>
     <t>가지고 계신 대출은 전부 됩니다</t>
@@ -636,7 +663,8 @@
     <t>관리업무요강 제18조②: 약정은 채무관계자 기준으로, 대상채권 계좌별로 채무부담액을 따로 산정한 뒤 합산해 한꺼번에 체결함</t>
   </si>
   <si>
-    <t>부실차주 일괄 신청, 부실우려 선택 신청</t>
+    <t xml:space="preserve">부실차주는 대출을 골라 신청 못 해요.
+부실우려차주는 골라서 신청할 수 있어요.</t>
   </si>
   <si>
     <t>원하시는 대출만 골라서 신청하시면 됩니다</t>
@@ -662,7 +690,8 @@
 ㅇ 따라서, 위 경우에는 담보가 12억원으로 한도를 초과하였기 때문에, 무담보가 3억원으로 한도를 초과하지 않아도 지원대상이 아닙니다.</t>
   </si>
   <si>
-    <t>총 15억, 담보 10억, 무담보 5억</t>
+    <t xml:space="preserve">조정 한도는 총 15억 원입니다.
+담보 10억, 무담보 5억을 넘으면 안 돼요.</t>
   </si>
   <si>
     <t>15억 안이면 됩니다</t>
@@ -688,7 +717,8 @@
     <t>새출발기금 지원 협약 / 관리업무요강 제13조: 신청을 완료한 다음 영업일 이내에 금융회사에 추심·강제경매·임의경매 등의 중지를 요청함</t>
   </si>
   <si>
-    <t>추심 중단, 매각기일, 개별 협의</t>
+    <t xml:space="preserve">신청 다음 날 추심 중지 요청(제13조)
+매각기일 잡힌 경매는 협의가 필요해요.</t>
   </si>
   <si>
     <t>신청하시면 경매가 모두 멈춥니다</t>
@@ -722,7 +752,9 @@
     <t>관리업무요강 제13조: 신청을 완료한 다음 영업일 이내에 금융회사에 추심행위 중지를 요청함 / 제47조: 폭행·협박, 반복·야간 전화나 방문 등 불법 추심은 금지</t>
   </si>
   <si>
-    <t>상계 2주, 신청 사실 고지</t>
+    <t xml:space="preserve">신청 후 2주간 예금 상계는 가능해요.
+금융기관에 신청 사실을 알려 주세요.
+반복·야간 추심은 금지입니다.(제47조)</t>
   </si>
   <si>
     <t>해당 금융기관 → 새출발기금 1660-1378</t>
@@ -749,7 +781,9 @@
     <t>관리업무요강 제15조①: 신청 후 2주일 이내 임시안 제시 / 제17조②: 확정안 승인 다음날부터 5영업일 이내에 약정(서명)하지 않으면 신청을 취소한 것으로 봄</t>
   </si>
   <si>
-    <t>임시안 2주, 매입형 3~4개월, 중개형 2~3개월</t>
+    <t xml:space="preserve">약 2주 안에 임시안이 나옵니다.
+매입형은 약정까지 3~4개월 걸려요.
+중개형은 확정까지 2~3개월 걸려요.</t>
   </si>
   <si>
     <t>한 달이면 끝납니다</t>
@@ -783,7 +817,9 @@
     <t>관리업무요강 제19조①: 부실우려차주는 원금 감면 없이 무담보채권 연체이자 전액 등을 감면 / ②: 부실차주는 별표 3 기준으로 채무부담액(감면 포함)을 산정</t>
   </si>
   <si>
-    <t>순부채, 무담보 대출</t>
+    <t xml:space="preserve">원금 감면은 부실차주 무담보만 돼요.
+담보대출은 원금 감면 대상이 아닙니다.
+부실우려차주는 연체이자 감면(제19조)</t>
   </si>
   <si>
     <t>신청하시면 원금을 깎아 드립니다</t>
@@ -813,7 +849,9 @@
     <t>관리업무요강 제20조: 사회취약계층은 별표 1 감면율을 적용하되, 재산이 있으면 회수가능액을 뺀 나머지 채무에만 감면율 적용. 약정 후 해당하게 되면 소급 신청 가능(소급 대상에 한함)</t>
   </si>
   <si>
-    <t>사회취약계층, 중위소득 60%, 순부채 90%</t>
+    <t xml:space="preserve">수급자·중증장애인·70세 이상 추가 지원
+부실차주 취약계층은 원금 90% 감면
+상환기간은 최대 20년까지 가능해요.</t>
   </si>
   <si>
     <t>027</t>
@@ -839,7 +877,8 @@
     <t>관리업무요강 제20조의2: 2020년 4월 이후 폐업한 부실차주가 지정 취업·재창업 교육을 이수하면 최대 10%p 추가 감면(신청서와 이수 증명서 제출, 상환 중 연체가 있으면 먼저 납부)</t>
   </si>
   <si>
-    <t>취업·재창업 교육, 최대 10%p</t>
+    <t xml:space="preserve">교육 이수한 폐업자는 최대 10%p 추가 감면
+영업 중이면 추가 감면 대상이 아니에요.</t>
   </si>
   <si>
     <t>교육 받으시면 10% 더 깎아 드립니다</t>
@@ -870,7 +909,9 @@
     <t>관리업무요강 제24조: 상환기간 변경은 1회만, 신청일까지 거치기간이자·연체 분할상환금을 모두 갚아야 함 / 제27조: 조기상환 승인 다음날부터 5영업일 이내에 잔액 전부 상환 / 제27조의2: 무담보 약정 1년·12회차 이상 납부한 부실차주가 일시상환하면 5~10% 추가 감면</t>
   </si>
   <si>
-    <t>동일 감면율 구간, 조기상환</t>
+    <t xml:space="preserve">상환기간 변경은 1회만 됩니다.(제24조)
+조기상환(중도상환)은 가능합니다.
+12회 이상 내고 일시상환 시 추가감면</t>
   </si>
   <si>
     <t>상환기간은 마음대로 바꾸실 수 있습니다</t>
@@ -901,7 +942,8 @@
     <t>관리업무요강 제46조④: 약정 때 등록한 공공정보는 1년(12회차) 성실상환하면 해제 / ⑤: 폐업한 부실차주가 지정 교육을 이수하고 취업·재창업하면 1회에 한해 신청으로 해제 가능</t>
   </si>
   <si>
-    <t>공공정보, 1년 12회 성실납부</t>
+    <t xml:space="preserve">1년 12회 성실납부하면 해제됩니다.
+폐업자는 취업·재창업 시 1회 해제돼요.</t>
   </si>
   <si>
     <t>약정하시면 바로 신용이 회복됩니다</t>
@@ -926,7 +968,8 @@
     <t>관리업무요강 제14조: 행정정보 공동이용망 등으로 채무관계자의 재산 유무를 확인함 / 제32조 제2·3호: 신청 자료가 허위이거나 재산 은닉 등이 발견되면 효력 상실</t>
   </si>
   <si>
-    <t>도덕적 해이 심사</t>
+    <t xml:space="preserve">신청자 전원 도덕적 해이 심사를 해요.
+고의 연체는 신청이 거절됩니다.</t>
   </si>
   <si>
     <t>새출발기금 홈페이지 자주하는 질문 &gt; 도덕적해이 (https://www.newstartfund.or.kr/Faq/List.do)</t>
@@ -952,7 +995,8 @@
     <t>관리업무요강 제2조 제5호: 채무조정 대상은 협약에 가입한 채권금융회사의 채권</t>
   </si>
   <si>
-    <t>금융기관 조회, 협약 가입 금융기관</t>
+    <t xml:space="preserve">홈페이지 '금융기관 조회'에서 확인하세요.
+협약 가입 기관 대출만 지원됩니다.</t>
   </si>
   <si>
     <t>모든 금융기관 대출이 다 지원됩니다</t>
@@ -986,7 +1030,8 @@
     <t>관리업무요강 제17조③: 약정할 때 재기지원 사업(취업알선, 상품안내 등)을 안내할 수 있음</t>
   </si>
   <si>
-    <t>성실상환자 재기지원 사업, 웹플랫폼 공지</t>
+    <t xml:space="preserve">성실상환자 재기지원 사업이 있습니다.
+웹플랫폼 공지와 알림톡으로 안내해요.</t>
   </si>
   <si>
     <t>신청하시면 자금 지원을 꼭 받으실 수 있습니다</t>
@@ -1014,7 +1059,8 @@
     <t>관리업무요강 제32조 제4호: 새출발기금 약정 후에 파산이나 개인회생을 신청하면 채무조정 효력이 상실됨</t>
   </si>
   <si>
-    <t>개인회생 폐지 후 신청, 유리한 제도 선택</t>
+    <t xml:space="preserve">개인회생 폐지 후 신청할 수 있습니다.
+두 제도를 비교해 유리한 쪽을 고르세요.</t>
   </si>
   <si>
     <t>새출발기금이 무조건 더 유리합니다</t>
@@ -1036,7 +1082,8 @@
 ㅇ 다만, 한명의 대표자가 두 개의 개인사업자 사업장을 운영하는 경우, 1개의 사업자로 1회에 한하여 신청 가능합니다.</t>
   </si>
   <si>
-    <t>사업자별 신청, 1개 사업자 1회</t>
+    <t xml:space="preserve">개인·법인 사업자는 각각 신청돼요.
+개인사업장 두 곳이면 1회만 신청돼요.</t>
   </si>
   <si>
     <t>사업장마다 따로 신청하시면 됩니다</t>
@@ -1058,7 +1105,8 @@
 ㅇ 다만, 지원 단계별 엄격한 심사 기준을 통과하는 경우에 한하여 채무조정 혜택을 부여하여 도덕적 해이 발생을 방지하고 있습니다.</t>
   </si>
   <si>
-    <t>사업자등록증, 단계별 심사</t>
+    <t xml:space="preserve">외국인도 대상이면 신청할 수 있습니다.
+사업자등록증이 있어야 합니다.</t>
   </si>
   <si>
     <t>외국인은 신청할 수 없습니다</t>
@@ -1083,7 +1131,8 @@
     <t>관리업무요강 제12조 제3호: 신청 서류 중 신분증 자리에, 법인 소상공인은 소상공인확인서를 냄</t>
   </si>
   <si>
-    <t>중소기업현황정보시스템, 일반 소상공인확인서</t>
+    <t xml:space="preserve">소진공 확인서는 쓸 수 없습니다.
+일반 소상공인확인서를 내 주세요.</t>
   </si>
   <si>
     <t>소진공 확인서를 내셔도 됩니다</t>
@@ -1111,7 +1160,8 @@
     <t>관리업무요강 제15조②: 금융회사에서 채권 인수가 끝나면 매입전산자료·원인서류(대출약정서 등)를 확인해 채무조정확정안을 제시함</t>
   </si>
   <si>
-    <t>대출정보와 연체정보 함께 조회, 약정 시 확인</t>
+    <t xml:space="preserve">대출과 연체정보가 함께 보여 그래요.
+약정 때 대상 채무를 확인할 수 있어요.</t>
   </si>
   <si>
     <t>038</t>
@@ -1133,7 +1183,8 @@
 □ 다만, 미협약기관 대출, 개인 자산형성 목적의 대출 등 새출발기금 지원 제외 대출은 지원이 어렵습니다.</t>
   </si>
   <si>
-    <t>중개형 채무조정, 채권 매입</t>
+    <t xml:space="preserve">먼저 신복위 중개형으로 지원합니다.
+부동의하면 기금이 채권을 매입해요.</t>
   </si>
   <si>
     <t>금융회사가 부동의하면 채무조정이 끝납니다</t>
@@ -1162,7 +1213,9 @@
     <t>관리업무요강 제59조: 새출발기금의 보전조치(가압류 등)는 원칙적으로 완납 때까지 유지. 채무조정 중 해제를 요청하면 재산의 회수가능액 이상 변제 등 요건을 갖출 때 취하 가능</t>
   </si>
   <si>
-    <t>약정 후 완제, 재산가치 이상 변제</t>
+    <t xml:space="preserve">신청만으로 가압류가 풀리지 않아요.
+원칙적으로 다 갚은 뒤 해제됩니다.
+재산가치 이상 갚으면 해제될 수 있어요.</t>
   </si>
   <si>
     <t>신청하시면 가압류가 바로 풀립니다</t>
@@ -1186,6 +1239,10 @@
     <t>관리업무요강 제2조 제6호, 제19조③: 중개형 채무조정 효력이 상실된 부실우려차주 등은 매입형 채무조정으로 진행하고, 채무부담액은 부실차주 기준으로 산정함</t>
   </si>
   <si>
+    <t xml:space="preserve">부실차주 신용·보증은 매입형입니다.
+담보·부실우려 채무는 중개형입니다.</t>
+  </si>
+  <si>
     <t>041</t>
   </si>
   <si>
@@ -1204,7 +1261,8 @@
     <t>관리업무요강 제2조 제26호: 대상채권은 협약 금융회사 채권 중 새출발기금 지원 대상이 되는 채권(원금·이자·수수료 등)</t>
   </si>
   <si>
-    <t>카드론, 현금서비스, 협약 금융회사</t>
+    <t xml:space="preserve">카드론·현금서비스도 지원될 수 있어요.
+협약 금융회사 채권이어야 합니다.</t>
   </si>
   <si>
     <t>카드빚은 지원되지 않습니다</t>
@@ -1228,7 +1286,8 @@
     <t>관리업무요강 제43조: 특수한 사정이 있으면 채무조정심의위원회 심의·의결로 감면율 조정 등을 결정할 수 있음</t>
   </si>
   <si>
-    <t>이의신청, 재심사</t>
+    <t xml:space="preserve">심사 결과에 이의신청할 수 있습니다.
+재심사 후 추가 심사는 어렵습니다.</t>
   </si>
   <si>
     <t>몇 번이고 다시 심사받으실 수 있습니다</t>
@@ -1253,7 +1312,8 @@
     <t>관리업무요강 제32조 제3·7호: 재산 도피·은닉이 발견되거나, 신청 때 회수 가능한 재산을 신고하지 않고 약정한 경우 효력 상실 / 제14조: 완제 후 재산조사는 1회</t>
   </si>
   <si>
-    <t>정기적 재산 조사, 채무조정 무효</t>
+    <t xml:space="preserve">약정 후에도 재산 조사를 합니다.
+은닉재산이 나오면 조정이 무효예요.</t>
   </si>
   <si>
     <t>약정하고 나면 더 조사하지 않습니다</t>
@@ -1297,7 +1357,9 @@
     <t>관리업무요강 제26조</t>
   </si>
   <si>
-    <t>채무상환 유예(연장) 신청서, 최장 3년, 연체 먼저 해소</t>
+    <t xml:space="preserve">입원·실직·출산 등은 유예 신청 가능
+총 유예기간은 최장 3년(제26조)
+밀린 상환금을 먼저 내셔야 해요.</t>
   </si>
   <si>
     <t>사유 없이도 유예해 드립니다</t>
@@ -1346,7 +1408,9 @@
     <t>관리업무요강 제32조, 제33조</t>
   </si>
   <si>
-    <t>3회차 연체, 효력 상실 예정 통지</t>
+    <t xml:space="preserve">3회차 이상 연체하면 효력 상실(제32조)
+상실 10영업일 전에 미리 알려 드려요.
+회생·파산 신청도 상실 사유입니다.</t>
   </si>
   <si>
     <t>몇 달 밀려도 괜찮습니다</t>
@@ -1376,7 +1440,8 @@
     <t>관리업무요강 제34조</t>
   </si>
   <si>
-    <t>상실일부터 6개월 이내, 1회분 납부 부활</t>
+    <t xml:space="preserve">상실 후 6개월 안에 부활할 수 있어요.
+1회분만 내고 부활할 수도 있어요.(제34조)</t>
   </si>
   <si>
     <t>언제든지 부활할 수 있습니다</t>
@@ -1409,7 +1474,8 @@
     <t>관리업무요강 제35조</t>
   </si>
   <si>
-    <t>재약정 신청서, 거치기간 없음</t>
+    <t xml:space="preserve">효력 상실 후 재약정할 수 있습니다.
+재약정에는 거치기간이 없습니다.(제35조)</t>
   </si>
   <si>
     <t>재약정하면 거치기간을 다시 받으실 수 있습니다</t>
@@ -1446,7 +1512,8 @@
     <t>관리업무요강 제21조</t>
   </si>
   <si>
-    <t>최초 약정 1회, 최대 1년(특례 3년)</t>
+    <t xml:space="preserve">거치기간은 최초 약정 때 1회만 돼요.
+최대 1년, 특례대상은 3년(제21조)</t>
   </si>
   <si>
     <t>거치기간은 언제든 다시 받을 수 있습니다</t>
@@ -1485,7 +1552,9 @@
     <t>관리업무요강 제23조, 제25조, 제30조</t>
   </si>
   <si>
-    <t>5·10·15·20·25일, 상환기일 변경 1회, CMS 자동이체</t>
+    <t xml:space="preserve">상환일은 5·10·15·20·25일 중 고르세요.
+상환일 변경은 1회만 됩니다.(제25조)
+CMS 자동이체 수수료는 기금 부담이에요.</t>
   </si>
   <si>
     <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
@@ -1522,7 +1591,8 @@
     <t>관리업무요강 제12조</t>
   </si>
   <si>
-    <t>채무승인 및 조정 확약서, 사업자등록증, 행정정보 공동이용 동의</t>
+    <t xml:space="preserve">확약서·사업자등록증·신분증이 필요해요.
+정보 이용 동의서도 함께 받습니다.(제12조)</t>
   </si>
   <si>
     <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
@@ -1554,7 +1624,8 @@
     <t>관리업무요강 제11조</t>
   </si>
   <si>
-    <t>순자산 6.5억원, 채무조정 신청 위임장</t>
+    <t xml:space="preserve">순자산 6.5억 원 초과면 제외(제11조)
+대리 신청은 위임장이 필요합니다.</t>
   </si>
   <si>
     <t>재산과 상관없이 누구나 됩니다</t>
@@ -1639,6 +1710,9 @@
   </si>
   <si>
     <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본) 본문 조문 73개를 원문 그대로 옮긴 시트. 추천DB "관련 규정" 칸의 조문 번호로 찾아 카드에 전문을 보여 준다.</t>
+  </si>
+  <si>
+    <t>상담 중 그대로 말할 수 있는 30자 이내 문장 2~3개(칸 안에서 줄바꿈으로 구분). 답변 요약·FAQ 원문·관련 규정 내용만으로 썼고, 요강에서 온 내용은 (제N조)를 붙였다. 실제 사용 전 담당자 검토 필요(2026-10-29 초안).</t>
   </si>
   <si>
     <t>조문</t>
@@ -5250,7 +5324,7 @@
         <v>361</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>90</v>
+        <v>362</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>49</v>
@@ -5270,10 +5344,10 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -5291,22 +5365,22 @@
         <v>67</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>49</v>
@@ -5323,10 +5397,10 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -5344,22 +5418,22 @@
         <v>128</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>49</v>
@@ -5376,10 +5450,10 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -5397,22 +5471,22 @@
         <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>49</v>
@@ -5429,10 +5503,10 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -5447,31 +5521,31 @@
         <v>19</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>30</v>
@@ -5482,10 +5556,10 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -5503,28 +5577,28 @@
         <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>30</v>
@@ -5535,10 +5609,10 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -5556,28 +5630,28 @@
         <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>30</v>
@@ -5588,10 +5662,10 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -5609,28 +5683,28 @@
         <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>30</v>
@@ -5641,10 +5715,10 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -5653,7 +5727,7 @@
         <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>19</v>
@@ -5662,28 +5736,28 @@
         <v>232</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>30</v>
@@ -5694,10 +5768,10 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -5715,28 +5789,28 @@
         <v>232</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>30</v>
@@ -5747,10 +5821,10 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -5768,19 +5842,19 @@
         <v>52</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>49</v>
@@ -5789,7 +5863,7 @@
         <v>49</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>30</v>
@@ -5800,10 +5874,10 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -5821,28 +5895,28 @@
         <v>43</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>30</v>
@@ -5868,10 +5942,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5879,7 +5953,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5887,7 +5961,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5895,7 +5969,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5903,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5911,23 +5985,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5938,7 +6012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5947,18 +6021,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5966,7 +6040,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5974,7 +6048,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5982,15 +6056,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5998,15 +6072,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6014,15 +6088,23 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B10" t="s">
-        <v>484</v>
+        <v>485</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -6047,16 +6129,16 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>14</v>
@@ -6070,19 +6152,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
@@ -6093,19 +6175,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="E3" t="s">
         <v>495</v>
-      </c>
-      <c r="C3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="E3" t="s">
-        <v>493</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
@@ -6116,19 +6198,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
         <v>30</v>
@@ -6139,19 +6221,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B5" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -6162,19 +6244,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -6185,19 +6267,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -6208,19 +6290,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B8" t="s">
+        <v>513</v>
+      </c>
+      <c r="C8" t="s">
         <v>510</v>
       </c>
-      <c r="B8" t="s">
-        <v>511</v>
-      </c>
-      <c r="C8" t="s">
-        <v>508</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
@@ -6231,19 +6313,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B9" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
@@ -6254,19 +6336,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>519</v>
+      </c>
+      <c r="B10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" t="s">
         <v>517</v>
       </c>
-      <c r="B10" t="s">
-        <v>518</v>
-      </c>
-      <c r="C10" t="s">
-        <v>515</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
@@ -6277,19 +6359,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B11" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -6300,19 +6382,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E12" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
@@ -6323,19 +6405,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C13" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E13" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
@@ -6346,19 +6428,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E14" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
@@ -6369,19 +6451,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E15" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
@@ -6392,19 +6474,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>538</v>
+      </c>
+      <c r="B16" t="s">
+        <v>539</v>
+      </c>
+      <c r="C16" t="s">
         <v>536</v>
       </c>
-      <c r="B16" t="s">
-        <v>537</v>
-      </c>
-      <c r="C16" t="s">
-        <v>534</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E16" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
@@ -6415,19 +6497,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B17" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E17" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -6438,19 +6520,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B18" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E18" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
@@ -6461,19 +6543,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B19" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C19" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E19" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
@@ -6484,19 +6566,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B20" t="s">
         <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E20" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
@@ -6507,19 +6589,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B21" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C21" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E21" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
@@ -6530,19 +6612,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B22" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C22" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E22" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
@@ -6553,19 +6635,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B23" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C23" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E23" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
@@ -6576,19 +6658,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B24" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C24" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
@@ -6599,19 +6681,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>565</v>
+      </c>
+      <c r="B25" t="s">
+        <v>566</v>
+      </c>
+      <c r="C25" t="s">
         <v>563</v>
       </c>
-      <c r="B25" t="s">
-        <v>564</v>
-      </c>
-      <c r="C25" t="s">
-        <v>561</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E25" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
@@ -6622,19 +6704,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B26" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C26" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E26" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
@@ -6645,19 +6727,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B27" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C27" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E27" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
@@ -6668,19 +6750,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B28" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C28" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E28" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
@@ -6691,19 +6773,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B29" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C29" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E29" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
@@ -6714,19 +6796,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B30" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C30" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E30" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F30" t="s">
         <v>30</v>
@@ -6737,19 +6819,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B31" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F31" t="s">
         <v>30</v>
@@ -6760,19 +6842,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B32" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C32" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E32" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
@@ -6783,19 +6865,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B33" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C33" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E33" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F33" t="s">
         <v>30</v>
@@ -6806,19 +6888,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B34" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C34" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E34" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
@@ -6829,19 +6911,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B35" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C35" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E35" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
@@ -6852,19 +6934,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B36" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C36" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E36" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
@@ -6875,19 +6957,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B37" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C37" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E37" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
@@ -6898,19 +6980,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B38" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C38" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E38" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
@@ -6921,19 +7003,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>608</v>
+      </c>
+      <c r="B39" t="s">
+        <v>609</v>
+      </c>
+      <c r="C39" t="s">
         <v>606</v>
       </c>
-      <c r="B39" t="s">
-        <v>607</v>
-      </c>
-      <c r="C39" t="s">
-        <v>604</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E39" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F39" t="s">
         <v>30</v>
@@ -6944,19 +7026,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B40" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C40" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E40" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
@@ -6967,19 +7049,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B41" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C41" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F41" t="s">
         <v>30</v>
@@ -6990,19 +7072,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B42" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C42" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E42" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F42" t="s">
         <v>30</v>
@@ -7013,19 +7095,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B43" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C43" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E43" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
@@ -7036,19 +7118,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B44" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C44" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E44" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F44" t="s">
         <v>30</v>
@@ -7059,19 +7141,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B45" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C45" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E45" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
@@ -7082,19 +7164,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B46" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C46" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E46" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
@@ -7105,19 +7187,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B47" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C47" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E47" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
@@ -7128,19 +7210,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B48" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C48" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E48" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
@@ -7151,19 +7233,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B49" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C49" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E49" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
@@ -7174,19 +7256,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B50" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C50" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E50" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
@@ -7197,19 +7279,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B51" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C51" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E51" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
@@ -7220,19 +7302,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B52" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C52" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E52" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
@@ -7243,19 +7325,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B53" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C53" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E53" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
@@ -7266,19 +7348,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B54" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C54" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E54" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
@@ -7289,19 +7371,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B55" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C55" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E55" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
@@ -7312,19 +7394,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B56" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C56" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E56" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
@@ -7335,19 +7417,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B57" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C57" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E57" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
@@ -7358,19 +7440,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B58" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C58" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E58" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F58" t="s">
         <v>30</v>
@@ -7381,19 +7463,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>669</v>
+      </c>
+      <c r="B59" t="s">
+        <v>670</v>
+      </c>
+      <c r="C59" t="s">
         <v>667</v>
       </c>
-      <c r="B59" t="s">
-        <v>668</v>
-      </c>
-      <c r="C59" t="s">
-        <v>665</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E59" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
@@ -7404,19 +7486,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B60" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C60" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E60" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
@@ -7427,19 +7509,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B61" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C61" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E61" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
@@ -7450,19 +7532,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B62" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C62" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E62" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -7473,19 +7555,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B63" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C63" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E63" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -7496,19 +7578,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B64" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C64" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E64" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
@@ -7519,19 +7601,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B65" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C65" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E65" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
@@ -7542,19 +7624,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B66" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C66" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E66" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
@@ -7565,19 +7647,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B67" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C67" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E67" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
@@ -7588,19 +7670,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B68" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C68" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E68" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
@@ -7611,19 +7693,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B69" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C69" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E69" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
@@ -7634,19 +7716,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B70" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C70" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E70" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
@@ -7657,19 +7739,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B71" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C71" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E71" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
@@ -7680,19 +7762,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>709</v>
+      </c>
+      <c r="B72" t="s">
+        <v>710</v>
+      </c>
+      <c r="C72" t="s">
         <v>707</v>
       </c>
-      <c r="B72" t="s">
-        <v>708</v>
-      </c>
-      <c r="C72" t="s">
-        <v>705</v>
-      </c>
       <c r="D72" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E72" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
@@ -7703,19 +7785,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B73" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C73" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E73" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
@@ -7726,19 +7808,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B74" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C74" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E74" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
@@ -7749,6 +7831,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="726">
   <si>
     <t>번호</t>
   </si>
@@ -425,7 +425,7 @@
     <t>□ 신청량 증가로 2주안에 채무조정(안)을 받아보지 못한 경우가 있을 수 있고, 개인정보(선택적동의정보)를 동의하지 않아 재동의 절차 진행 등으로 시간이 추가 소요되는 경우도 있습니다.</t>
   </si>
   <si>
-    <t>관리업무요강 제15조①: 신청을 마치면 신청일 다음날부터 2주일 이내에 채무조정임시안을 제시함</t>
+    <t>관리업무요강 제15조①: 신청을 마치면 신청일 다음날부터 2주일 이내에 채무조정임시안을 제시함(가상자산·비상장주식 등 추가 재산조사가 필요하면 관련 서류 제출을 마친 때부터 2주일 이내)</t>
   </si>
   <si>
     <t xml:space="preserve">신청이 몰리면 2주를 넘길 수 있어요.
@@ -433,6 +433,9 @@
   </si>
   <si>
     <t>2주 안에 무조건 나옵니다</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
   </si>
   <si>
     <t>013</t>
@@ -778,7 +781,7 @@
 ㅇ (중개형 채무조정) 중개형 채무조정 신청부터 채무조정 확정까지 평균 2~3개월 가량 소요, 보증부 채권의 경우 대위변제 절차 등으로 추가 3~4개월 소요</t>
   </si>
   <si>
-    <t>관리업무요강 제15조①: 신청 후 2주일 이내 임시안 제시 / 제17조②: 확정안 승인 다음날부터 5영업일 이내에 약정(서명)하지 않으면 신청을 취소한 것으로 봄</t>
+    <t>관리업무요강 제15조①: 신청 후 2주일 이내 임시안 제시(가상자산·비상장주식 등 추가 재산조사가 필요하면 관련 서류 제출을 마친 때부터 2주일 이내) / 제17조②: 확정안 승인 다음날부터 5영업일 이내에 약정(서명)하지 않으면 신청을 취소한 것으로 봄</t>
   </si>
   <si>
     <t xml:space="preserve">약 2주 안에 임시안이 나옵니다.
@@ -1003,9 +1006,6 @@
   </si>
   <si>
     <t>새출발기금 홈페이지 '금융기관 조회'</t>
-  </si>
-  <si>
-    <t>2026-10-29</t>
   </si>
   <si>
     <t>032</t>
@@ -1344,7 +1344,7 @@
 6. 채무관계자 또는 그 배우자가 출산·육아휴직하는 경우(2026.3.25. 본호신설)
 7. 1년(12회차) 이상 상환한 채무관계자가 제1호에서 제6호까지 외의 기타 사정으로 채무변제가 어려울 경우(2026.3.25. 본호신설)
 8. 그 밖에 주무부점의 장이 긴급하게 상환유예가 필요하다고 인정하는 경우
-② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대해서는 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
+② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대하여 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
 ③ 제1항제4호에 해당하는 채무관계자에 대하여 채무부담액의 상환유예 사유가 해소될 때까지 상환을 유예할 수 있다.
 ④ 제1항 제6호 중 출산의 경우에는 출생일로부터 1년, 육아휴직의 경우에는 휴직기간 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
 ⑤ 제1항 제7호에 해당하는 경우에는 상환유예 신청일로부터 2개월 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
@@ -1365,7 +1365,7 @@
     <t>사유 없이도 유예해 드립니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제26조(채무부담액의 상환유예) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제26조(채무부담액의 상환유예) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>045</t>
@@ -1416,7 +1416,7 @@
     <t>몇 달 밀려도 괜찮습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제32조(채무조정의 효력 상실), 제33조(연체 및 채무조정의 효력 상실 등 통지) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제32조(채무조정의 효력 상실), 제33조(연체 및 채무조정의 효력 상실 등 통지) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>046</t>
@@ -1447,7 +1447,7 @@
     <t>언제든지 부활할 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제34조(채무조정의 효력 부활) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제34조(채무조정의 효력 부활) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>047</t>
@@ -1481,7 +1481,7 @@
     <t>재약정하면 거치기간을 다시 받으실 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제35조(채무조정의 재약정) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제35조(채무조정의 재약정) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>048</t>
@@ -1519,7 +1519,7 @@
     <t>거치기간은 언제든 다시 받을 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제21조(거치기간) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제21조(거치기간) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>049</t>
@@ -1560,7 +1560,7 @@
     <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제23조(채무부담액의 상환방법), 제25조(상환기일의 변경), 제30조(채무부담액 등 회수) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제23조(채무부담액의 상환방법), 제25조(상환기일의 변경), 제30조(채무부담액 등 회수) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>050</t>
@@ -1595,24 +1595,24 @@
 정보 이용 동의서도 함께 받습니다.(제12조)</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>051</t>
   </si>
   <si>
-    <t>순자산, 재산 많으면, 자산, 6.5억, 지원 제외, 대리인, 위임장, 대리 신청, 대신 신청</t>
-  </si>
-  <si>
-    <t>[규정] 재산이 많아도 신청할 수 있나요? (순자산 기준·대리 신청)</t>
-  </si>
-  <si>
-    <t>온라인 플랫폼으로 신청하고, 어려우면 상담창구 등으로 신청한다. 주채무자의 순자산(자산-부채)이 6.5억원을 넘으면 지원 대상에서 제외되지만, 1회 이상 채무조정 약정을 맺은 이력이 있으면 지원 대상이다. 대리인이 신청하면 위임장을 받고 대리권을 확인한다.</t>
+    <t>대리인, 위임장, 대리 신청, 대신 신청, 위임 신청, 대위변제, 대신 갚기, 제3자 상환</t>
+  </si>
+  <si>
+    <t>[규정] 대리인이 대신 신청하거나 대신 갚을 수 있나요?</t>
+  </si>
+  <si>
+    <t>새출발기금 온라인 플랫폼으로 신청하고, 온라인 이용이 어려우면 상담창구 등으로 신청할 수 있다. 대리인이 신청하면 위임장(별지 제1호·제2호서식)을 받아 대리권을 확인한다. 채무관계자가 아닌 사람이 대신 갚으려면 대위변제 승낙서를 받는다.</t>
   </si>
   <si>
     <t xml:space="preserve">제11조(채무조정의 신청)
 ① 채무조정의 신청은 대상채권의 채무관계자가 새출발기금의 온라인 플랫폼을 통하여 신청한다. 다만, 채무관계자가 온라인 플랫폼을 이용하여 신청하기 어려운 경우에는 새출발기금 상담창구 등을 통하여 신청할 수 있다.
-② 주채무자의 순자산(자산-부채)규모가 6.5억원을 초과하는 경우에는 채무조정 지원 대상에서 제외한다. 다만, 1회 이상 채무조정 약정을 체결한 이력이 있는 채무관계자의 경우에는 채무조정 지원 대상으로 한다.
+② (비공개)
 ③ 채무관계자가 대리인을 통하여 채무조정을 신청하고자 할 경우에는 채무조정 신청 위임장(별지 제1호서식 또는 별지 제2호서식)을 수령하고 대리권이 있는지 여부를 확인하여야 한다.
 ④ 채무관계자가 아닌 제3자가 채무부담액의 전부 또는 일부에 대하여 대위변제를 신청하는 경우에는 별지 제3호서식의 대위변제에 대한 승낙서를 받은 후 변제받을 수 있다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 대위변제에 대한 승낙서 제출을 생략할 수 있다.
 1. 채무관계자가 아닌 제3자가 구상권을 행사하지 않기로 동의하여 별지 제4호서식의 대위변제 신청서를 받은 경우
@@ -1624,14 +1624,15 @@
     <t>관리업무요강 제11조</t>
   </si>
   <si>
-    <t xml:space="preserve">순자산 6.5억 원 초과면 제외(제11조)
-대리 신청은 위임장이 필요합니다.</t>
-  </si>
-  <si>
-    <t>재산과 상관없이 누구나 됩니다</t>
-  </si>
-  <si>
-    <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) — 2026.3.25. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t xml:space="preserve">온라인 플랫폼으로 신청합니다(제11조)
+대리 신청은 위임장이 필요합니다.
+대신 갚으려면 승낙서가 필요해요(제11조)</t>
+  </si>
+  <si>
+    <t>가족이면 위임장 없이 대신 신청돼요</t>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>버튼</t>
@@ -1676,7 +1677,7 @@
     <t>자료 출처</t>
   </si>
   <si>
-    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인) / 044~051은 「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행) 조문 기반 자료로, 제목 앞에 [규정]을 붙이고 "FAQ 원문" 칸에 조문을 그대로 옮겼다(2026-10-29).</t>
+    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인) / 044~051은 「새출발기금 위탁채권 관리업무요강」(2026.6.29. 시행 공개본) 조문 기반 자료로, 제목 앞에 [규정]을 붙이고 "FAQ 원문" 칸에 조문을 그대로 옮겼다(2026-10-29).</t>
   </si>
   <si>
     <t>홈페이지에 게시된 답변을 그대로 옮긴 칸. 근거 정확도 확인은 이 칸과 대조한다.</t>
@@ -1703,18 +1704,24 @@
     <t>민원인 이름·전화번호·고객번호 등 개인정보는 넣지 않는다.</t>
   </si>
   <si>
-    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 공개 위치: 캠코 홈페이지 정보공개 &gt; 법무자료 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100). 2026-10-29 확인 시 게시본은 2026.6.29. 일부개정·시행본이라, 바뀐 조항이 있으면 다시 맞춰야 한다.</t>
+    <t>「새출발기금 위탁채권 관리업무요강」(2026.6.29. 시행본, 새출발인수운영처) 조항을 줄인 칸. '관리업무요강 제N조'로 조항을 표시했다. 공개 위치: 캠코 홈페이지 정보공개 &gt; 법무자료 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100). 2026-10-29에 6.29. 일부개정·시행 공개본으로 다시 맞췄다.</t>
   </si>
   <si>
     <t>요강조문</t>
   </si>
   <si>
-    <t>「새출발기금 위탁채권 관리업무요강」(2026.3.25. 시행본) 본문 조문 73개를 원문 그대로 옮긴 시트. 추천DB "관련 규정" 칸의 조문 번호로 찾아 카드에 전문을 보여 준다.</t>
+    <t>「새출발기금 위탁채권 관리업무요강」(2026.6.29. 시행본, 공개본) 본문 조문 75개를 원문 그대로 옮긴 시트. 추천DB "관련 규정" 칸의 조문 번호로 찾아 카드에 전문을 보여 준다. 표는 "칸 | 칸" 줄로 옮겼다.</t>
   </si>
   <si>
     <t>상담 중 그대로 말할 수 있는 30자 이내 문장 2~3개(칸 안에서 줄바꿈으로 구분). 답변 요약·FAQ 원문·관련 규정 내용만으로 썼고, 요강에서 온 내용은 (제N조)를 붙였다. 실제 사용 전 담당자 검토 필요(2026-10-29 초안).</t>
   </si>
   <si>
+    <t>비공개</t>
+  </si>
+  <si>
+    <t>요강 공개본에서 '(비공개)'로 가려진 부분(제11조②, 제50조⑤ 제4~7호, 제53조②, 제53조의2·제53조의3, 별표 1~4, 별표 11, 별지 제42호서식)은 내용을 넣지 않고 '(비공개)' 표시만 그대로 둔다. 예전 3.25본에서 가져온 제11조②(순자산 기준) 내용은 2026-10-29에 뺐다.</t>
+  </si>
+  <si>
     <t>조문</t>
   </si>
   <si>
@@ -1739,7 +1746,7 @@
     <t>이 요강은 소상공인자영업자새출발기금 주식회사로부터 위탁받은 수탁채권에 대하여 「소상공인·자영업자 새출발기금 지원 협약」, 「소상공인자영업자새출발기금 운영 기준」 등에 따라 해당채권의 관리·운용·처분 및 기타 업무수행을 위한 세부사항, 절차 및 방법을 규정함을 목적으로 한다.</t>
   </si>
   <si>
-    <t>새출발기금 위탁채권 관리업무요강 (2026.3.25. 시행본) — 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+    <t>새출발기금 위탁채권 관리업무요강 (2026.6.29. 시행본) — 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
     <t>제2조</t>
@@ -1870,7 +1877,7 @@
     <t xml:space="preserve">① 담보물의 보전 및 관리는 「경비업법」에 따라 경비업의 허가를 받은 법인(이하 “경비회사”라 한다)과 관리용역계약을 체결하여 관리한다. 다만, 관리용역계약 체결이 곤란하거나 그 밖의 사유로 필요하다고 인정되는 경우에는 담보물을 관리하는 부점장의 승인을 얻어 달리 정할 수 있다.
 ② 담보물을 관리함에 있어 담보물의 가치, 성질, 이동가능성 등을 고려하여 사물인터넷디바이스(IOT) 전문업체를 이용하여 경비하거나 담보물을 창고 업체에 위탁하여 보관할 수 있다.
 ③ 담보물 보전 및 관리를 위하여 필요한 경우에는 해당 담보물에 새출발기금이 보유한 채권의 담보물임을 나타내는 표지를 부착할 수 있다.
-④ 양도담보물의 관리와 처분은 별표 5 새출발기금 양도담보물 관리ㆍ처분 기준에 따르고, 기계기구 경비는 별표 6 기계기구 경비용역 실시기준에 따른다.(2024.9.11., 2024.12.30. 본항개정)
+④ 양도담보물의 관리와 처분은 별표 5 새출발기금 양도담보물 관리·처분 기준, 기계기구 경비는 별표 6 기계기구 경비용역 실시기준에 따르고, 동산담보채권 및 이에 부수하는 동산담보물의 관리와 처분은 별표 10 새출발기금 동산담보 관리기준에 따른다..(2024.9.11., 2024.12.30., 2026.6.29 본항개정)
 ⑤ 제4항에도 불구하고 담보물 중 공장의 기계기구 보전관리는 「기계기구 유지보수·개보수 및 분리매각요강」에서 정하는 바에 따른다.(2024.9.11. 본항개정)
 ⑥ 제1항부터 제5항까지 규정된 사항 외에 담보물 보전 및 경비관리업무의 세부절차 및 방법 등은 「경비관리업무처리요강」에서 정한 바에 따른다.(2024.9.11. 본항신설)</t>
   </si>
@@ -1882,38 +1889,9 @@
   </si>
   <si>
     <t xml:space="preserve">① 담보물건에 대한 점검방법은 다음과 같다. 다만, 경비회사 등에서 관리하는 경우에는 이상유무보고서로 갈음할 수 있다.
-&lt;table border="1" cellspacing="0" cellpadding="4" style="border-collapse:collapse"&gt;
-&lt;tr&gt;
-&lt;td&gt;
-&lt;p&gt;종          류&lt;/p&gt;
-&lt;/td&gt;
-&lt;td&gt;
-&lt;p&gt;점검 주기&lt;/p&gt;
-&lt;/td&gt;
-&lt;td&gt;
-&lt;p&gt;점검횟수&lt;/p&gt;
-&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td&gt;
-&lt;p&gt;건물. 공장&lt;/p&gt;
-&lt;/td&gt;
-&lt;td&gt;
-&lt;p&gt;6개월&lt;/p&gt;
-&lt;/td&gt;
-&lt;td rowspan="2"&gt;
-&lt;p&gt;1회 이상&lt;/p&gt;
-&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td&gt;
-&lt;p&gt;기계기구 등 동산&lt;/p&gt;
-&lt;/td&gt;
-&lt;td&gt;
-&lt;p&gt;3개월&lt;/p&gt;
-&lt;/td&gt;
-&lt;/tr&gt;
-&lt;/table&gt;
+종류 | 점검 주기 | 점검횟수
+건물. 공장 | 6개월 | 1회 이상
+기계기구 등 동산 | 3개월 | 1회 이상
 ② 도난, 멸실, 훼손, 변질 또는 무단점유 등의 우려가 있을 때에는 제1항에도 불구하고 수시로 점검하여야 한다.
 ③ 제1항에도 불구하고 사고발생의 우려가 없을 것으로 예상되거나 점검을 실시하기 곤란한 사유가 발생한 경우에는 정기점검을 생략하거나 점검기간을 연장할 수 있다.
 ④ 등록원부를 통해 관리되는 동산 담보물건에 대한 점검은 생략할 수 있다.
@@ -1972,7 +1950,7 @@
   </si>
   <si>
     <t xml:space="preserve">① 채무조정의 신청은 대상채권의 채무관계자가 새출발기금의 온라인 플랫폼을 통하여 신청한다. 다만, 채무관계자가 온라인 플랫폼을 이용하여 신청하기 어려운 경우에는 새출발기금 상담창구 등을 통하여 신청할 수 있다.
-② 주채무자의 순자산(자산-부채)규모가 6.5억원을 초과하는 경우에는 채무조정 지원 대상에서 제외한다. 다만, 1회 이상 채무조정 약정을 체결한 이력이 있는 채무관계자의 경우에는 채무조정 지원 대상으로 한다.
+② (비공개)
 ③ 채무관계자가 대리인을 통하여 채무조정을 신청하고자 할 경우에는 채무조정 신청 위임장(별지 제1호서식 또는 별지 제2호서식)을 수령하고 대리권이 있는지 여부를 확인하여야 한다.
 ④ 채무관계자가 아닌 제3자가 채무부담액의 전부 또는 일부에 대하여 대위변제를 신청하는 경우에는 별지 제3호서식의 대위변제에 대한 승낙서를 받은 후 변제받을 수 있다. 다만, 다음 각 호의 어느 하나에 해당하는 경우에는 대위변제에 대한 승낙서 제출을 생략할 수 있다.
 1. 채무관계자가 아닌 제3자가 구상권을 행사하지 않기로 동의하여 별지 제4호서식의 대위변제 신청서를 받은 경우
@@ -2029,7 +2007,7 @@
     <t>제15조</t>
   </si>
   <si>
-    <t xml:space="preserve">① 채무관계자가 채무조정의 신청을 완료한 경우에는 한국신용정보원에서 제공한 채무액을 기초로 작성한 채무조정임시안을 주무부점의 소관업무 담당 팀장의 승인을 얻어 채무조정의 신청일의 다음날로부터 2주일 이내에 신청인에게 제시하여야 한다.
+    <t xml:space="preserve">① 채무관계자가 채무조정의 신청을 완료한 경우에는 한국신용정보원에서 제공한 채무액을 기초로 작성한 채무조정임시안을 주무부점의 소관업무 담당 팀장의 승인을 얻어 채무조정의 신청일의 다음날로부터 2주일 이내에 신청인에게 제시하여야 한다. 다만, 가상자산, 비상장주식 등 추가 재산조사가 필요한 경우에는 채무관계자가 추가 재산조사에 필요한 서류 제출을 완료한 시점부터 2주일 이내에 채무조정 임시안을 제시하여야 한다.(2026.6.29., 단서신설)
 ② 채권금융회사로부터 대상채권의 인수가 완료된 경우 매입전산자료, 원인서류(대출약정서, 대위변제증서 등을 포함한다) 등을 확인하여 채무조정확정안을 「위임전결규정」 별표의 Ⅲ-1-라-(1)에 따른 전결권자의 승인을 얻어 신청인에게 제시하여야 한다.
 ③ 제2항에 따른 채무조정확정안의 승인권자는 채무관계자의 소유재산 여부, 소득수준, 채무자의 연령, 상환기간 등을 종합적으로 검토하여 채무조정확정안의 승인 여부를 결정하여야 한다. 다만, 담보부채권의 경우에는 검토를 생략할 수 있다.
 ④ 채권금융회사의 요청에 의해 매입한 대상채권의 경우에는 해당채권의 채무관계자에게 우편 또는 문자메시지 등을 통해 채무상환을 안내하며, 채무관계자가 채무조정 신청 시에는 제2항에 따라 채무조정확정안을 신청인에게 제시하여야 한다.</t>
@@ -2076,7 +2054,8 @@
   <si>
     <t xml:space="preserve">① 채무조정을 신청한 채무관계자는 일시상환 방식 또는 분할상환 방식 중에서 상환 방식을 선택 할 수 있다. 다만, 채무부담액이 10만원 이하인 경우에는 일시상환 방식으로 하여야 한다.(2024.12.30. 본항개정)
 ② 채무조정의 약정은 채무관계자를 기준으로 체결하되, 대상채권 계좌별로 채무부담액을 개별적으로 산정한 후 이를 합산하여 채무관계자와 일괄 약정한다.
-③ 일괄 약정을 체결할 경우 납부(가상)계좌는 대상차주 단위로 부여한다. 다만, 부실차주가 담보부채무 및 무담보채무를 동시에 채무조정 신청하는 경우에는 채무별로 개별 약정하고, 납부(가상)계좌를 각각 부여할 수 있다.</t>
+③ 일괄 약정을 체결할 경우 납부(가상)계좌는 대상차주 단위로 부여한다. 다만, 부실차주가 담보부채무 및 무담보채무를 동시에 채무조정 신청하는 경우에는 채무별로 개별 약정하고, 납부(가상)계좌를 각각 부여할 수 있다.
+➃ 회수가능액이 500만원 이상인 부동산을 보유한 채무관계자가 상환 방식을 분할상환 방식으로 정한 경우에는 해당 재산에 대해 회수가능액의 120%를 채권최고액으로 하는 (근)저당권 설정 등 채권보전조치를 취하여야 한다. 다만, 채무관계자의 채무부담액이 500만원 미만인 경우에는 (근)저당권을 설정하지 않을 수 있다.(2026.6.29., 본항신설)</t>
   </si>
   <si>
     <t>제19조</t>
@@ -2203,7 +2182,7 @@
 6. 채무관계자 또는 그 배우자가 출산·육아휴직하는 경우(2026.3.25. 본호신설)
 7. 1년(12회차) 이상 상환한 채무관계자가 제1호에서 제6호까지 외의 기타 사정으로 채무변제가 어려울 경우(2026.3.25. 본호신설)
 8. 그 밖에 주무부점의 장이 긴급하게 상환유예가 필요하다고 인정하는 경우
-② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대해서는 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
+② 제1항 제1호부터 제3호까지, 제5호 및 제8호에 해당하는 채무관계자에 대하여 6개월 단위로 채무부담액의 상환유예 신청일로부터 최장 3년까지 상환을 유예할 수 있다.(2026.3.25. 본항개정)
 ③ 제1항제4호에 해당하는 채무관계자에 대하여 채무부담액의 상환유예 사유가 해소될 때까지 상환을 유예할 수 있다.
 ④ 제1항 제6호 중 출산의 경우에는 출생일로부터 1년, 육아휴직의 경우에는 휴직기간 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
 ⑤ 제1항 제7호에 해당하는 경우에는 상환유예 신청일로부터 2개월 동안 상환을 유예할 수 있다.(2026.3.25. 본항신설)
@@ -2219,7 +2198,7 @@
     <t>채무부담액의 조기상환</t>
   </si>
   <si>
-    <t xml:space="preserve">① 분할상환 중인 채무관계자가 개별 약정의 잔여 채무부담액 일시 상환을 신청하는 경우에는 별지 제15호서식 조기상환신청서를 받고 이를 승인할 수 있다.(2026.3.25. 본항개정)
+    <t xml:space="preserve">① 분할상환 중인 채무관계자가 개별 약정의 잔여 채무부담액 일시 상환을 신청하는 경우에는 별지 제15호서식 조기상환신청서를 받고 이를 승인할 수 있다.(2026.3.25. 본항개정).
 ② 조기상환을 신청한 채무관계자는 조기상환 승인일 다음날부터 5영업일 이내에 잔여 채무부담액 전부를 상환하여야 한다.
 ③ 부실우려차주 및 그 채무관계자 또는 부동산 담보부채무를 부담하는 부실차주 및 그 채무관계자는 제22조 제2항 및 제3항에 따라 잔여 채무부담액 및 조기상환일 전일까지의 발생이자를 포함하여 상환하여야 한다.(2025.5.29. 본항신설)</t>
   </si>
@@ -2549,8 +2528,22 @@
     <t>시효소송수행 기준</t>
   </si>
   <si>
-    <t xml:space="preserve">① 주무부점의 장은 대상채권의 시효중단을 위하여 시효완성 예정일 3개월 전에 시효관리대상채권의 선정 및 시효중단조치의 착수여부를 결정하여야 하며, 시효완성 예정일 1개월 전까지는 시효중단 조치를 하여야 한다.
-② 제1항에도 불구하고 시효관리대상채권 중 채권액에 비해 시효소송의 비용이 과다하거나 회수가능성이 적은 채권은 시효중단조치를 유보할 수 있다.</t>
+    <t xml:space="preserve">① 주무부점의 장은 대상채권의 시효중단을 위하여 시효완성 예정일 3개월 전에 시효관리대상채권의 선정 및 시효중단조치(지급명령 및 시효중단 소송을 포함한다. 이하 “시효중단조치”라 한다.)의 착수여부를 결정하여야 하며, 시효완성 예정일 1개월 전까지는 시효중단 조치를 하여야 한다. (2026.6.29., 본항개정)
+② 제1항에도 불구하고 시효관리대상채권 중 채권액에 비해 시효소송의 비용이 과다하거나 회수가능성이 적은 채권은 시효중단조치를 유보할 수 있다.
+➂ 대상채권을 인수한 후 처음으로 소멸시효가 도래한 때에는 채무관계자에 대하여 시효중단조치 착수를 원칙으로 한다.(2026.6.29. 본항신설)
+➃ 제3항에 따라 시효중단조치를 한 후 다시 소멸시효가 도래한 때에는 소멸시효 완성을 원칙으로 한다. 다만, 제53조의2에 따른 상환능력 심사 결과 상환능력이 있는 경우에는 시효중단조치에 착수하여야 한다.(2026.6.29. 본항신설)
+➄ 제4항 본문, 제53조제1항제1호부터 제6의2호까지 및 제10호 에도 불구하고 다음 각호의 어느 하나에 해당하는 경우에는 시효중단조치에 착수한다.(2026.6.29. 본항신설)
+1. 소멸시효 완성일이 도래할 때까지 공공정보 수집 등 재산조사가 이루어지지 않은 경우
+2. 주채무자 아닌 채무관계자에 대해 다음 각 목의 어느 하나에 해당하는 절차가 진행 중인 경우. 다만, 이 때에는 해당 절차가 진행 중인 채무관계자를 제외하고 시효중단조치에 착수한다.
+가. 한국자산관리공사 내규에 따른 채무조정 절차
+나. 「채무자 회생 및 파산에 관한 법률」에 따른 파산절차
+다. 「채무자 회생 및 파산에 관한 법률」에 따른 (개인)회생절차
+라. 「서민의 금융생활 지원에 관한 법률」에 따른 신용회복위원회 채무조정 절차
+3. 기타 소멸시효를 완성시키는 것이 채무자에 대한 도덕적 해이가 발생할 우려가 있거나 사회통념에 비추어 부적절하다고 인정되는 경우
+4. (비공개)
+5. (비공개)
+6. (비공개)
+7. (비공개)</t>
   </si>
   <si>
     <t>제51조</t>
@@ -2579,25 +2572,38 @@
     <t>시효중단조치 제외대상</t>
   </si>
   <si>
-    <t xml:space="preserve">① 시효가 도래한 대상채권의 채무관계자가 다음 각 호의 어느 하나에 해당되어 채권회수의 실익이 없는 것으로 인정되는 경우에는 시효중단조치를 하지 아니할 수 있다.
-1. 주채무자가 60세 이상으로 원금잔액이 5백만원 이하이고, 보증인이 없는 경우
-2. 주채무자가 60세 이상으로 원금잔액이 5백만원 이하이고, 보증인이 있는 경우로써 보증인이 사망한 후 피상속인 소유의 회수실익이 있는 발견재산이 없는 경우
-3. 보증인이 없는 주채무자가 사망한 경우로써 피상속인 소유의 회수실익이 있는 발견재산이 없는 경우
-4. 보증인이 있는 주채무자가 사망한 경우로써 피상속인 및 보증인 소유의 회수실익이 있는 발견재산이 없는 경우
-5. 보증인이 사망한 경우로써 피상속인 소유의 회수실익 있는 발견재산이 없는 경우
+    <t xml:space="preserve">① 시효가 도래한 대상채권의 채무관계자가 다음 각 호의 어느 하나에 해당하는 경우에는 시효도래횟수에 관계없이 시효중단조치를 하지 않을 수 있다.(2026.6.29. 본항개정)
+1. 채무관계자가 「국민기초생활보장법」제2조에 따른 수급자인 경우(2025.06.29. 본호개정)
+2. 채무관계자가 「장애인연금법」제2조에 따른 수급자인 경우(2025.06.29. 본호개정)
+3. 채무관계자가 「한부모가족지원법」제12조에 따라 복지급여를 받고 있는 한부모가족인 경우(2025.06.29. 본호개정)
+4. 채무관계자가 국가유공자·독립유공자·보훈보상대상자·5·18민주유공자·고엽제후유의증 등 환자·참전유공자·특수임무유공자 등 국가보훈부에서 생계지원금 또는 생활조정수당을 지급받고 있는 사람인 경우(2025.06.29. 본호개정)
+5. 채무관계자가 「국민기초생활보장법」제2조에 따른 차상위계층인 경우(2025.06.29. 본호개정)
 6. 채무관계자의 총 채무원금 잔액이 2백만원 이하인 경우(2024.12.30. 본호개정)
 6의2. 무담보채무 중 시효가 1년 내 도래하는 모든 개별 채무의 원금 및 가지급금 잔액의 합계가 1백만원 미만인 경우 해당 채무(2025.5.29. 본호신설, 2025.9.19. 본호개정)
 6의3. 무담보채무 중 해당 개별 채무의 원금 및 가지급금 잔액이 0인 경우(2025.5.29. 본호신설, 2025.9.19. 본호개정)
-7. 「국민기초생활 보장법」 제2조제2호에 따른 수급자 중 생계급여, 주거급여, 의료급여, 교육급여 수급자
-8. 「국민기초생활 보장법」제2조제10호에 따른 차상위계층이고, 회수가능재산이 없는 경우
-9. 「장애인연금법」 제2조제3호에 따른 장애인연금의 수급권자
+7. (2026.6.29. 본호삭제)
+8. (2026.6.29. 본호삭제)
+9. (2026.6.29. 본호삭제)
 10. 주채무자가 70세 이상이고, 회수가능재산이 없는 경우
 11. 채권원인서류의 부존재 등 기타 사유로 소송의 진행이 불가능한 경우
 12. 그 밖에 시효연장 실익이 없다고 판단되는 경우
-② 제1항에도 불구하고 제1항제8호의 경우에는 수급자 자격을 상실할 경우에는 시효중단조치를 하여야 한다. 다만, 채권금융회사에서 신청하여 진행 중인 소송은 다음 각 호의 기준에 따른다.
-1. 시효연장을 위한 대여금 청구소송 등은 소송승계 참가를 포기
-2. 배당금(공탁금) 및 추심금 수령을 위한 본안소송 등은 소송승계 참가
+② (비공개)
 ③ 제1항에도 불구하고 채권회수의 실익이 있는 것으로 판단되는 경우에는 시효중단조치를 할 수 있다.</t>
+  </si>
+  <si>
+    <t>제53조의2</t>
+  </si>
+  <si>
+    <t>상환능력심사</t>
+  </si>
+  <si>
+    <t>(비공개)</t>
+  </si>
+  <si>
+    <t>제53조의3</t>
+  </si>
+  <si>
+    <t>상환능력심사 자료</t>
   </si>
   <si>
     <t>제54조</t>
@@ -2618,7 +2624,7 @@
   </si>
   <si>
     <t xml:space="preserve">① 주무부점의 장은 시효관리대상채권 중 지급명령의 신청을 하지 않았거나 지급명령을 신청하였으나 송달불능 또는 이의신청이 있는 채권은 시효중단을 위한 소송을 제기하여야 한다.
-② 제1항에도 불구하고 채무관계자에게 회수가능재산이 없고, 월평균소득이 「국민기초생활 보장법」 제2조제11호에 따른 기준 중위소득의 100분의60 이하임이 확인된 경우 시효중단을 위한 소송은 양도자산확정일 이후 1회에 한한다.</t>
+② (2026.6.29. 본항삭제)</t>
   </si>
   <si>
     <t>제56조</t>
@@ -2664,7 +2670,7 @@
 1. 보전조치 대상 재산의 회수가능성이 있는 경우(2025.9.19. 본호신설)
 가. 부동산 등 유형재산에 대한 가압류·가처분 : 해당 재산의 회수가능액(제2호가목 단서의 승용자동차를 제외한 차량의 경우 감정평가액 또는 시가를 회수가능액으로 산정한다) 이상을 변제하는 경우
 나. 채권에 대한 (가)압류 : 제3채무자 적립금액과 법원공탁금액의 회수가능액의 합계금액 또는 해당 재산의 회수가능액을 변제하는 경우. 다만, 회수가능액의 합계금액 또는 해당 재산의 회수가능액이 500만원 이하인 경우 변제없이 취하하고, 500만원을 초과하는 경우 회수가능액 합계금액에서 500만원을 차감한 금액을 변제(2026.3.25. 본목개정)
-다. 이미 보전조치된 발견재산이 아닌 새로운 발견재산에 대한 담보권 설정 등 채무부담액 또는 회수가능액 이상의 실익 있는 대체 담보 제공이 있는 경우
+다. 이미 보전조치된 발견재산 또는 새로운 발견재산에 대한 담보권 설정 등 채무부담액 또는 해당 재산의 회수가능액 이상의 실익 있는 대체 담보 제공이 있는 경우(2026.6.29. 본목개정)
 2. 보전조치 대상 재산의 회수가능성이 없는 경우(2025.9.19. 본호신설)
 가. 부동산 등 유형재산에 대한 가압류·가처분 : 채무관계자가 채무부담액의 10% 이상을 변제하는 경우. 다만, 해당 재산이 멸실 등으로 채권보전조치를 할 수 없거나 「재산조사업무요강」 [별표4]에 따라 재산평가액 산정에서 제외되는 자동차의 경우 변제 없이 취하(2026.3.25. 본목개정)
 나. 채권에 대한 (가)압류 : 「민사집행법 시행령」 제7조에 따른 압류금지 예금 등의 금액범위 이하인 경우 변제없이 취하
@@ -2681,8 +2687,8 @@
   <si>
     <t xml:space="preserve">① 강제집행 절차가 진행 중인 채무관계자가 분할상환을 요청하는 경우 다음 각 호의 어느 하나에 해당하는 조치를 하고 강제집행을 취하할 수 있다.
 1. 강제집행비용과 회수가능액의 합계금액을 일시에 변제한 경우
-2. 채권금융회사가 신청한 강제집행의 경우 채무관계자가 제17조에 따라 채무조정 약정을 체결하고, 압류의 순위보전여부 등을 검토하여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 근저당권 설정금액이 5백만원 미만인 경우에는 근저당권 설정을 아니 할 수 있다.(2026.3.25. 본호개정)
-3. 새출발기금이 신청한 강제집행의 경우 압류의 순위보전 여부 등을 검토하여 강제집행비용과 채무부담액의 10% 이상을 상환받은 후 잔여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 근저당권 설정금액이 5백만원 미만인 경우에는 근저당권 설정을 아니할수 있다.(2026.3.25. 본호신설)
+2. 채권금융회사가 신청한 강제집행의 경우 채무관계자가 제17조에 따라 채무조정 약정을 체결하고, 압류의 순위보전여부 등을 검토하여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 해당 부동산의 회수가능액 또는 채무부담액이 5백만원 미만인 경우에는 근저당권을 설정하지 않을 수 있다.(2026.3.25., 2026.6.29. 본호개정)
+3. 새출발기금이 신청한 강제집행의 경우 채무관계자가 제17조에 따라 채무조정 약정을 체결하고, 압류의 순위보전 여부 등을 검토하여 강제집행비용과 채무부담액의 10% 이상을 상환받은 후 잔여 채무부담액과 해당 부동산의 회수가능액 중 적은 금액의 120%를 채권최고액으로 한 근저당권을 설정한 경우. 다만, 해당 부동산의 회수가능액 또는 채무부담액이 5백만원 미만인 경우에는 근저당권을 설정하지 않을 수 있다.(2026.3.25. 본호신설, 2026.6.29. 본호개정)
 ② 제1항에 따라 저당권을 설정 또는 해지하는 경우 그에 필요한 비용은 새출발기금의 부담으로 한다. 다만, 채무관계자가 채무조정약정에 따른 채무조정의 효력을 상실하는 경우에는 채무관계자에게 비용을 청구하여야 한다.(2024.12.30. 본항개정)
 [2024.9.11. 본조신설]</t>
   </si>
@@ -3855,15 +3861,15 @@
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -3878,22 +3884,22 @@
         <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>49</v>
@@ -3913,13 +3919,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>19</v>
@@ -3931,28 +3937,28 @@
         <v>19</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>49</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>83</v>
@@ -3966,10 +3972,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>19</v>
@@ -3978,7 +3984,7 @@
         <v>19</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>19</v>
@@ -3987,22 +3993,22 @@
         <v>52</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>28</v>
@@ -4019,10 +4025,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>19</v>
@@ -4031,7 +4037,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
@@ -4040,25 +4046,25 @@
         <v>67</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>83</v>
@@ -4072,10 +4078,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -4093,28 +4099,28 @@
         <v>43</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>74</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>30</v>
@@ -4125,10 +4131,10 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>19</v>
@@ -4146,28 +4152,28 @@
         <v>43</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>30</v>
@@ -4178,10 +4184,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>19</v>
@@ -4199,28 +4205,28 @@
         <v>67</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>30</v>
@@ -4231,10 +4237,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>19</v>
@@ -4252,28 +4258,28 @@
         <v>67</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>30</v>
@@ -4284,16 +4290,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
@@ -4305,28 +4311,28 @@
         <v>67</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>30</v>
@@ -4337,10 +4343,10 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -4349,7 +4355,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>19</v>
@@ -4358,28 +4364,28 @@
         <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>30</v>
@@ -4390,10 +4396,10 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -4402,7 +4408,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
@@ -4411,28 +4417,28 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>30</v>
@@ -4443,10 +4449,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
@@ -4464,48 +4470,48 @@
         <v>52</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>19</v>
@@ -4514,31 +4520,31 @@
         <v>19</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>30</v>
@@ -4549,10 +4555,10 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
@@ -4567,22 +4573,22 @@
         <v>19</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>49</v>
@@ -4591,7 +4597,7 @@
         <v>28</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>30</v>
@@ -4602,49 +4608,49 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>30</v>
@@ -4655,10 +4661,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>19</v>
@@ -4667,37 +4673,37 @@
         <v>19</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>30</v>
@@ -4708,49 +4714,49 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>30</v>
@@ -4761,10 +4767,10 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -4773,7 +4779,7 @@
         <v>19</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>19</v>
@@ -4782,19 +4788,19 @@
         <v>43</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>49</v>
@@ -4803,7 +4809,7 @@
         <v>49</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>30</v>
@@ -4814,10 +4820,10 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -4835,25 +4841,25 @@
         <v>67</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>29</v>
@@ -4862,7 +4868,7 @@
         <v>30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -4879,7 +4885,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>19</v>
@@ -4915,7 +4921,7 @@
         <v>30</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -4968,7 +4974,7 @@
         <v>30</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5021,7 +5027,7 @@
         <v>30</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5074,7 +5080,7 @@
         <v>30</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5091,7 +5097,7 @@
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>19</v>
@@ -5127,7 +5133,7 @@
         <v>30</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5144,7 +5150,7 @@
         <v>19</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>19</v>
@@ -5180,7 +5186,7 @@
         <v>30</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5227,13 +5233,13 @@
         <v>347</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5280,13 +5286,13 @@
         <v>49</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5333,13 +5339,13 @@
         <v>49</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5386,13 +5392,13 @@
         <v>49</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -5409,13 +5415,13 @@
         <v>19</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>373</v>
@@ -5439,13 +5445,13 @@
         <v>49</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5462,7 +5468,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>19</v>
@@ -5492,13 +5498,13 @@
         <v>49</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -5515,7 +5521,7 @@
         <v>19</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>19</v>
@@ -5551,7 +5557,7 @@
         <v>30</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -5568,7 +5574,7 @@
         <v>19</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>19</v>
@@ -5604,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -5621,7 +5627,7 @@
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>19</v>
@@ -5657,7 +5663,7 @@
         <v>30</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -5674,7 +5680,7 @@
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>19</v>
@@ -5710,7 +5716,7 @@
         <v>30</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -5733,7 +5739,7 @@
         <v>19</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>427</v>
@@ -5763,7 +5769,7 @@
         <v>30</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -5780,13 +5786,13 @@
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>436</v>
@@ -5816,7 +5822,7 @@
         <v>30</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -5833,7 +5839,7 @@
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>19</v>
@@ -5869,7 +5875,7 @@
         <v>30</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -5892,7 +5898,7 @@
         <v>19</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>453</v>
@@ -5922,7 +5928,7 @@
         <v>30</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -6012,7 +6018,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6107,6 +6113,14 @@
         <v>486</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>487</v>
+      </c>
+      <c r="B12" t="s">
+        <v>488</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -6115,7 +6129,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6129,16 +6143,16 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>14</v>
@@ -6152,1612 +6166,1612 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E3" t="s">
         <v>497</v>
       </c>
-      <c r="C3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="E3" t="s">
-        <v>495</v>
-      </c>
       <c r="F3" t="s">
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F4" t="s">
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B8" t="s">
+        <v>515</v>
+      </c>
+      <c r="C8" t="s">
         <v>512</v>
       </c>
-      <c r="B8" t="s">
-        <v>513</v>
-      </c>
-      <c r="C8" t="s">
-        <v>510</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B9" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C10" t="s">
         <v>519</v>
       </c>
-      <c r="B10" t="s">
-        <v>520</v>
-      </c>
-      <c r="C10" t="s">
-        <v>517</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B11" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E11" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C12" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E12" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B13" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C13" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E13" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B14" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E14" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B15" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C15" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>540</v>
+      </c>
+      <c r="B16" t="s">
+        <v>541</v>
+      </c>
+      <c r="C16" t="s">
         <v>538</v>
       </c>
-      <c r="B16" t="s">
-        <v>539</v>
-      </c>
-      <c r="C16" t="s">
-        <v>536</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E16" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B17" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C17" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B18" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C18" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E18" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B19" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C19" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E19" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B20" t="s">
         <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E20" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B21" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C21" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E21" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B22" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C22" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E22" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B23" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C23" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B24" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C24" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E24" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>567</v>
+      </c>
+      <c r="B25" t="s">
+        <v>568</v>
+      </c>
+      <c r="C25" t="s">
         <v>565</v>
       </c>
-      <c r="B25" t="s">
-        <v>566</v>
-      </c>
-      <c r="C25" t="s">
-        <v>563</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B26" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C26" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E26" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B27" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C27" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E27" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B28" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C28" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E28" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B29" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C29" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E29" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B30" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C30" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E30" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F30" t="s">
         <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B31" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F31" t="s">
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B32" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C32" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E32" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B33" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E33" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F33" t="s">
         <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B34" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C34" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E34" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B35" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C35" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E35" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B36" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C36" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E36" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B37" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C37" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E37" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B38" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C38" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E38" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>610</v>
+      </c>
+      <c r="B39" t="s">
+        <v>611</v>
+      </c>
+      <c r="C39" t="s">
         <v>608</v>
       </c>
-      <c r="B39" t="s">
-        <v>609</v>
-      </c>
-      <c r="C39" t="s">
-        <v>606</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E39" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F39" t="s">
         <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B40" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C40" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E40" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B41" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C41" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E41" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F41" t="s">
         <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B42" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C42" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E42" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F42" t="s">
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B43" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C43" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E43" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B44" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C44" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E44" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F44" t="s">
         <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B45" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C45" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E45" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B46" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C46" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E46" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B47" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C47" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E47" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B48" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C48" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E48" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B49" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C49" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E49" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B50" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C50" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E50" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B51" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C51" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E51" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B52" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C52" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E52" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B53" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C53" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E53" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B54" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C54" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E54" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B55" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C55" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E55" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B56" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C56" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E56" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B57" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C57" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E57" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B58" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C58" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E58" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F58" t="s">
         <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>671</v>
+      </c>
+      <c r="B59" t="s">
+        <v>672</v>
+      </c>
+      <c r="C59" t="s">
         <v>669</v>
       </c>
-      <c r="B59" t="s">
-        <v>670</v>
-      </c>
-      <c r="C59" t="s">
-        <v>667</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E59" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B60" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C60" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E60" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B61" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C61" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E61" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B62" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C62" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E62" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B63" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C63" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E63" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B64" t="s">
+        <v>687</v>
+      </c>
+      <c r="C64" t="s">
+        <v>669</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="C64" t="s">
-        <v>667</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>686</v>
-      </c>
       <c r="E64" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B65" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C65" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E65" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B66" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C66" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E66" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B67" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C67" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E67" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B68" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C68" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E68" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B69" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C69" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E69" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B70" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C70" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E70" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B71" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C71" t="s">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>708</v>
       </c>
       <c r="E71" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -7768,19 +7782,19 @@
         <v>710</v>
       </c>
       <c r="C72" t="s">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>711</v>
       </c>
       <c r="E72" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -7791,42 +7805,88 @@
         <v>713</v>
       </c>
       <c r="C73" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E73" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B74" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C74" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>718</v>
       </c>
       <c r="E74" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>291</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>719</v>
+      </c>
+      <c r="B75" t="s">
+        <v>720</v>
+      </c>
+      <c r="C75" t="s">
+        <v>714</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="E75" t="s">
+        <v>497</v>
+      </c>
+      <c r="F75" t="s">
+        <v>30</v>
+      </c>
+      <c r="G75" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>722</v>
+      </c>
+      <c r="B76" t="s">
+        <v>723</v>
+      </c>
+      <c r="C76" t="s">
+        <v>724</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="E76" t="s">
+        <v>497</v>
+      </c>
+      <c r="F76" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="736">
   <si>
     <t>번호</t>
   </si>
@@ -1635,6 +1635,52 @@
     <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>재산가액, 재산가치, 재산 평가, 재산 산정, 회수가능액, 유효담보가액, 회수가능재산, 순부채, 채무부담액, 채무부담액 산정, 산정, 감면 계산</t>
+  </si>
+  <si>
+    <t>[규정] 재산가액(회수가능액)과 채무부담액은 어떻게 산정하나요?</t>
+  </si>
+  <si>
+    <t>채무관계자가 가진 재산은 회수가능액(유효담보가액)으로 따지며, 요강 별표 2 기준으로 산정하는데 이 산정기준은 공개되지 않는다. 부실우려차주는 원금·기발생이자·경과이자·가지급금을 합산해 채무부담액을 정하고(무담보채권은 연체이자 전액 감면), 부실차주는 별표 3 기준(비공개)으로 정한다. 사회취약계층도 재산이 있으면 대상채무액에서 회수가능액을 뺀 나머지에만 감면율을 적용한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제2조(정의)
+이 요강에서 사용하는 용어의 뜻은 다음과 같다. 다만, 이 요강에서 정의되지 않은 용어의 정의는 「소상공인·자영업자 새출발기금 지원 협약」(이하 “협약”이라 한다)에 따른다.
+33. “회수가능재산”이란 새출발기금이 대상채권의 채무관계자로부터 회수할 수 있는 재산을 말한다.
+34. “유효담보가액” 또는 “회수가능액”이란 별표 2의 “유효담보가액 및 회수가능액 산정기준”에 따라 산정한 금액을 말한다.
+제19조(채무부담액의 산정)
+① 부실우려차주 및 그 채무관계자는 원금, 기발생이자, 경과이자, 가지급금을 합산하여 채무부담액으로 산정하되, 기발생이자는 채무유형에 따라 다음 각 호의 기준을 적용한다. 단, 최초약정에 한하여 경과이자를 제외한 금액으로 채무부담액을 산정한다.(2024.9.11. 단서신설)
+1. 무담보채권 : 각 채권금융회사의 연체이자를 전액 감면
+2. 담보부채권 : 채무부담액에서 가지급금을 제외한 금액이 유효담보가액을 초과하는 경우 초과하는 범위에서 각 채권금융회사의 연체이자를 감면
+② 부실차주 및 그 채무관계자의 채무부담액은 별표 3의 부실차주의 채무유형별 채무부담액 산정기준에 따라 산정한다.
+③ 제1항의 부실우려차주 및 그 채무관계자가 3개월 이상 연체 등으로 채무조정약정의 효력이 상실되거나, 협약 제16조 제1항의 신용회복지원협약에서 정하는 사유에 따라 중개형 채무조정약정의 효력이 상실되는 경우 해당 부실우려차주에 대하여 협약 제10조 내지 제13조에서 정한 매입형 채무조정을 실시하며, 채무부담액은 별표 3 부실차주의 채무유형별 채무부담액 산정기준에 따라 산정한다.(2024.9.11. 본항신설)
+④ 본 조 차주에 대한 채무부담액 산정 시 제비용 전액을 채무부담액에 포함한다. 다만, 제비용 중 소송비용은 해당 채무관계자의 소송비용에 채무감면율을 적용한 금액을 채무부담액으로 한다.(2024.9.11. 본항신설, 2024.12.30. 본항개정)
+⑤ 제5조의3에 따라 장래 이자채권을 면제한 개인금융채권에 대해서는 채무조정 시 채무부담액에 경과이자를 부과하지 않는다.(2025.5.29. 본항신설)
+제20조(사회취약계층 감면)
+① 사회취약계층이 채무조정을 신청하는 경우에는 해당기준 부합여부의 확인 후에 별표 1의 사회취약계층 감면표에서 정하는 채무감면율을 적용한다. 다만, 사회취약계층이 재산을 소유한 경우에는 대상채무액에서 회수가능액을 차감한 후에 잔여 대상채무액에 대하여만 감면율을 적용한다.(2025.5.29. 본항개정)
+② 부실차주가 채무조정 약정 이후 사회취약계층(별표 1 소급적용 대상에 한정한다)에 해당하게 된 경우에는 별지 제39호서식 사회취약계층 감면율 소급 신청서를 제출받아 제1항에 따라 감면율을 소급하여 적용할 수 있다.(2025.5.29. 본항신설, 2026.1.20. 본항개정)</t>
+  </si>
+  <si>
+    <t>관리업무요강 제2조 제33·34호: 회수가능재산은 새출발기금이 회수할 수 있는 재산, 회수가능액(유효담보가액)은 별표 2 산정기준(비공개)으로 산정 / 관리업무요강 제19조: 부실우려차주는 원금·기발생이자·경과이자·가지급금을 합산(무담보채권 연체이자 전액 감면), 부실차주는 별표 3 기준(비공개)으로 채무부담액 산정 / 관리업무요강 제20조①: 사회취약계층이 재산을 가지면 대상채무액에서 회수가능액을 뺀 나머지에만 감면율 적용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재산은 회수가능액으로 따집니다(제2조)
+재산 가치를 뺀 나머지에 감면돼요(제20조)
+세부 산정기준표는 공개되지 않아요.</t>
+  </si>
+  <si>
+    <t>재산은 감면 계산과 상관없어요</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>새출발기금 위탁채권 관리업무요강 제2조(정의), 제19조(채무부담액의 산정), 제20조(사회취약계층 감면) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
+  </si>
+  <si>
     <t>버튼</t>
   </si>
   <si>
@@ -1677,7 +1723,7 @@
     <t>자료 출처</t>
   </si>
   <si>
-    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인) / 044~051은 「새출발기금 위탁채권 관리업무요강」(2026.6.29. 시행 공개본) 조문 기반 자료로, 제목 앞에 [규정]을 붙이고 "FAQ 원문" 칸에 조문을 그대로 옮겼다(2026-10-29).</t>
+    <t>새출발기금(한국자산관리공사) 공식 홈페이지 공개 FAQ 43건 전부 (https://www.newstartfund.or.kr/Faq/List.do, 001~030은 2026-10-28, 031~043은 2026-10-29 확인) / 044~052는 「새출발기금 위탁채권 관리업무요강」(2026.6.29. 시행 공개본) 조문 기반 자료로, 제목 앞에 [규정]을 붙이고 "FAQ 원문" 칸에 조문을 그대로 옮겼다(2026-10-29).</t>
   </si>
   <si>
     <t>홈페이지에 게시된 답변을 그대로 옮긴 칸. 근거 정확도 확인은 이 칸과 대조한다.</t>
@@ -3156,7 +3202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -5931,6 +5977,59 @@
         <v>126</v>
       </c>
     </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -5948,10 +6047,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -5959,7 +6058,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5967,7 +6066,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5975,7 +6074,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5983,7 +6082,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5991,23 +6090,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -6027,18 +6126,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6046,7 +6145,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6054,7 +6153,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6062,15 +6161,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6078,15 +6177,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6094,15 +6193,15 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="B10" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6110,15 +6209,15 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="B12" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -6143,16 +6242,16 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>14</v>
@@ -6166,19 +6265,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B2" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C2" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="E2" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
@@ -6189,19 +6288,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="B3" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="C3" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="E3" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
@@ -6212,19 +6311,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="C4" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F4" t="s">
         <v>30</v>
@@ -6235,19 +6334,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="B5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C5" t="s">
         <v>505</v>
       </c>
-      <c r="C5" t="s">
-        <v>495</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="E5" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -6258,19 +6357,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C6" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E6" t="s">
         <v>507</v>
-      </c>
-      <c r="B6" t="s">
-        <v>508</v>
-      </c>
-      <c r="C6" t="s">
-        <v>495</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="E6" t="s">
-        <v>497</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -6281,19 +6380,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B7" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="C7" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="E7" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -6304,19 +6403,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="B8" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="E8" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
@@ -6327,19 +6426,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="B9" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="C9" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="E9" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
@@ -6350,19 +6449,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B10" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="C10" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="E10" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
@@ -6373,19 +6472,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="B11" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="C11" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="E11" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -6396,19 +6495,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="B12" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C12" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="E12" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
@@ -6419,19 +6518,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="B13" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="C13" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="E13" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
@@ -6442,19 +6541,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B14" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="C14" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="E14" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
@@ -6465,19 +6564,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="B15" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="C15" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="E15" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
@@ -6488,19 +6587,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B16" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="E16" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
@@ -6511,19 +6610,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="B17" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="C17" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="E17" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -6534,19 +6633,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="B18" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="C18" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E18" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
@@ -6557,19 +6656,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B19" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C19" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="E19" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
@@ -6580,19 +6679,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="B20" t="s">
         <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="E20" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
@@ -6603,19 +6702,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="B21" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C21" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="E21" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
@@ -6626,19 +6725,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="B22" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="C22" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E22" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
@@ -6649,19 +6748,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="B23" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="C23" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
@@ -6672,19 +6771,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B24" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C24" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="E24" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
@@ -6695,19 +6794,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B25" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="C25" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="E25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
@@ -6718,19 +6817,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B26" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="C26" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="E26" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
@@ -6741,19 +6840,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="B27" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="C27" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="E27" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
@@ -6764,19 +6863,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="B28" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="C28" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="E28" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
@@ -6787,19 +6886,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="B29" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="C29" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="E29" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
@@ -6810,19 +6909,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="B30" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="C30" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="E30" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F30" t="s">
         <v>30</v>
@@ -6833,19 +6932,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="B31" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="C31" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="E31" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F31" t="s">
         <v>30</v>
@@ -6856,19 +6955,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="B32" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="C32" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
@@ -6879,19 +6978,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B33" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="C33" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="E33" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F33" t="s">
         <v>30</v>
@@ -6902,19 +7001,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="B34" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C34" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="E34" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
@@ -6925,19 +7024,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="B35" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="C35" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="E35" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
@@ -6948,19 +7047,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="B36" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="C36" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="E36" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
@@ -6971,19 +7070,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="B37" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="C37" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="E37" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
@@ -6994,19 +7093,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="B38" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="C38" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="E38" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
@@ -7017,19 +7116,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="B39" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="C39" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="E39" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F39" t="s">
         <v>30</v>
@@ -7040,19 +7139,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="B40" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="C40" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="E40" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
@@ -7063,19 +7162,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="B41" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="C41" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="E41" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F41" t="s">
         <v>30</v>
@@ -7086,19 +7185,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="B42" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="C42" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="E42" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F42" t="s">
         <v>30</v>
@@ -7109,19 +7208,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="B43" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="C43" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="E43" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
@@ -7132,19 +7231,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="B44" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="C44" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="E44" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F44" t="s">
         <v>30</v>
@@ -7155,19 +7254,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="B45" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="C45" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="E45" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
@@ -7178,19 +7277,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="B46" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="C46" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="E46" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
@@ -7201,19 +7300,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="B47" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="C47" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="E47" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
@@ -7224,19 +7323,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="B48" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="C48" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="E48" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
@@ -7247,19 +7346,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="B49" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="C49" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="E49" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
@@ -7270,19 +7369,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="B50" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="C50" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="E50" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
@@ -7293,19 +7392,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="B51" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="C51" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="E51" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
@@ -7316,19 +7415,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="B52" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="C52" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="E52" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
@@ -7339,19 +7438,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="B53" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="C53" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="E53" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
@@ -7362,19 +7461,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="B54" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="C54" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="E54" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
@@ -7385,19 +7484,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="B55" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="C55" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="E55" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
@@ -7408,19 +7507,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="B56" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="C56" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="E56" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
@@ -7431,19 +7530,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="B57" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C57" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="E57" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
@@ -7454,19 +7553,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="B58" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="C58" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="E58" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F58" t="s">
         <v>30</v>
@@ -7477,19 +7576,19 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="B59" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="C59" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="E59" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
@@ -7500,19 +7599,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="B60" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="C60" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="E60" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
@@ -7523,19 +7622,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="B61" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="C61" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="E61" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
@@ -7546,19 +7645,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="B62" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="C62" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="E62" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -7569,19 +7668,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="B63" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="C63" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="E63" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -7592,19 +7691,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="B64" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="C64" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="E64" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
@@ -7615,19 +7714,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="B65" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="C65" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="E65" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
@@ -7638,19 +7737,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="B66" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="C66" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="E66" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
@@ -7661,19 +7760,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="B67" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="C67" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="E67" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
@@ -7684,19 +7783,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="B68" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="C68" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="E68" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
@@ -7707,19 +7806,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="B69" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="C69" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="E69" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
@@ -7730,19 +7829,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B70" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="C70" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="E70" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
@@ -7753,19 +7852,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B71" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="C71" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="E71" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
@@ -7776,19 +7875,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="B72" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="C72" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="E72" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
@@ -7799,19 +7898,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B73" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="C73" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="E73" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
@@ -7822,19 +7921,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="B74" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="C74" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="E74" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
@@ -7845,19 +7944,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="B75" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="C75" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="E75" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F75" t="s">
         <v>30</v>
@@ -7868,19 +7967,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="B76" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
       <c r="C76" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="E76" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F76" t="s">
         <v>30</v>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="753">
   <si>
     <t>번호</t>
   </si>
@@ -176,7 +176,7 @@
 폐업·휴업도 부실우려차주일 수 있어요.</t>
   </si>
   <si>
-    <t>-</t>
+    <t>10일만 연체돼도 부실차주예요</t>
   </si>
   <si>
     <t>004</t>
@@ -199,6 +199,9 @@
 ㅇ 또한 채무조정 약정 후 부실차주에 대하여는 연체정보를 삭제하고 공공정보를 등록(1년간 성실상환 시 해제)함을 안내드립니다.</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t xml:space="preserve">신청 후 예·적금이 상계될 수 있어요.
 카드 이용이 정지될 수 있습니다.
 1년 성실상환하면 공공정보가 해제돼요.</t>
@@ -230,6 +233,9 @@
     <t xml:space="preserve">소상공인·자영업자 전용 제도입니다.
 무담보 10년, 담보 20년까지 갚아요.
 약정 후 회생 신청 시 효력 상실(제32조)</t>
+  </si>
+  <si>
+    <t>개인회생이나 신복위와 똑같은 제도예요</t>
   </si>
   <si>
     <t>006</t>
@@ -291,6 +297,9 @@
 담보대출은 신복위 방문 접수입니다.</t>
   </si>
   <si>
+    <t>모든 대출을 홈페이지에서 한 번에 신청하시면 돼요</t>
+  </si>
+  <si>
     <t>캠코 상담 창구 / 신용회복위원회 서민금융통합지원센터</t>
   </si>
   <si>
@@ -318,6 +327,9 @@
   <si>
     <t xml:space="preserve">신용·보증대출은 캠코 매입형입니다.
 담보대출은 신복위 중개형입니다.</t>
+  </si>
+  <si>
+    <t>모든 대출은 캠코에서 직접 조정해 드려요</t>
   </si>
   <si>
     <t>캠코(매입형) / 신용회복위원회(중개형)</t>
@@ -404,6 +416,9 @@
 신청 단계면 취소 후 신청할 수 있어요.</t>
   </si>
   <si>
+    <t>개인회생 중이셔도 그냥 새출발기금 신청하시면 돼요</t>
+  </si>
+  <si>
     <t>신용회복위원회, 법원</t>
   </si>
   <si>
@@ -464,6 +479,9 @@
 잘못 입력한 건 본 약정 때 고치면 돼요.</t>
   </si>
   <si>
+    <t>잘못 입력하셨으면 처음부터 다시 신청하셔야 해요</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
@@ -488,6 +506,9 @@
   <si>
     <t xml:space="preserve">홈페이지 이의신청으로 접수해 주세요.
 부채증명원 등 증빙을 첨부해 주세요.</t>
+  </si>
+  <si>
+    <t>전산에 연체정보가 없으면 신청할 방법이 없어요</t>
   </si>
   <si>
     <t>새출발기금 홈페이지 이의신청</t>
@@ -551,6 +572,9 @@
     <t xml:space="preserve">실효되면 기금이 채권을 매입합니다.
 빠진 대출도 추가로 신청할 수 있어요.
 고객센터로 미신청 채무를 신청하세요.</t>
+  </si>
+  <si>
+    <t>처음에 신청 안 한 대출은 이제 넣을 수 없어요</t>
   </si>
   <si>
     <t>새출발기금 고객센터 1660-1378</t>
@@ -760,6 +784,9 @@
 반복·야간 추심은 금지입니다.(제47조)</t>
   </si>
   <si>
+    <t>신청만 하면 모든 추심이 바로 멈춰요</t>
+  </si>
+  <si>
     <t>해당 금융기관 → 새출발기금 1660-1378</t>
   </si>
   <si>
@@ -857,6 +884,9 @@
 상환기간은 최대 20년까지 가능해요.</t>
   </si>
   <si>
+    <t>취약계층이면 빚을 전부 탕감받으세요</t>
+  </si>
+  <si>
     <t>027</t>
   </si>
   <si>
@@ -975,6 +1005,9 @@
 고의 연체는 신청이 거절됩니다.</t>
   </si>
   <si>
+    <t>심사는 일부만 받으니 걱정 안 하셔도 돼요</t>
+  </si>
+  <si>
     <t>새출발기금 홈페이지 자주하는 질문 &gt; 도덕적해이 (https://www.newstartfund.or.kr/Faq/List.do)</t>
   </si>
   <si>
@@ -1066,6 +1099,9 @@
     <t>새출발기금이 무조건 더 유리합니다</t>
   </si>
   <si>
+    <t>법원(개인회생 사건) / 새출발기금 콜센터 1660-1378</t>
+  </si>
+  <si>
     <t>034</t>
   </si>
   <si>
@@ -1162,6 +1198,12 @@
   <si>
     <t xml:space="preserve">대출과 연체정보가 함께 보여 그래요.
 약정 때 대상 채무를 확인할 수 있어요.</t>
+  </si>
+  <si>
+    <t>중복으로 나온 건 빚이 두 배라는 뜻이에요</t>
+  </si>
+  <si>
+    <t>해당 금융기관 → 새출발기금 콜센터 1660-1378</t>
   </si>
   <si>
     <t>038</t>
@@ -1241,6 +1283,9 @@
   <si>
     <t xml:space="preserve">부실차주 신용·보증은 매입형입니다.
 담보·부실우려 채무는 중개형입니다.</t>
+  </si>
+  <si>
+    <t>어떤 대출이든 조정 방식은 다 똑같아요</t>
   </si>
   <si>
     <t>041</t>
@@ -1595,6 +1640,9 @@
 정보 이용 동의서도 함께 받습니다.(제12조)</t>
   </si>
   <si>
+    <t>신분증만 있으면 다른 서류는 필요 없어요</t>
+  </si>
+  <si>
     <t>새출발기금 위탁채권 관리업무요강 제12조(채무조정의 신청서류) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
@@ -1630,6 +1678,9 @@
   </si>
   <si>
     <t>가족이면 위임장 없이 대신 신청돼요</t>
+  </si>
+  <si>
+    <t>새출발기금 상담창구 / 새출발기금 콜센터 1660-1378</t>
   </si>
   <si>
     <t>새출발기금 위탁채권 관리업무요강 제11조(채무조정의 신청) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
@@ -1675,9 +1726,6 @@
     <t>재산은 감면 계산과 상관없어요</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>새출발기금 위탁채권 관리업무요강 제2조(정의), 제19조(채무부담액의 산정), 제20조(사회취약계층 감면) — 2026.6.29. 시행본 기준, 캠코 정보공개 &gt; 현행내규 (https://www.kamco.or.kr/portal/bbs/view.do?bIdx=27867&amp;ptIdx=270&amp;mId=0601070100)</t>
   </si>
   <si>
@@ -1732,7 +1780,7 @@
     <t>FAQ 원문을 2~3문장으로 줄인 칸. 원문에 없는 내용은 넣지 않았다.</t>
   </si>
   <si>
-    <t>FAQ 원문 내용과 어긋나는 안내를 예시로 적은 초안. 실제 사용 전 담당자 검토가 필요하다.</t>
+    <t>FAQ 원문·답변 요약과 어긋나는 안내를 예시로 적은 초안. 모든 줄에 채우고 카드에 늘 보여 준다(2026-10-29). 실제 사용 전 담당자 검토가 필요하다.</t>
   </si>
   <si>
     <t>버튼 기준</t>
@@ -1766,6 +1814,9 @@
   </si>
   <si>
     <t>요강 공개본에서 '(비공개)'로 가려진 부분(제11조②, 제50조⑤ 제4~7호, 제53조②, 제53조의2·제53조의3, 별표 1~4, 별표 11, 별지 제42호서식)은 내용을 넣지 않고 '(비공개)' 표시만 그대로 둔다. 예전 3.25본에서 가져온 제11조②(순자산 기준) 내용은 2026-10-29에 뺐다.</t>
+  </si>
+  <si>
+    <t>민원인을 안내할 담당 창구. 모든 줄에 채운다. 원문에 기관이 나오면 그 기관을, 없으면 새출발기금 콜센터를 적었다(2026-10-29 초안, 담당자 검토 필요).</t>
   </si>
   <si>
     <t>조문</t>
@@ -3465,13 +3516,13 @@
         <v>55</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>28</v>
@@ -3488,10 +3539,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>19</v>
@@ -3509,22 +3560,22 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>28</v>
@@ -3541,10 +3592,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
@@ -3559,28 +3610,28 @@
         <v>19</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
@@ -3594,10 +3645,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
@@ -3615,28 +3666,28 @@
         <v>52</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>30</v>
@@ -3647,10 +3698,10 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>19</v>
@@ -3668,28 +3719,28 @@
         <v>52</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>30</v>
@@ -3700,10 +3751,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>19</v>
@@ -3721,28 +3772,28 @@
         <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>30</v>
@@ -3753,13 +3804,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>19</v>
@@ -3774,28 +3825,28 @@
         <v>43</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>30</v>
@@ -3806,10 +3857,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>19</v>
@@ -3827,28 +3878,28 @@
         <v>43</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>30</v>
@@ -3859,10 +3910,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>19</v>
@@ -3871,7 +3922,7 @@
         <v>19</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>19</v>
@@ -3880,42 +3931,42 @@
         <v>52</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>19</v>
@@ -3924,37 +3975,37 @@
         <v>19</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>30</v>
@@ -3965,13 +4016,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>19</v>
@@ -3983,31 +4034,31 @@
         <v>19</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>30</v>
@@ -4018,10 +4069,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>19</v>
@@ -4030,7 +4081,7 @@
         <v>19</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>19</v>
@@ -4039,28 +4090,28 @@
         <v>52</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>30</v>
@@ -4071,10 +4122,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>19</v>
@@ -4083,37 +4134,37 @@
         <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>30</v>
@@ -4124,10 +4175,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>19</v>
@@ -4145,28 +4196,28 @@
         <v>43</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>30</v>
@@ -4177,10 +4228,10 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>19</v>
@@ -4198,28 +4249,28 @@
         <v>43</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>30</v>
@@ -4230,10 +4281,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>19</v>
@@ -4248,31 +4299,31 @@
         <v>19</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>30</v>
@@ -4283,10 +4334,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>19</v>
@@ -4301,31 +4352,31 @@
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>30</v>
@@ -4336,16 +4387,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>19</v>
@@ -4354,31 +4405,31 @@
         <v>19</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>30</v>
@@ -4389,10 +4440,10 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -4401,7 +4452,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>19</v>
@@ -4410,28 +4461,28 @@
         <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>30</v>
@@ -4442,10 +4493,10 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -4454,7 +4505,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
@@ -4463,28 +4514,28 @@
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>49</v>
+        <v>228</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>30</v>
@@ -4495,10 +4546,10 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
@@ -4507,7 +4558,7 @@
         <v>19</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>19</v>
@@ -4516,48 +4567,48 @@
         <v>52</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>19</v>
@@ -4566,31 +4617,31 @@
         <v>19</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L26" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>30</v>
@@ -4601,10 +4652,10 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
@@ -4619,31 +4670,31 @@
         <v>19</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>49</v>
+        <v>256</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>30</v>
@@ -4654,49 +4705,49 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>30</v>
@@ -4707,10 +4758,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>19</v>
@@ -4719,37 +4770,37 @@
         <v>19</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>30</v>
@@ -4760,49 +4811,49 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>30</v>
@@ -4813,10 +4864,10 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>19</v>
@@ -4825,7 +4876,7 @@
         <v>19</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>19</v>
@@ -4834,28 +4885,28 @@
         <v>43</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>49</v>
+        <v>292</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>30</v>
@@ -4866,10 +4917,10 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>19</v>
@@ -4884,28 +4935,28 @@
         <v>19</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>29</v>
@@ -4914,15 +4965,15 @@
         <v>30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>19</v>
@@ -4931,7 +4982,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>19</v>
@@ -4940,25 +4991,25 @@
         <v>21</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>29</v>
@@ -4967,15 +5018,15 @@
         <v>30</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>19</v>
@@ -4993,42 +5044,42 @@
         <v>43</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>49</v>
+        <v>320</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>19</v>
@@ -5046,42 +5097,42 @@
         <v>52</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>19</v>
@@ -5099,42 +5150,42 @@
         <v>43</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>19</v>
@@ -5143,7 +5194,7 @@
         <v>19</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>19</v>
@@ -5152,42 +5203,42 @@
         <v>52</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>19</v>
@@ -5196,7 +5247,7 @@
         <v>19</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>19</v>
@@ -5205,95 +5256,95 @@
         <v>52</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>49</v>
+        <v>351</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>49</v>
+        <v>352</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>19</v>
@@ -5311,42 +5362,42 @@
         <v>21</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="J40" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="N40" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="O40" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>19</v>
@@ -5364,42 +5415,42 @@
         <v>52</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>49</v>
+        <v>377</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>19</v>
@@ -5414,45 +5465,45 @@
         <v>19</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>19</v>
@@ -5461,51 +5512,51 @@
         <v>19</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>19</v>
@@ -5514,7 +5565,7 @@
         <v>19</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>19</v>
@@ -5523,42 +5574,42 @@
         <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>19</v>
@@ -5567,51 +5618,51 @@
         <v>19</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>19</v>
@@ -5620,7 +5671,7 @@
         <v>19</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>19</v>
@@ -5629,42 +5680,42 @@
         <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>19</v>
@@ -5673,7 +5724,7 @@
         <v>19</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>19</v>
@@ -5682,42 +5733,42 @@
         <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>19</v>
@@ -5726,7 +5777,7 @@
         <v>19</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>19</v>
@@ -5735,42 +5786,42 @@
         <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>19</v>
@@ -5779,51 +5830,51 @@
         <v>19</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>19</v>
@@ -5832,51 +5883,51 @@
         <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>19</v>
@@ -5885,7 +5936,7 @@
         <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>19</v>
@@ -5894,42 +5945,42 @@
         <v>52</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>49</v>
+        <v>465</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>19</v>
@@ -5947,42 +5998,42 @@
         <v>52</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>49</v>
+        <v>475</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>19</v>
@@ -5997,37 +6048,37 @@
         <v>19</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>468</v>
+        <v>28</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="P53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -6047,10 +6098,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6058,7 +6109,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6066,7 +6117,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>473</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6074,7 +6125,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6082,7 +6133,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6090,23 +6141,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>478</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -6117,7 +6168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6126,18 +6177,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6145,7 +6196,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>485</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6153,7 +6204,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6161,15 +6212,15 @@
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>489</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6177,15 +6228,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6193,15 +6244,15 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="B10" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6209,15 +6260,23 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B12" t="s">
-        <v>498</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -6242,16 +6301,16 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>14</v>
@@ -6265,1727 +6324,1727 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="B2" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="C2" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="E2" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="B3" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="C3" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="E3" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F3" t="s">
         <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="B4" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="C4" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="E4" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F4" t="s">
         <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="B5" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="E5" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="B6" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="E6" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="B7" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C7" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="E7" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" t="s">
+        <v>542</v>
+      </c>
+      <c r="C8" t="s">
+        <v>539</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E8" t="s">
         <v>524</v>
       </c>
-      <c r="B8" t="s">
-        <v>525</v>
-      </c>
-      <c r="C8" t="s">
-        <v>522</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="E8" t="s">
-        <v>507</v>
-      </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="B9" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="C9" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="E9" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="B10" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C10" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="E10" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="B11" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="C11" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="E11" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="B12" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="C12" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="E12" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B13" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="C13" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="E13" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F13" t="s">
         <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="B14" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="C14" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="E14" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="B15" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="C15" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="E15" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="B16" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="C16" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="E16" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="B17" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C17" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="E17" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="B18" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="C18" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="E18" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="B19" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="C19" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="E19" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="E20" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="B21" t="s">
+        <v>582</v>
+      </c>
+      <c r="C21" t="s">
         <v>565</v>
       </c>
-      <c r="C21" t="s">
-        <v>548</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="E21" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="B22" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="C22" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="E22" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="B23" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="C23" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="E23" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="B24" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="C24" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="E24" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="B25" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="C25" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="E25" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="B26" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="C26" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="E26" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="B27" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="C27" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="B28" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="C28" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="E28" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="B29" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="C29" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="E29" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>609</v>
+      </c>
+      <c r="B30" t="s">
+        <v>610</v>
+      </c>
+      <c r="C30" t="s">
         <v>592</v>
       </c>
-      <c r="B30" t="s">
-        <v>593</v>
-      </c>
-      <c r="C30" t="s">
-        <v>575</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="E30" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F30" t="s">
         <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="B31" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="C31" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="E31" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F31" t="s">
         <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B32" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="C32" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="E32" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="B33" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="C33" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="E33" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F33" t="s">
         <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
       <c r="B34" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="C34" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
       <c r="E34" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
       <c r="B35" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="C35" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="E35" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="B36" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="C36" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="E36" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="B37" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="C37" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="E37" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="B38" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="C38" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="E38" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="B39" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="C39" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="E39" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F39" t="s">
         <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="B40" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="C40" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="E40" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="B41" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="C41" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="E41" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F41" t="s">
         <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="B42" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="C42" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="E42" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F42" t="s">
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
       <c r="B43" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="C43" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="E43" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>652</v>
+      </c>
+      <c r="B44" t="s">
+        <v>653</v>
+      </c>
+      <c r="C44" t="s">
         <v>635</v>
       </c>
-      <c r="B44" t="s">
-        <v>636</v>
-      </c>
-      <c r="C44" t="s">
-        <v>618</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
       <c r="E44" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F44" t="s">
         <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="B45" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
       <c r="C45" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="E45" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="B46" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="C46" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="E46" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="B47" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="C47" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="E47" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
       <c r="B48" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="C48" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="E48" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="B49" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="C49" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="E49" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="B50" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="C50" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="E50" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="B51" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="C51" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="E51" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="B52" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
       <c r="C52" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
       <c r="E52" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
       <c r="B53" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="C53" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="E53" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="B54" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
       <c r="C54" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="E54" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
       <c r="B55" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="C55" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="E55" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B56" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="C56" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="E56" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
       </c>
       <c r="G56" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="B57" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
       <c r="C57" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="E57" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="B58" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="C58" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="E58" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F58" t="s">
         <v>30</v>
       </c>
       <c r="G58" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
       <c r="B59" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="C59" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="E59" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
       <c r="B60" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="C60" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
       <c r="E60" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
       </c>
       <c r="G60" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="B61" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="C61" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="E61" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="B62" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="C62" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="E62" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
       </c>
       <c r="G62" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="B63" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
       <c r="C63" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="E63" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>713</v>
+      </c>
+      <c r="B64" t="s">
+        <v>714</v>
+      </c>
+      <c r="C64" t="s">
         <v>696</v>
       </c>
-      <c r="B64" t="s">
-        <v>697</v>
-      </c>
-      <c r="C64" t="s">
-        <v>679</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="E64" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="B65" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="C65" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
       <c r="E65" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="B66" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="C66" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="E66" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B67" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="C67" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="E67" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
       <c r="B68" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="C68" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="E68" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="B69" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
       <c r="C69" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="E69" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="B70" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="C70" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
       <c r="E70" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
       <c r="B71" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="C71" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
       <c r="E71" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
       <c r="B72" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="C72" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
       <c r="E72" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="B73" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
       <c r="C73" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
       <c r="E73" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="B74" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
       <c r="C74" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
       <c r="E74" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="B75" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="C75" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="E75" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F75" t="s">
         <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="B76" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="C76" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="E76" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="F76" t="s">
         <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="806">
   <si>
     <t>번호</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>추천 문장</t>
+  </si>
+  <si>
+    <t>확인 질문</t>
   </si>
   <si>
     <t>하면 안 되는 말</t>
@@ -102,6 +105,11 @@
 새로 대출해 주는 제도는 아닙니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">새 대출을 받으려고 문의하셨나요? | 예 / 아니요
+사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인 / 사업자 아님
+연체 중인 대출이 있나요? | 3개월 이상 / 3개월 미만 / 없음</t>
+  </si>
+  <si>
     <t>새로 대출을 받으실 수 있습니다</t>
   </si>
   <si>
@@ -142,6 +150,11 @@
 기금 사칭 보이스피싱에 주의하세요.</t>
   </si>
   <si>
+    <t xml:space="preserve">자금을 새로 빌리려고 문의하셨나요? | 예 / 아니요
+수수료나 선입금을 요구받으셨나요? | 예 / 아니요
+기존 대출 상환이 어려우신가요? | 예 / 아니요</t>
+  </si>
+  <si>
     <t>수수료를 내시면 빨리 처리됩니다</t>
   </si>
   <si>
@@ -176,6 +189,11 @@
 폐업·휴업도 부실우려차주일 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">가장 오래 연체된 대출은 얼마나 되었나요? | 3개월 이상 / 10~89일 / 10일 미만
+폐업했거나 6개월 이상 휴업 중인가요? | 예 / 아니요
+세금 체납으로 신용정보에 등재되었나요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>10일만 연체돼도 부실차주예요</t>
   </si>
   <si>
@@ -207,6 +225,11 @@
 1년 성실상환하면 공공정보가 해제돼요.</t>
   </si>
   <si>
+    <t xml:space="preserve">신청할 금융회사에 예·적금이 있나요? | 있음 / 없음
+그 금융회사의 마이너스통장·신용카드를 쓰시나요? | 예 / 아니요
+3개월 이상 연체된 대출이 있나요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>신청하셔도 아무 불이익이 없습니다</t>
   </si>
   <si>
@@ -235,6 +258,11 @@
 약정 후 회생 신청 시 효력 상실(제32조)</t>
   </si>
   <si>
+    <t xml:space="preserve">다른 채무조정을 이용 중인가요? | 개인회생 / 신복위 / 없음
+소상공인·자영업자이신가요? | 예 / 아니요
+대출 종류는 무엇인가요? | 담보 / 무담보 / 둘 다</t>
+  </si>
+  <si>
     <t>개인회생이나 신복위와 똑같은 제도예요</t>
   </si>
   <si>
@@ -263,6 +291,11 @@
   <si>
     <t xml:space="preserve">협약 금융기관 대출만 지원됩니다.
 미협약 대출은 다른 제도를 안내해요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대출 금융기관이 협약기관인지 확인하셨나요? | 확인함 / 모름
+연체 기간은 어느 정도인가요? | 3개월 이상 / 10~89일 / 연체 없음
+그 대출이 신복위 협약기관 대출인가요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
     <t>모든 금융기관 대출이 다 됩니다</t>
@@ -297,6 +330,11 @@
 담보대출은 신복위 방문 접수입니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+신청하려는 대출에 담보가 있나요? | 담보 / 무담보 / 둘 다
+홈페이지로 신청할 수 있으신가요? | 가능 / 어려움</t>
+  </si>
+  <si>
     <t>모든 대출을 홈페이지에서 한 번에 신청하시면 돼요</t>
   </si>
   <si>
@@ -329,6 +367,11 @@
 담보대출은 신복위 중개형입니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+대출 종류는 무엇인가요? | 신용·보증 / 담보 / 둘 다
+폐업·휴업 등 부실우려 요건에 해당하나요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>모든 대출은 캠코에서 직접 조정해 드려요</t>
   </si>
   <si>
@@ -356,6 +399,11 @@
   <si>
     <t xml:space="preserve">채무조정 신청은 1회로 제한됩니다.
 취소하면 3개월 재신청 불가(제16조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전에 새출발기금을 신청한 적이 있나요? | 있음 / 없음
+이전 약정이 부실우려 채무조정이었나요? | 예 / 아니요 / 해당 없음
+그 약정이 미납으로 실효되었나요? | 예 / 아니요 / 해당 없음</t>
   </si>
   <si>
     <t>언제든 다시 신청하시면 됩니다</t>
@@ -386,6 +434,11 @@
   <si>
     <t xml:space="preserve">연체가 없어도 신청할 수 있습니다.
 폐업·휴업·세금 체납이면 해당돼요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폐업했거나 6개월 이상 휴업 중인가요? | 예 / 아니요
+국세·지방세·관세 체납으로 등재되었나요? | 예 / 아니요 / 모름
+지금 연체 중인 대출이 있나요? | 있음 / 없음</t>
   </si>
   <si>
     <t>연체가 없으면 신청하실 수 없습니다</t>
@@ -416,6 +469,11 @@
 신청 단계면 취소 후 신청할 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">이용 중인 다른 제도가 있나요? | 신복위 / 개인회생 / 없음
+그 제도는 어느 단계인가요? | 신청 단계 / 상환 중
+기존 신청을 취소할 생각이 있으신가요? | 예 / 아니요 / 고민 중</t>
+  </si>
+  <si>
     <t>개인회생 중이셔도 그냥 새출발기금 신청하시면 돼요</t>
   </si>
   <si>
@@ -447,6 +505,11 @@
 선택 동의를 다시 하셔야 할 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">신청한 지 2주가 지났나요? | 예 / 아니요
+선택적 개인정보 동의를 하셨나요? | 했음 / 안 했음 / 모름
+재동의 안내를 받으셨나요? | 받음 / 못 받음</t>
+  </si>
+  <si>
     <t>2주 안에 무조건 나옵니다</t>
   </si>
   <si>
@@ -479,6 +542,11 @@
 잘못 입력한 건 본 약정 때 고치면 돼요.</t>
   </si>
   <si>
+    <t xml:space="preserve">잘못 입력한 항목은 무엇인가요? | 금융자산 / 보증금 / 기타
+임시 채무조정안을 받으셨나요? | 받음 / 아직
+본 약정을 체결하셨나요? | 체결함 / 아직</t>
+  </si>
+  <si>
     <t>잘못 입력하셨으면 처음부터 다시 신청하셔야 해요</t>
   </si>
   <si>
@@ -506,6 +574,11 @@
   <si>
     <t xml:space="preserve">홈페이지 이의신청으로 접수해 주세요.
 부채증명원 등 증빙을 첨부해 주세요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+부채증명원을 발급받으셨나요? | 있음 / 없음
+홈페이지 이의신청을 해 보셨나요? | 했음 / 안 했음</t>
   </si>
   <si>
     <t>전산에 연체정보가 없으면 신청할 방법이 없어요</t>
@@ -543,6 +616,11 @@
 취소하면 3개월 재신청 불가(제16조)</t>
   </si>
   <si>
+    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 / 중개형 / 모름
+신청한 달의 다음 달 15일이 지났나요? | 지남 / 안 지남
+채무조정이 확정되었나요? | 확정됨 / 아직</t>
+  </si>
+  <si>
     <t>취소하고 바로 다시 신청하시면 됩니다</t>
   </si>
   <si>
@@ -574,6 +652,11 @@
 고객센터로 미신청 채무를 신청하세요.</t>
   </si>
   <si>
+    <t xml:space="preserve">부실우려 약정이 미납으로 실효되었나요? | 예 / 아니요
+처음 신청 때 빠진 대출이 있나요? | 있음 / 없음
+빠진 대출이 협약 금융회사 대출인가요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>처음에 신청 안 한 대출은 이제 넣을 수 없어요</t>
   </si>
   <si>
@@ -604,6 +687,11 @@
 폐업한 법인은 지원되지 않습니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인
+지금 영업 상태는 어떤가요? | 영업 중 / 휴업 / 폐업
+휴·폐업했다면 2020년 4월 이후인가요? | 예 / 아니요 / 해당 없음</t>
+  </si>
+  <si>
     <t>폐업한 법인도 신청하실 수 있습니다</t>
   </si>
   <si>
@@ -632,6 +720,11 @@
   <si>
     <t xml:space="preserve">정책자금 제외 업종은 지원이 어려워요.
 부동산임대·금융·전문직 등이 해당돼요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주업종은 무엇인가요? | 일반 업종 / 부동산임대·금융 / 전문직
+정책자금 제외 업종인지 확인하셨나요? | 확인함 / 모름
+사업자등록증의 업종을 확인하셨나요? | 확인함 / 모름</t>
   </si>
   <si>
     <t>모든 업종이 다 됩니다</t>
@@ -663,6 +756,11 @@
   <si>
     <t xml:space="preserve">사업자대출과 가계대출 모두 됩니다.
 6개월 내 신규대출은 제외될 수 있어요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">총 채무가 15억 원 이내인가요? | 예 / 아니요
+최근 6개월 안에 받은 대출이 있나요? | 있음 / 없음
+법인 대표자의 가계대출인가요? | 예 / 아니요 / 해당 없음</t>
   </si>
   <si>
     <t>가지고 계신 대출은 전부 됩니다</t>
@@ -694,6 +792,11 @@
 부실우려차주는 골라서 신청할 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+빼고 싶은 대출의 종류는 무엇인가요? | 신용·보증 / 담보
+폐업·휴업 등 부실우려 요건에 해당하나요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>원하시는 대출만 골라서 신청하시면 됩니다</t>
   </si>
   <si>
@@ -721,6 +824,11 @@
 담보 10억, 무담보 5억을 넘으면 안 돼요.</t>
   </si>
   <si>
+    <t xml:space="preserve">담보 채무가 10억 원 이내인가요? | 예 / 아니요
+무담보 채무가 5억 원 이내인가요? | 예 / 아니요
+총 채무가 15억 원 이내인가요? | 예 / 아니요</t>
+  </si>
+  <si>
     <t>15억 안이면 됩니다</t>
   </si>
   <si>
@@ -746,6 +854,11 @@
   <si>
     <t xml:space="preserve">신청 다음 날 추심 중지 요청(제13조)
 매각기일 잡힌 경매는 협의가 필요해요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">진행 중인 법조치는 무엇인가요? | 강제집행·경매 / 가압류 / 추심
+신청 전에 매각기일이 잡혔나요? | 예 / 아니요 / 모름
+조치한 곳이 협약 금융기관인가요? | 협약기관 / 제3자 / 모름</t>
   </si>
   <si>
     <t>신청하시면 경매가 모두 멈춥니다</t>
@@ -784,6 +897,11 @@
 반복·야간 추심은 금지입니다.(제47조)</t>
   </si>
   <si>
+    <t xml:space="preserve">신청한 지 2주가 지났나요? | 예 / 아니요
+계속되는 추심은 무엇인가요? | 예·적금 상계 / 강제집행 / 독촉
+금융기관에 신청 사실을 알리셨나요? | 알림 / 안 알림</t>
+  </si>
+  <si>
     <t>신청만 하면 모든 추심이 바로 멈춰요</t>
   </si>
   <si>
@@ -816,6 +934,11 @@
 중개형은 확정까지 2~3개월 걸려요.</t>
   </si>
   <si>
+    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 / 중개형 / 모름
+임시 채무조정안을 받으셨나요? | 받음 / 아직
+보증서 대출(보증부 채권)이 있나요? | 있음 / 없음 / 모름</t>
+  </si>
+  <si>
     <t>한 달이면 끝납니다</t>
   </si>
   <si>
@@ -850,6 +973,11 @@
     <t xml:space="preserve">원금 감면은 부실차주 무담보만 돼요.
 담보대출은 원금 감면 대상이 아닙니다.
 부실우려차주는 연체이자 감면(제19조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+감면받으려는 대출은 무엇인가요? | 무담보 / 담보
+부동산·예금 등 보유 재산이 있나요? | 있음 / 없음</t>
   </si>
   <si>
     <t>신청하시면 원금을 깎아 드립니다</t>
@@ -884,6 +1012,11 @@
 상환기간은 최대 20년까지 가능해요.</t>
   </si>
   <si>
+    <t xml:space="preserve">해당하는 사항이 있나요? | 기초수급·중증장애 / 70세 이상 / 해당 없음
+총 채무가 1억 원 이하인가요? | 예 / 아니요
+소득이 중위소득 60% 이하인가요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>취약계층이면 빚을 전부 탕감받으세요</t>
   </si>
   <si>
@@ -914,6 +1047,11 @@
 영업 중이면 추가 감면 대상이 아니에요.</t>
   </si>
   <si>
+    <t xml:space="preserve">폐업하셨나요? | 폐업 / 영업 중
+취업·재창업 교육을 이수하셨나요? | 이수 / 미이수
+연체 기간이 3개월 이상인가요? | 예 / 아니요</t>
+  </si>
+  <si>
     <t>교육 받으시면 10% 더 깎아 드립니다</t>
   </si>
   <si>
@@ -945,6 +1083,11 @@
     <t xml:space="preserve">상환기간 변경은 1회만 됩니다.(제24조)
 조기상환(중도상환)은 가능합니다.
 12회 이상 내고 일시상환 시 추가감면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환기간 변경 / 조기상환
+약정을 체결하셨나요? | 체결함 / 아직
+감면율 구간이 바뀌는지 확인하셨나요? | 확인함 / 모름</t>
   </si>
   <si>
     <t>상환기간은 마음대로 바꾸실 수 있습니다</t>
@@ -979,6 +1122,11 @@
 폐업자는 취업·재창업 시 1회 해제돼요.</t>
   </si>
   <si>
+    <t xml:space="preserve">첫 상환일부터 1년이 지났나요? | 예 / 아니요
+12회 이상 빠짐없이 납부하셨나요? | 예 / 아니요
+폐업 후 취업·재창업에 성공하셨나요? | 예 / 아니요 / 해당 없음</t>
+  </si>
+  <si>
     <t>약정하시면 바로 신용이 회복됩니다</t>
   </si>
   <si>
@@ -1003,6 +1151,11 @@
   <si>
     <t xml:space="preserve">신청자 전원 도덕적 해이 심사를 해요.
 고의 연체는 신청이 거절됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신청 직전에 연체가 시작되었나요? | 예 / 아니요
+보유 재산이 채무보다 많은가요? | 예 / 아니요 / 모름
+심사 결과를 통보받으셨나요? | 받음 / 아직</t>
   </si>
   <si>
     <t>심사는 일부만 받으니 걱정 안 하셔도 돼요</t>
@@ -1033,6 +1186,11 @@
   <si>
     <t xml:space="preserve">홈페이지 '금융기관 조회'에서 확인하세요.
 협약 가입 기관 대출만 지원됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대출받은 금융기관을 알고 계신가요? | 앎 / 모름
+홈페이지 금융기관 조회를 해 보셨나요? | 했음 / 안 했음
+조회 결과 협약기관이었나요? | 예 / 아니요 / 조회 전</t>
   </si>
   <si>
     <t>모든 금융기관 대출이 다 지원됩니다</t>
@@ -1067,6 +1225,11 @@
 웹플랫폼 공지와 알림톡으로 안내해요.</t>
   </si>
   <si>
+    <t xml:space="preserve">약정 후 성실히 상환 중인가요? | 예 / 아니요
+관심 있는 지원은 무엇인가요? | 교육 / 자금 / 경영개선
+웹플랫폼 공지·알림톡을 받으셨나요? | 받음 / 못 받음</t>
+  </si>
+  <si>
     <t>신청하시면 자금 지원을 꼭 받으실 수 있습니다</t>
   </si>
   <si>
@@ -1096,6 +1259,11 @@
 두 제도를 비교해 유리한 쪽을 고르세요.</t>
   </si>
   <si>
+    <t xml:space="preserve">개인회생은 어느 단계인가요? | 신청 중 / 인가 후 상환 중
+채무가 협약 금융기관 대출인가요? | 예 / 아니요 / 모름
+개인사업자나 법인 소상공인인가요? | 예 / 아니요</t>
+  </si>
+  <si>
     <t>새출발기금이 무조건 더 유리합니다</t>
   </si>
   <si>
@@ -1122,6 +1290,11 @@
 개인사업장 두 곳이면 1회만 신청돼요.</t>
   </si>
   <si>
+    <t xml:space="preserve">운영하는 사업자는 어떻게 되나요? | 개인+법인 / 개인 2곳
+각각 사업자등록이 되어 있나요? | 예 / 아니요
+이미 한 사업자로 신청하셨나요? | 신청함 / 아직</t>
+  </si>
+  <si>
     <t>사업장마다 따로 신청하시면 됩니다</t>
   </si>
   <si>
@@ -1145,6 +1318,11 @@
 사업자등록증이 있어야 합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">사업자등록증이 있나요? | 있음 / 없음
+지금 사업을 하고 계신가요? | 영업 중 / 휴업 / 폐업
+대출이 협약 금융기관 대출인가요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>외국인은 신청할 수 없습니다</t>
   </si>
   <si>
@@ -1171,6 +1349,11 @@
 일반 소상공인확인서를 내 주세요.</t>
   </si>
   <si>
+    <t xml:space="preserve">소상공인확인서는 어디서 받으셨나요? | 중소기업현황정보시스템 / 소진공 / 모름
+법인 소상공인이신가요? | 예 / 아니요
+착한임대인 세제혜택용 확인서인가요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>소진공 확인서를 내셔도 됩니다</t>
   </si>
   <si>
@@ -1200,6 +1383,11 @@
 약정 때 대상 채무를 확인할 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">같은 대출이 두 번 보이나요? | 예 / 아니요
+그 대출이 연체 중인가요? | 예 / 아니요
+약정 단계까지 진행되었나요? | 약정 전 / 약정 단계</t>
+  </si>
+  <si>
     <t>중복으로 나온 건 빚이 두 배라는 뜻이에요</t>
   </si>
   <si>
@@ -1227,6 +1415,11 @@
   <si>
     <t xml:space="preserve">먼저 신복위 중개형으로 지원합니다.
 부동의하면 기금이 채권을 매입해요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담보 금융회사가 부동의했나요? | 부동의 / 동의 / 모름
+담보 종류는 무엇인가요? | 부동산 / 기타
+미협약기관 대출이 있나요? | 있음 / 없음 / 모름</t>
   </si>
   <si>
     <t>금융회사가 부동의하면 채무조정이 끝납니다</t>
@@ -1260,6 +1453,11 @@
 재산가치 이상 갚으면 해제될 수 있어요.</t>
   </si>
   <si>
+    <t xml:space="preserve">걸려 있는 법조치는 무엇인가요? | 가압류 / 압류·경매 / 기타
+채무조정 약정을 체결하셨나요? | 체결함 / 아직
+해당 재산가치 이상 갚을 여력이 있나요? | 있음 / 없음 / 모름</t>
+  </si>
+  <si>
     <t>신청하시면 가압류가 바로 풀립니다</t>
   </si>
   <si>
@@ -1310,6 +1508,11 @@
 협약 금융회사 채권이어야 합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">해당 채무는 무엇인가요? | 카드론 / 카드대금 / 현금서비스
+그 카드사가 협약 금융회사인가요? | 예 / 아니요 / 모름
+연체 기간은 어느 정도인가요? | 3개월 이상 / 3개월 미만 / 없음</t>
+  </si>
+  <si>
     <t>카드빚은 지원되지 않습니다</t>
   </si>
   <si>
@@ -1335,6 +1538,11 @@
 재심사 후 추가 심사는 어렵습니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">심사 결과를 통보받으셨나요? | 받음 / 아직
+이미 이의신청을 하셨나요? | 했음 / 안 했음
+재심사 결과를 받으셨나요? | 받음 / 아직 / 해당 없음</t>
+  </si>
+  <si>
     <t>몇 번이고 다시 심사받으실 수 있습니다</t>
   </si>
   <si>
@@ -1359,6 +1567,11 @@
   <si>
     <t xml:space="preserve">약정 후에도 재산 조사를 합니다.
 은닉재산이 나오면 조정이 무효예요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약정 후 새로 생긴 재산이 있나요? | 있음 / 없음
+신청 때 신고하지 않은 재산이 있나요? | 있음 / 없음
+재산 조사 안내를 받으셨나요? | 받음 / 못 받음</t>
   </si>
   <si>
     <t>약정하고 나면 더 조사하지 않습니다</t>
@@ -1405,6 +1618,11 @@
     <t xml:space="preserve">입원·실직·출산 등은 유예 신청 가능
 총 유예기간은 최장 3년(제26조)
 밀린 상환금을 먼저 내셔야 해요.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지금 분할상환금 연체가 있나요? | 있음 / 없음
+유예 사유는 무엇인가요? | 입원·질병 / 실직·휴폐업 / 출산·육아·기타
+대출 종류는 무엇인가요? | 무담보·동산담보 / 부동산담보</t>
   </si>
   <si>
     <t>사유 없이도 유예해 드립니다</t>
@@ -1458,6 +1676,11 @@
 회생·파산 신청도 상실 사유입니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">분할상환금이 몇 회 밀렸나요? | 3회 이상 / 1~2회 / 없음
+효력 상실 예정 통지를 받으셨나요? | 받음 / 못 받음
+파산·회생·신복위를 신청하셨나요? | 예 / 아니요</t>
+  </si>
+  <si>
     <t>몇 달 밀려도 괜찮습니다</t>
   </si>
   <si>
@@ -1487,6 +1710,11 @@
   <si>
     <t xml:space="preserve">상실 후 6개월 안에 부활할 수 있어요.
 1회분만 내고 부활할 수도 있어요.(제34조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효력 상실 후 6개월이 지났나요? | 지남 / 안 지남
+상실 사유가 3개월 이상 연체인가요? | 예 / 아니요
+약정 후 새로 취득한 재산이 있나요? | 있음 / 없음</t>
   </si>
   <si>
     <t>언제든지 부활할 수 있습니다</t>
@@ -1521,6 +1749,11 @@
   <si>
     <t xml:space="preserve">효력 상실 후 재약정할 수 있습니다.
 재약정에는 거치기간이 없습니다.(제35조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효력 상실 사유는 무엇인가요? | 연체 / 자료허위·재산은닉 / 파산·회생 신청
+그 사유가 해소되었나요? | 해소됨 / 아직 / 해당 없음
+차주 구분은 무엇인가요? | 부실차주 / 부실우려차주 / 모름</t>
   </si>
   <si>
     <t>재약정하면 거치기간을 다시 받으실 수 있습니다</t>
@@ -1559,6 +1792,11 @@
   <si>
     <t xml:space="preserve">거치기간은 최초 약정 때 1회만 돼요.
 최대 1년, 특례대상은 3년(제21조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최초 약정 단계인가요? | 예 / 이미 약정함
+해당하는 사항이 있나요? | 취약계층 특례 / 저소득 / 해당 없음
+담보는 어떻게 되나요? | 부동산담보 / 무담보 / 둘 다</t>
   </si>
   <si>
     <t>거치기간은 언제든 다시 받을 수 있습니다</t>
@@ -1602,6 +1840,11 @@
 CMS 자동이체 수수료는 기금 부담이에요.</t>
   </si>
   <si>
+    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환일 변경 / 납부 방법 / 일시상환
+상환일을 바꾼 적이 있나요? | 있음 / 없음
+지금 연체가 있나요? | 있음 / 없음</t>
+  </si>
+  <si>
     <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
   </si>
   <si>
@@ -1640,6 +1883,11 @@
 정보 이용 동의서도 함께 받습니다.(제12조)</t>
   </si>
   <si>
+    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인 / 특고·프리랜서
+상환 방식은 무엇인가요? | 분할상환 / 일시상환
+신분증·사업자등록증을 준비하셨나요? | 준비함 / 아직</t>
+  </si>
+  <si>
     <t>신분증만 있으면 다른 서류는 필요 없어요</t>
   </si>
   <si>
@@ -1675,6 +1923,11 @@
     <t xml:space="preserve">온라인 플랫폼으로 신청합니다(제11조)
 대리 신청은 위임장이 필요합니다.
 대신 갚으려면 승낙서가 필요해요(제11조)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">누가 신청하시나요? | 본인 / 대리인
+대리인이라면 위임장이 있나요? | 있음 / 없음 / 해당 없음
+채무자 아닌 분이 대신 갚으려 하시나요? | 예 / 아니요</t>
   </si>
   <si>
     <t>가족이면 위임장 없이 대신 신청돼요</t>
@@ -1723,6 +1976,11 @@
 세부 산정기준표는 공개되지 않아요.</t>
   </si>
   <si>
+    <t xml:space="preserve">보유 재산이 있나요? | 있음 / 없음
+연체 기간이 3개월 이상인가요? | 예 / 아니요
+사회취약계층에 해당하나요? | 예 / 아니요 / 모름</t>
+  </si>
+  <si>
     <t>재산은 감면 계산과 상관없어요</t>
   </si>
   <si>
@@ -1817,6 +2075,9 @@
   </si>
   <si>
     <t>민원인을 안내할 담당 창구. 모든 줄에 채운다. 원문에 기관이 나오면 그 기관을, 없으면 새출발기금 콜센터를 적었다(2026-10-29 초안, 담당자 검토 필요).</t>
+  </si>
+  <si>
+    <t>정확히 안내하려고 민원인에게 물어볼 질문 3개(칸 안에서 줄바꿈으로 구분). 한 줄은 "질문 | 선택지 / 선택지" 꼴이고 선택지는 2~3개. FAQ 답변·요강 조문에 나온 조건만 묻고 이름·전화번호·고객번호 등 개인정보는 묻지 않는다. 비워 두면 data/default-questions.json의 주제별 기본 질문이 나온다(2026-10-29 초안, 담당자 검토 필요).</t>
   </si>
   <si>
     <t>조문</t>
@@ -3253,7 +3514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3266,13 +3527,15 @@
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="10" max="10" width="70" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="15" width="40" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+    <col min="13" max="13" width="60" customWidth="1"/>
+    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3324,2761 +3587,2920 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="P11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="P32" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="Q32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="3" t="s">
+      <c r="H35" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="P35" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="3" t="s">
+      <c r="F40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="O42" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="P42" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="O44" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q7" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="P44" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="3" t="s">
+      <c r="P45" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="P46" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="O47" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P11" s="3" t="s">
+      <c r="P47" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="O48" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="P48" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P13" s="3" t="s">
+      <c r="P49" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="O50" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="P50" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="O51" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P15" s="3" t="s">
+      <c r="P51" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="O53" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>485</v>
-      </c>
       <c r="P53" s="3" t="s">
-        <v>30</v>
+        <v>537</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>131</v>
+        <v>32</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6098,10 +6520,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>486</v>
+        <v>538</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6109,7 +6531,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>488</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6117,7 +6539,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>489</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6125,7 +6547,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>490</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6133,7 +6555,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>491</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6141,23 +6563,23 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>492</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>493</v>
+        <v>545</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>494</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>547</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>496</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -6168,7 +6590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6177,18 +6599,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>497</v>
+        <v>549</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>498</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>499</v>
+        <v>551</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>500</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6196,7 +6618,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>501</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6204,39 +6626,39 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>502</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>503</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>506</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>508</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6244,15 +6666,15 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>510</v>
+        <v>562</v>
       </c>
       <c r="B10" t="s">
-        <v>511</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6260,23 +6682,31 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>512</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>513</v>
+        <v>565</v>
       </c>
       <c r="B12" t="s">
-        <v>514</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>515</v>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -6301,1750 +6731,1750 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>516</v>
+        <v>569</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>517</v>
+        <v>570</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>518</v>
+        <v>571</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>519</v>
+        <v>572</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>520</v>
+        <v>573</v>
       </c>
       <c r="B2" t="s">
-        <v>521</v>
+        <v>574</v>
       </c>
       <c r="C2" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>523</v>
+        <v>576</v>
       </c>
       <c r="E2" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>578</v>
       </c>
       <c r="B3" t="s">
-        <v>526</v>
+        <v>579</v>
       </c>
       <c r="C3" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>527</v>
+        <v>580</v>
       </c>
       <c r="E3" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>528</v>
+        <v>581</v>
       </c>
       <c r="B4" t="s">
-        <v>529</v>
+        <v>582</v>
       </c>
       <c r="C4" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>530</v>
+        <v>583</v>
       </c>
       <c r="E4" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>531</v>
+        <v>584</v>
       </c>
       <c r="B5" t="s">
-        <v>532</v>
+        <v>585</v>
       </c>
       <c r="C5" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>533</v>
+        <v>586</v>
       </c>
       <c r="E5" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>534</v>
+        <v>587</v>
       </c>
       <c r="B6" t="s">
-        <v>535</v>
+        <v>588</v>
       </c>
       <c r="C6" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>536</v>
+        <v>589</v>
       </c>
       <c r="E6" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>537</v>
+        <v>590</v>
       </c>
       <c r="B7" t="s">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="C7" t="s">
-        <v>539</v>
+        <v>592</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>540</v>
+        <v>593</v>
       </c>
       <c r="E7" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="B8" t="s">
-        <v>542</v>
+        <v>595</v>
       </c>
       <c r="C8" t="s">
-        <v>539</v>
+        <v>592</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>543</v>
+        <v>596</v>
       </c>
       <c r="E8" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>544</v>
+        <v>597</v>
       </c>
       <c r="B9" t="s">
-        <v>545</v>
+        <v>598</v>
       </c>
       <c r="C9" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>547</v>
+        <v>600</v>
       </c>
       <c r="E9" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>548</v>
+        <v>601</v>
       </c>
       <c r="B10" t="s">
-        <v>549</v>
+        <v>602</v>
       </c>
       <c r="C10" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>550</v>
+        <v>603</v>
       </c>
       <c r="E10" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="B11" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="C11" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>553</v>
+        <v>606</v>
       </c>
       <c r="E11" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>554</v>
+        <v>607</v>
       </c>
       <c r="B12" t="s">
-        <v>555</v>
+        <v>608</v>
       </c>
       <c r="C12" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>556</v>
+        <v>609</v>
       </c>
       <c r="E12" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="B13" t="s">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="C13" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>559</v>
+        <v>612</v>
       </c>
       <c r="E13" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>560</v>
+        <v>613</v>
       </c>
       <c r="B14" t="s">
-        <v>561</v>
+        <v>614</v>
       </c>
       <c r="C14" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>562</v>
+        <v>615</v>
       </c>
       <c r="E14" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>563</v>
+        <v>616</v>
       </c>
       <c r="B15" t="s">
-        <v>564</v>
+        <v>617</v>
       </c>
       <c r="C15" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="E15" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>567</v>
+        <v>620</v>
       </c>
       <c r="B16" t="s">
-        <v>568</v>
+        <v>621</v>
       </c>
       <c r="C16" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>569</v>
+        <v>622</v>
       </c>
       <c r="E16" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="B17" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="C17" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>572</v>
+        <v>625</v>
       </c>
       <c r="E17" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="B18" t="s">
-        <v>574</v>
+        <v>627</v>
       </c>
       <c r="C18" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="E18" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>576</v>
+        <v>629</v>
       </c>
       <c r="B19" t="s">
+        <v>630</v>
+      </c>
+      <c r="C19" t="s">
+        <v>618</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E19" t="s">
         <v>577</v>
       </c>
-      <c r="C19" t="s">
-        <v>565</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="E19" t="s">
-        <v>524</v>
-      </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>579</v>
+        <v>632</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="E20" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="B21" t="s">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="C21" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>583</v>
+        <v>636</v>
       </c>
       <c r="E21" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>584</v>
+        <v>637</v>
       </c>
       <c r="B22" t="s">
-        <v>585</v>
+        <v>638</v>
       </c>
       <c r="C22" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
       <c r="E22" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="B23" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="C23" t="s">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>589</v>
+        <v>642</v>
       </c>
       <c r="E23" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="B24" t="s">
-        <v>591</v>
+        <v>644</v>
       </c>
       <c r="C24" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
       <c r="E24" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>594</v>
+        <v>647</v>
       </c>
       <c r="B25" t="s">
-        <v>595</v>
+        <v>648</v>
       </c>
       <c r="C25" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>596</v>
+        <v>649</v>
       </c>
       <c r="E25" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>597</v>
+        <v>650</v>
       </c>
       <c r="B26" t="s">
-        <v>598</v>
+        <v>651</v>
       </c>
       <c r="C26" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>599</v>
+        <v>652</v>
       </c>
       <c r="E26" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>600</v>
+        <v>653</v>
       </c>
       <c r="B27" t="s">
-        <v>601</v>
+        <v>654</v>
       </c>
       <c r="C27" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>602</v>
+        <v>655</v>
       </c>
       <c r="E27" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>603</v>
+        <v>656</v>
       </c>
       <c r="B28" t="s">
-        <v>604</v>
+        <v>657</v>
       </c>
       <c r="C28" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>605</v>
+        <v>658</v>
       </c>
       <c r="E28" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>606</v>
+        <v>659</v>
       </c>
       <c r="B29" t="s">
-        <v>607</v>
+        <v>660</v>
       </c>
       <c r="C29" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>608</v>
+        <v>661</v>
       </c>
       <c r="E29" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>609</v>
+        <v>662</v>
       </c>
       <c r="B30" t="s">
-        <v>610</v>
+        <v>663</v>
       </c>
       <c r="C30" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>611</v>
+        <v>664</v>
       </c>
       <c r="E30" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="B31" t="s">
-        <v>613</v>
+        <v>666</v>
       </c>
       <c r="C31" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>614</v>
+        <v>667</v>
       </c>
       <c r="E31" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>615</v>
+        <v>668</v>
       </c>
       <c r="B32" t="s">
-        <v>616</v>
+        <v>669</v>
       </c>
       <c r="C32" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>617</v>
+        <v>670</v>
       </c>
       <c r="E32" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>618</v>
+        <v>671</v>
       </c>
       <c r="B33" t="s">
-        <v>619</v>
+        <v>672</v>
       </c>
       <c r="C33" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>620</v>
+        <v>673</v>
       </c>
       <c r="E33" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>621</v>
+        <v>674</v>
       </c>
       <c r="B34" t="s">
-        <v>622</v>
+        <v>675</v>
       </c>
       <c r="C34" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="E34" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G34" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>624</v>
+        <v>677</v>
       </c>
       <c r="B35" t="s">
-        <v>625</v>
+        <v>678</v>
       </c>
       <c r="C35" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>626</v>
+        <v>679</v>
       </c>
       <c r="E35" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G35" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>627</v>
+        <v>680</v>
       </c>
       <c r="B36" t="s">
-        <v>628</v>
+        <v>681</v>
       </c>
       <c r="C36" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>629</v>
+        <v>682</v>
       </c>
       <c r="E36" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G36" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>630</v>
+        <v>683</v>
       </c>
       <c r="B37" t="s">
-        <v>631</v>
+        <v>684</v>
       </c>
       <c r="C37" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>632</v>
+        <v>685</v>
       </c>
       <c r="E37" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>633</v>
+        <v>686</v>
       </c>
       <c r="B38" t="s">
-        <v>634</v>
+        <v>687</v>
       </c>
       <c r="C38" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>636</v>
+        <v>689</v>
       </c>
       <c r="E38" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>637</v>
+        <v>690</v>
       </c>
       <c r="B39" t="s">
-        <v>638</v>
+        <v>691</v>
       </c>
       <c r="C39" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>639</v>
+        <v>692</v>
       </c>
       <c r="E39" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>640</v>
+        <v>693</v>
       </c>
       <c r="B40" t="s">
-        <v>641</v>
+        <v>694</v>
       </c>
       <c r="C40" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>642</v>
+        <v>695</v>
       </c>
       <c r="E40" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G40" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>643</v>
+        <v>696</v>
       </c>
       <c r="B41" t="s">
-        <v>644</v>
+        <v>697</v>
       </c>
       <c r="C41" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>645</v>
+        <v>698</v>
       </c>
       <c r="E41" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G41" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>646</v>
+        <v>699</v>
       </c>
       <c r="B42" t="s">
-        <v>647</v>
+        <v>700</v>
       </c>
       <c r="C42" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>648</v>
+        <v>701</v>
       </c>
       <c r="E42" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>649</v>
+        <v>702</v>
       </c>
       <c r="B43" t="s">
-        <v>650</v>
+        <v>703</v>
       </c>
       <c r="C43" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>651</v>
+        <v>704</v>
       </c>
       <c r="E43" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G43" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>652</v>
+        <v>705</v>
       </c>
       <c r="B44" t="s">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="C44" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>654</v>
+        <v>707</v>
       </c>
       <c r="E44" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G44" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="B45" t="s">
-        <v>656</v>
+        <v>709</v>
       </c>
       <c r="C45" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>657</v>
+        <v>710</v>
       </c>
       <c r="E45" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G45" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>658</v>
+        <v>711</v>
       </c>
       <c r="B46" t="s">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="C46" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>660</v>
+        <v>713</v>
       </c>
       <c r="E46" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G46" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="B47" t="s">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="C47" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>663</v>
+        <v>716</v>
       </c>
       <c r="E47" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F47" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G47" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>664</v>
+        <v>717</v>
       </c>
       <c r="B48" t="s">
-        <v>665</v>
+        <v>718</v>
       </c>
       <c r="C48" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>666</v>
+        <v>719</v>
       </c>
       <c r="E48" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F48" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G48" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>667</v>
+        <v>720</v>
       </c>
       <c r="B49" t="s">
-        <v>668</v>
+        <v>721</v>
       </c>
       <c r="C49" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>669</v>
+        <v>722</v>
       </c>
       <c r="E49" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G49" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>670</v>
+        <v>723</v>
       </c>
       <c r="B50" t="s">
-        <v>671</v>
+        <v>724</v>
       </c>
       <c r="C50" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>672</v>
+        <v>725</v>
       </c>
       <c r="E50" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F50" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G50" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="B51" t="s">
-        <v>674</v>
+        <v>727</v>
       </c>
       <c r="C51" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>675</v>
+        <v>728</v>
       </c>
       <c r="E51" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F51" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G51" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>676</v>
+        <v>729</v>
       </c>
       <c r="B52" t="s">
-        <v>677</v>
+        <v>730</v>
       </c>
       <c r="C52" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>678</v>
+        <v>731</v>
       </c>
       <c r="E52" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F52" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G52" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>679</v>
+        <v>732</v>
       </c>
       <c r="B53" t="s">
-        <v>680</v>
+        <v>733</v>
       </c>
       <c r="C53" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>681</v>
+        <v>734</v>
       </c>
       <c r="E53" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F53" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G53" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>682</v>
+        <v>735</v>
       </c>
       <c r="B54" t="s">
-        <v>683</v>
+        <v>736</v>
       </c>
       <c r="C54" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>684</v>
+        <v>737</v>
       </c>
       <c r="E54" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F54" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G54" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>685</v>
+        <v>738</v>
       </c>
       <c r="B55" t="s">
-        <v>686</v>
+        <v>739</v>
       </c>
       <c r="C55" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>687</v>
+        <v>740</v>
       </c>
       <c r="E55" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F55" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G55" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>741</v>
+      </c>
+      <c r="B56" t="s">
+        <v>742</v>
+      </c>
+      <c r="C56" t="s">
         <v>688</v>
       </c>
-      <c r="B56" t="s">
-        <v>689</v>
-      </c>
-      <c r="C56" t="s">
-        <v>635</v>
-      </c>
       <c r="D56" s="3" t="s">
-        <v>690</v>
+        <v>743</v>
       </c>
       <c r="E56" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F56" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>691</v>
+        <v>744</v>
       </c>
       <c r="B57" t="s">
-        <v>692</v>
+        <v>745</v>
       </c>
       <c r="C57" t="s">
-        <v>635</v>
+        <v>688</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>693</v>
+        <v>746</v>
       </c>
       <c r="E57" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F57" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G57" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>694</v>
+        <v>747</v>
       </c>
       <c r="B58" t="s">
-        <v>695</v>
+        <v>748</v>
       </c>
       <c r="C58" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>697</v>
+        <v>750</v>
       </c>
       <c r="E58" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F58" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G58" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>698</v>
+        <v>751</v>
       </c>
       <c r="B59" t="s">
-        <v>699</v>
+        <v>752</v>
       </c>
       <c r="C59" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>700</v>
+        <v>753</v>
       </c>
       <c r="E59" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F59" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G59" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>701</v>
+        <v>754</v>
       </c>
       <c r="B60" t="s">
-        <v>702</v>
+        <v>755</v>
       </c>
       <c r="C60" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>703</v>
+        <v>756</v>
       </c>
       <c r="E60" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>704</v>
+        <v>757</v>
       </c>
       <c r="B61" t="s">
-        <v>705</v>
+        <v>758</v>
       </c>
       <c r="C61" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>706</v>
+        <v>759</v>
       </c>
       <c r="E61" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F61" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G61" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>707</v>
+        <v>760</v>
       </c>
       <c r="B62" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="C62" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>709</v>
+        <v>762</v>
       </c>
       <c r="E62" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F62" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G62" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>710</v>
+        <v>763</v>
       </c>
       <c r="B63" t="s">
-        <v>711</v>
+        <v>764</v>
       </c>
       <c r="C63" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>712</v>
+        <v>765</v>
       </c>
       <c r="E63" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F63" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G63" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>713</v>
+        <v>766</v>
       </c>
       <c r="B64" t="s">
-        <v>714</v>
+        <v>767</v>
       </c>
       <c r="C64" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>712</v>
+        <v>765</v>
       </c>
       <c r="E64" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F64" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G64" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>715</v>
+        <v>768</v>
       </c>
       <c r="B65" t="s">
-        <v>716</v>
+        <v>769</v>
       </c>
       <c r="C65" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>717</v>
+        <v>770</v>
       </c>
       <c r="E65" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F65" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G65" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>718</v>
+        <v>771</v>
       </c>
       <c r="B66" t="s">
-        <v>719</v>
+        <v>772</v>
       </c>
       <c r="C66" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>720</v>
+        <v>773</v>
       </c>
       <c r="E66" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F66" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G66" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>721</v>
+        <v>774</v>
       </c>
       <c r="B67" t="s">
-        <v>722</v>
+        <v>775</v>
       </c>
       <c r="C67" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>723</v>
+        <v>776</v>
       </c>
       <c r="E67" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F67" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G67" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>724</v>
+        <v>777</v>
       </c>
       <c r="B68" t="s">
-        <v>725</v>
+        <v>778</v>
       </c>
       <c r="C68" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>726</v>
+        <v>779</v>
       </c>
       <c r="E68" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G68" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>727</v>
+        <v>780</v>
       </c>
       <c r="B69" t="s">
-        <v>728</v>
+        <v>781</v>
       </c>
       <c r="C69" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>729</v>
+        <v>782</v>
       </c>
       <c r="E69" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G69" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>730</v>
+        <v>783</v>
       </c>
       <c r="B70" t="s">
-        <v>731</v>
+        <v>784</v>
       </c>
       <c r="C70" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>732</v>
+        <v>785</v>
       </c>
       <c r="E70" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F70" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G70" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>733</v>
+        <v>786</v>
       </c>
       <c r="B71" t="s">
-        <v>734</v>
+        <v>787</v>
       </c>
       <c r="C71" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>735</v>
+        <v>788</v>
       </c>
       <c r="E71" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F71" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G71" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>736</v>
+        <v>789</v>
       </c>
       <c r="B72" t="s">
-        <v>737</v>
+        <v>790</v>
       </c>
       <c r="C72" t="s">
-        <v>696</v>
+        <v>749</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>738</v>
+        <v>791</v>
       </c>
       <c r="E72" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F72" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G72" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>739</v>
+        <v>792</v>
       </c>
       <c r="B73" t="s">
-        <v>740</v>
+        <v>793</v>
       </c>
       <c r="C73" t="s">
-        <v>741</v>
+        <v>794</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>742</v>
+        <v>795</v>
       </c>
       <c r="E73" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F73" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G73" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>743</v>
+        <v>796</v>
       </c>
       <c r="B74" t="s">
-        <v>744</v>
+        <v>797</v>
       </c>
       <c r="C74" t="s">
-        <v>741</v>
+        <v>794</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>745</v>
+        <v>798</v>
       </c>
       <c r="E74" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F74" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>746</v>
+        <v>799</v>
       </c>
       <c r="B75" t="s">
-        <v>747</v>
+        <v>800</v>
       </c>
       <c r="C75" t="s">
-        <v>741</v>
+        <v>794</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>748</v>
+        <v>801</v>
       </c>
       <c r="E75" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F75" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G75" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>749</v>
+        <v>802</v>
       </c>
       <c r="B76" t="s">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="C76" t="s">
-        <v>751</v>
+        <v>804</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>752</v>
+        <v>805</v>
       </c>
       <c r="E76" t="s">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="F76" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G76" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/counsel-db.xlsx
+++ b/data/counsel-db.xlsx
@@ -105,9 +105,9 @@
 새로 대출해 주는 제도는 아닙니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">새 대출을 받으려고 문의하셨나요? | 예 / 아니요
-사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인 / 사업자 아님
-연체 중인 대출이 있나요? | 3개월 이상 / 3개월 미만 / 없음</t>
+    <t xml:space="preserve">새 대출을 받으려고 문의하셨나요? | 예 [키워드=대출 지원] / 아니요
+사업자 형태는 무엇인가요? | 개인사업자 [구분=개인사업자] / 법인 소상공인 [구분=법인 소상공인] / 사업자 아님
+연체 중인 대출이 있나요? | 3개월 이상 [연체=90일 이상] / 3개월 미만 / 없음 [연체=10일 미만]</t>
   </si>
   <si>
     <t>새로 대출을 받으실 수 있습니다</t>
@@ -151,8 +151,8 @@
   </si>
   <si>
     <t xml:space="preserve">자금을 새로 빌리려고 문의하셨나요? | 예 / 아니요
-수수료나 선입금을 요구받으셨나요? | 예 / 아니요
-기존 대출 상환이 어려우신가요? | 예 / 아니요</t>
+수수료나 선입금을 요구받으셨나요? | 예 [키워드=보이스피싱] / 아니요
+기존 대출 상환이 어려우신가요? | 예 [키워드=신청 방법; 주제=신청·서류] / 아니요</t>
   </si>
   <si>
     <t>수수료를 내시면 빨리 처리됩니다</t>
@@ -189,9 +189,9 @@
 폐업·휴업도 부실우려차주일 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">가장 오래 연체된 대출은 얼마나 되었나요? | 3개월 이상 / 10~89일 / 10일 미만
-폐업했거나 6개월 이상 휴업 중인가요? | 예 / 아니요
-세금 체납으로 신용정보에 등재되었나요? | 예 / 아니요 / 모름</t>
+    <t xml:space="preserve">가장 오래 연체된 대출은 얼마나 되었나요? | 3개월 이상 [연체=90일 이상] / 10~89일 [연체=10~89일] / 10일 미만 [연체=10일 미만]
+폐업했거나 6개월 이상 휴업 중인가요? | 예 [키워드=폐업] / 아니요
+세금 체납으로 신용정보에 등재되었나요? | 예 [키워드=체납] / 아니요 / 모름</t>
   </si>
   <si>
     <t>10일만 연체돼도 부실차주예요</t>
@@ -225,9 +225,9 @@
 1년 성실상환하면 공공정보가 해제돼요.</t>
   </si>
   <si>
-    <t xml:space="preserve">신청할 금융회사에 예·적금이 있나요? | 있음 / 없음
-그 금융회사의 마이너스통장·신용카드를 쓰시나요? | 예 / 아니요
-3개월 이상 연체된 대출이 있나요? | 예 / 아니요 / 모름</t>
+    <t xml:space="preserve">신청할 금융회사에 예·적금이 있나요? | 있음 [키워드=상계] / 없음
+그 금융회사의 마이너스통장·신용카드를 쓰시나요? | 예 [키워드=신용카드] / 아니요
+3개월 이상 연체된 대출이 있나요? | 예 [키워드=공공정보; 연체=90일 이상] / 아니요 / 모름</t>
   </si>
   <si>
     <t>신청하셔도 아무 불이익이 없습니다</t>
@@ -258,9 +258,9 @@
 약정 후 회생 신청 시 효력 상실(제32조)</t>
   </si>
   <si>
-    <t xml:space="preserve">다른 채무조정을 이용 중인가요? | 개인회생 / 신복위 / 없음
+    <t xml:space="preserve">다른 채무조정을 이용 중인가요? | 개인회생 [키워드=개인회생] / 신복위 [키워드=신복위] / 없음
 소상공인·자영업자이신가요? | 예 / 아니요
-대출 종류는 무엇인가요? | 담보 / 무담보 / 둘 다</t>
+대출 종류는 무엇인가요? | 담보 [채무=담보] / 무담보 [채무=무담보] / 둘 다 [채무=둘 다]</t>
   </si>
   <si>
     <t>개인회생이나 신복위와 똑같은 제도예요</t>
@@ -293,8 +293,8 @@
 미협약 대출은 다른 제도를 안내해요.</t>
   </si>
   <si>
-    <t xml:space="preserve">대출 금융기관이 협약기관인지 확인하셨나요? | 확인함 / 모름
-연체 기간은 어느 정도인가요? | 3개월 이상 / 10~89일 / 연체 없음
+    <t xml:space="preserve">대출 금융기관이 협약기관인지 확인하셨나요? | 확인함 / 모름 [키워드=협약 금융기관]
+연체 기간은 어느 정도인가요? | 3개월 이상 [연체=90일 이상] / 10~89일 [연체=10~89일] / 연체 없음 [연체=10일 미만]
 그 대출이 신복위 협약기관 대출인가요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
@@ -330,9 +330,9 @@
 담보대출은 신복위 방문 접수입니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
 신청하려는 대출에 담보가 있나요? | 담보 / 무담보 / 둘 다
-홈페이지로 신청할 수 있으신가요? | 가능 / 어려움</t>
+홈페이지로 신청할 수 있으신가요? | 가능 / 어려움 [키워드=상담창구]</t>
   </si>
   <si>
     <t>모든 대출을 홈페이지에서 한 번에 신청하시면 돼요</t>
@@ -367,9 +367,9 @@
 담보대출은 신복위 중개형입니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
-대출 종류는 무엇인가요? | 신용·보증 / 담보 / 둘 다
-폐업·휴업 등 부실우려 요건에 해당하나요? | 예 / 아니요 / 모름</t>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
+대출 종류는 무엇인가요? | 신용·보증 [채무=무담보] / 담보 [채무=담보] / 둘 다 [채무=둘 다]
+폐업·휴업 등 부실우려 요건에 해당하나요? | 예 [키워드=부실우려] / 아니요 / 모름</t>
   </si>
   <si>
     <t>모든 대출은 캠코에서 직접 조정해 드려요</t>
@@ -401,9 +401,9 @@
 취소하면 3개월 재신청 불가(제16조)</t>
   </si>
   <si>
-    <t xml:space="preserve">전에 새출발기금을 신청한 적이 있나요? | 있음 / 없음
+    <t xml:space="preserve">전에 새출발기금을 신청한 적이 있나요? | 있음 [키워드=재신청] / 없음
 이전 약정이 부실우려 채무조정이었나요? | 예 / 아니요 / 해당 없음
-그 약정이 미납으로 실효되었나요? | 예 / 아니요 / 해당 없음</t>
+그 약정이 미납으로 실효되었나요? | 예 [키워드=미납실효] / 아니요 / 해당 없음</t>
   </si>
   <si>
     <t>언제든 다시 신청하시면 됩니다</t>
@@ -436,9 +436,9 @@
 폐업·휴업·세금 체납이면 해당돼요.</t>
   </si>
   <si>
-    <t xml:space="preserve">폐업했거나 6개월 이상 휴업 중인가요? | 예 / 아니요
-국세·지방세·관세 체납으로 등재되었나요? | 예 / 아니요 / 모름
-지금 연체 중인 대출이 있나요? | 있음 / 없음</t>
+    <t xml:space="preserve">폐업했거나 6개월 이상 휴업 중인가요? | 예 [키워드=폐업; 구분=폐업자] / 아니요
+국세·지방세·관세 체납으로 등재되었나요? | 예 [키워드=체납] / 아니요 / 모름
+지금 연체 중인 대출이 있나요? | 있음 / 없음 [연체=10일 미만]</t>
   </si>
   <si>
     <t>연체가 없으면 신청하실 수 없습니다</t>
@@ -469,9 +469,9 @@
 신청 단계면 취소 후 신청할 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">이용 중인 다른 제도가 있나요? | 신복위 / 개인회생 / 없음
+    <t xml:space="preserve">이용 중인 다른 제도가 있나요? | 신복위 [키워드=신복위] / 개인회생 [키워드=개인회생] / 없음
 그 제도는 어느 단계인가요? | 신청 단계 / 상환 중
-기존 신청을 취소할 생각이 있으신가요? | 예 / 아니요 / 고민 중</t>
+기존 신청을 취소할 생각이 있으신가요? | 예 [키워드=개인회생 폐지] / 아니요 / 고민 중</t>
   </si>
   <si>
     <t>개인회생 중이셔도 그냥 새출발기금 신청하시면 돼요</t>
@@ -505,8 +505,8 @@
 선택 동의를 다시 하셔야 할 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">신청한 지 2주가 지났나요? | 예 / 아니요
-선택적 개인정보 동의를 하셨나요? | 했음 / 안 했음 / 모름
+    <t xml:space="preserve">신청한 지 2주가 지났나요? | 예 [키워드=2주] / 아니요
+선택적 개인정보 동의를 하셨나요? | 했음 / 안 했음 [키워드=재동의] / 모름
 재동의 안내를 받으셨나요? | 받음 / 못 받음</t>
   </si>
   <si>
@@ -543,8 +543,8 @@
   </si>
   <si>
     <t xml:space="preserve">잘못 입력한 항목은 무엇인가요? | 금융자산 / 보증금 / 기타
-임시 채무조정안을 받으셨나요? | 받음 / 아직
-본 약정을 체결하셨나요? | 체결함 / 아직</t>
+임시 채무조정안을 받으셨나요? | 받음 [단계=채무조정안 제시] / 아직
+본 약정을 체결하셨나요? | 체결함 [키워드=재산 조사; 단계=약정] / 아직</t>
   </si>
   <si>
     <t>잘못 입력하셨으면 처음부터 다시 신청하셔야 해요</t>
@@ -576,9 +576,9 @@
 부채증명원 등 증빙을 첨부해 주세요.</t>
   </si>
   <si>
-    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
-부채증명원을 발급받으셨나요? | 있음 / 없음
-홈페이지 이의신청을 해 보셨나요? | 했음 / 안 했음</t>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
+부채증명원을 발급받으셨나요? | 있음 [키워드=부채증명원] / 없음
+홈페이지 이의신청을 해 보셨나요? | 했음 [키워드=이의신청] / 안 했음</t>
   </si>
   <si>
     <t>전산에 연체정보가 없으면 신청할 방법이 없어요</t>
@@ -616,8 +616,8 @@
 취소하면 3개월 재신청 불가(제16조)</t>
   </si>
   <si>
-    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 / 중개형 / 모름
-신청한 달의 다음 달 15일이 지났나요? | 지남 / 안 지남
+    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 [키워드=매입형] / 중개형 [키워드=중개형] / 모름
+신청한 달의 다음 달 15일이 지났나요? | 지남 [키워드=재신청] / 안 지남
 채무조정이 확정되었나요? | 확정됨 / 아직</t>
   </si>
   <si>
@@ -653,8 +653,8 @@
   </si>
   <si>
     <t xml:space="preserve">부실우려 약정이 미납으로 실효되었나요? | 예 / 아니요
-처음 신청 때 빠진 대출이 있나요? | 있음 / 없음
-빠진 대출이 협약 금융회사 대출인가요? | 예 / 아니요 / 모름</t>
+처음 신청 때 빠진 대출이 있나요? | 있음 [키워드=미신청 채무] / 없음
+빠진 대출이 협약 금융회사 대출인가요? | 예 / 아니요 / 모름 [키워드=협약 금융기관]</t>
   </si>
   <si>
     <t>처음에 신청 안 한 대출은 이제 넣을 수 없어요</t>
@@ -687,9 +687,9 @@
 폐업한 법인은 지원되지 않습니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인
-지금 영업 상태는 어떤가요? | 영업 중 / 휴업 / 폐업
-휴·폐업했다면 2020년 4월 이후인가요? | 예 / 아니요 / 해당 없음</t>
+    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 [구분=개인사업자] / 법인 소상공인 [구분=법인 소상공인]
+지금 영업 상태는 어떤가요? | 영업 중 / 휴업 [키워드=휴업] / 폐업 [키워드=폐업; 구분=폐업자]
+휴·폐업했다면 2020년 4월 이후인가요? | 예 / 아니요 [키워드=개인회생] / 해당 없음</t>
   </si>
   <si>
     <t>폐업한 법인도 신청하실 수 있습니다</t>
@@ -722,7 +722,7 @@
 부동산임대·금융·전문직 등이 해당돼요.</t>
   </si>
   <si>
-    <t xml:space="preserve">주업종은 무엇인가요? | 일반 업종 / 부동산임대·금융 / 전문직
+    <t xml:space="preserve">주업종은 무엇인가요? | 일반 업종 / 부동산임대·금융 [키워드=업종] / 전문직 [키워드=업종]
 정책자금 제외 업종인지 확인하셨나요? | 확인함 / 모름
 사업자등록증의 업종을 확인하셨나요? | 확인함 / 모름</t>
   </si>
@@ -758,9 +758,9 @@
 6개월 내 신규대출은 제외될 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">총 채무가 15억 원 이내인가요? | 예 / 아니요
-최근 6개월 안에 받은 대출이 있나요? | 있음 / 없음
-법인 대표자의 가계대출인가요? | 예 / 아니요 / 해당 없음</t>
+    <t xml:space="preserve">총 채무가 15억 원 이내인가요? | 예 / 아니요 [키워드=채무한도]
+최근 6개월 안에 받은 대출이 있나요? | 있음 [키워드=신규대출] / 없음
+법인 대표자의 가계대출인가요? | 예 [키워드=가계대출] / 아니요 / 해당 없음</t>
   </si>
   <si>
     <t>가지고 계신 대출은 전부 됩니다</t>
@@ -792,8 +792,8 @@
 부실우려차주는 골라서 신청할 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
-빼고 싶은 대출의 종류는 무엇인가요? | 신용·보증 / 담보
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
+빼고 싶은 대출의 종류는 무엇인가요? | 신용·보증 [채무=무담보] / 담보 [채무=담보]
 폐업·휴업 등 부실우려 요건에 해당하나요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
@@ -826,7 +826,7 @@
   <si>
     <t xml:space="preserve">담보 채무가 10억 원 이내인가요? | 예 / 아니요
 무담보 채무가 5억 원 이내인가요? | 예 / 아니요
-총 채무가 15억 원 이내인가요? | 예 / 아니요</t>
+총 채무가 15억 원 이내인가요? | 예 / 아니요 [키워드=개인회생]</t>
   </si>
   <si>
     <t>15억 안이면 됩니다</t>
@@ -856,8 +856,8 @@
 매각기일 잡힌 경매는 협의가 필요해요.</t>
   </si>
   <si>
-    <t xml:space="preserve">진행 중인 법조치는 무엇인가요? | 강제집행·경매 / 가압류 / 추심
-신청 전에 매각기일이 잡혔나요? | 예 / 아니요 / 모름
+    <t xml:space="preserve">진행 중인 법조치는 무엇인가요? | 강제집행·경매 [키워드=경매] / 가압류 [키워드=가압류] / 추심 [키워드=추심]
+신청 전에 매각기일이 잡혔나요? | 예 [키워드=매각기일] / 아니요 / 모름
 조치한 곳이 협약 금융기관인가요? | 협약기관 / 제3자 / 모름</t>
   </si>
   <si>
@@ -898,8 +898,8 @@
   </si>
   <si>
     <t xml:space="preserve">신청한 지 2주가 지났나요? | 예 / 아니요
-계속되는 추심은 무엇인가요? | 예·적금 상계 / 강제집행 / 독촉
-금융기관에 신청 사실을 알리셨나요? | 알림 / 안 알림</t>
+계속되는 추심은 무엇인가요? | 예·적금 상계 [키워드=상계] / 강제집행 [키워드=강제집행] / 독촉 [키워드=추심]
+금융기관에 신청 사실을 알리셨나요? | 알림 / 안 알림 [키워드=추심 중단]</t>
   </si>
   <si>
     <t>신청만 하면 모든 추심이 바로 멈춰요</t>
@@ -934,9 +934,9 @@
 중개형은 확정까지 2~3개월 걸려요.</t>
   </si>
   <si>
-    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 / 중개형 / 모름
-임시 채무조정안을 받으셨나요? | 받음 / 아직
-보증서 대출(보증부 채권)이 있나요? | 있음 / 없음 / 모름</t>
+    <t xml:space="preserve">신청한 채무조정 방식은 무엇인가요? | 매입형 [키워드=매입형] / 중개형 [키워드=중개형] / 모름
+임시 채무조정안을 받으셨나요? | 받음 [단계=채무조정안 제시] / 아직
+보증서 대출(보증부 채권)이 있나요? | 있음 [키워드=대위변제] / 없음 / 모름</t>
   </si>
   <si>
     <t>한 달이면 끝납니다</t>
@@ -975,9 +975,9 @@
 부실우려차주는 연체이자 감면(제19조)</t>
   </si>
   <si>
-    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 / 아니요
-감면받으려는 대출은 무엇인가요? | 무담보 / 담보
-부동산·예금 등 보유 재산이 있나요? | 있음 / 없음</t>
+    <t xml:space="preserve">연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
+감면받으려는 대출은 무엇인가요? | 무담보 [채무=무담보] / 담보 [채무=담보]
+부동산·예금 등 보유 재산이 있나요? | 있음 [키워드=재산가액] / 없음</t>
   </si>
   <si>
     <t>신청하시면 원금을 깎아 드립니다</t>
@@ -1012,8 +1012,8 @@
 상환기간은 최대 20년까지 가능해요.</t>
   </si>
   <si>
-    <t xml:space="preserve">해당하는 사항이 있나요? | 기초수급·중증장애 / 70세 이상 / 해당 없음
-총 채무가 1억 원 이하인가요? | 예 / 아니요
+    <t xml:space="preserve">해당하는 사항이 있나요? | 기초수급·중증장애 [키워드=취약계층] / 70세 이상 [키워드=취약계층] / 해당 없음
+총 채무가 1억 원 이하인가요? | 예 [키워드=저소득] / 아니요
 소득이 중위소득 60% 이하인가요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
@@ -1047,9 +1047,9 @@
 영업 중이면 추가 감면 대상이 아니에요.</t>
   </si>
   <si>
-    <t xml:space="preserve">폐업하셨나요? | 폐업 / 영업 중
-취업·재창업 교육을 이수하셨나요? | 이수 / 미이수
-연체 기간이 3개월 이상인가요? | 예 / 아니요</t>
+    <t xml:space="preserve">폐업하셨나요? | 폐업 [구분=폐업자] / 영업 중
+취업·재창업 교육을 이수하셨나요? | 이수 [키워드=재창업 교육] / 미이수
+연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요</t>
   </si>
   <si>
     <t>교육 받으시면 10% 더 깎아 드립니다</t>
@@ -1085,8 +1085,8 @@
 12회 이상 내고 일시상환 시 추가감면</t>
   </si>
   <si>
-    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환기간 변경 / 조기상환
-약정을 체결하셨나요? | 체결함 / 아직
+    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환기간 변경 [키워드=상환기간 변경] / 조기상환 [키워드=조기상환]
+약정을 체결하셨나요? | 체결함 [단계=약정] / 아직
 감면율 구간이 바뀌는지 확인하셨나요? | 확인함 / 모름</t>
   </si>
   <si>
@@ -1122,9 +1122,9 @@
 폐업자는 취업·재창업 시 1회 해제돼요.</t>
   </si>
   <si>
-    <t xml:space="preserve">첫 상환일부터 1년이 지났나요? | 예 / 아니요
-12회 이상 빠짐없이 납부하셨나요? | 예 / 아니요
-폐업 후 취업·재창업에 성공하셨나요? | 예 / 아니요 / 해당 없음</t>
+    <t xml:space="preserve">첫 상환일부터 1년이 지났나요? | 예 [키워드=공공정보 해제] / 아니요
+12회 이상 빠짐없이 납부하셨나요? | 예 [키워드=공공정보 해제] / 아니요
+폐업 후 취업·재창업에 성공하셨나요? | 예 [키워드=재창업] / 아니요 / 해당 없음</t>
   </si>
   <si>
     <t>약정하시면 바로 신용이 회복됩니다</t>
@@ -1155,7 +1155,7 @@
   <si>
     <t xml:space="preserve">신청 직전에 연체가 시작되었나요? | 예 / 아니요
 보유 재산이 채무보다 많은가요? | 예 / 아니요 / 모름
-심사 결과를 통보받으셨나요? | 받음 / 아직</t>
+심사 결과를 통보받으셨나요? | 받음 [키워드=도덕적 해이 이의신청] / 아직</t>
   </si>
   <si>
     <t>심사는 일부만 받으니 걱정 안 하셔도 돼요</t>
@@ -1189,8 +1189,8 @@
   </si>
   <si>
     <t xml:space="preserve">대출받은 금융기관을 알고 계신가요? | 앎 / 모름
-홈페이지 금융기관 조회를 해 보셨나요? | 했음 / 안 했음
-조회 결과 협약기관이었나요? | 예 / 아니요 / 조회 전</t>
+홈페이지 금융기관 조회를 해 보셨나요? | 했음 / 안 했음 [키워드=금융기관 조회]
+조회 결과 협약기관이었나요? | 예 / 아니요 [키워드=미협약] / 조회 전</t>
   </si>
   <si>
     <t>모든 금융기관 대출이 다 지원됩니다</t>
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t xml:space="preserve">약정 후 성실히 상환 중인가요? | 예 / 아니요
-관심 있는 지원은 무엇인가요? | 교육 / 자금 / 경영개선
+관심 있는 지원은 무엇인가요? | 교육 [키워드=재도전 교육] / 자금 [키워드=재도전 특별자금] / 경영개선 [키워드=경영환경개선]
 웹플랫폼 공지·알림톡을 받으셨나요? | 받음 / 못 받음</t>
   </si>
   <si>
@@ -1259,8 +1259,8 @@
 두 제도를 비교해 유리한 쪽을 고르세요.</t>
   </si>
   <si>
-    <t xml:space="preserve">개인회생은 어느 단계인가요? | 신청 중 / 인가 후 상환 중
-채무가 협약 금융기관 대출인가요? | 예 / 아니요 / 모름
+    <t xml:space="preserve">개인회생은 어느 단계인가요? | 신청 중 / 인가 후 상환 중 [키워드=개인회생]
+채무가 협약 금융기관 대출인가요? | 예 / 아니요 [키워드=미협약] / 모름
 개인사업자나 법인 소상공인인가요? | 예 / 아니요</t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
   <si>
     <t xml:space="preserve">운영하는 사업자는 어떻게 되나요? | 개인+법인 / 개인 2곳
 각각 사업자등록이 되어 있나요? | 예 / 아니요
-이미 한 사업자로 신청하셨나요? | 신청함 / 아직</t>
+이미 한 사업자로 신청하셨나요? | 신청함 [키워드=신청 횟수] / 아직</t>
   </si>
   <si>
     <t>사업장마다 따로 신청하시면 됩니다</t>
@@ -1318,8 +1318,8 @@
 사업자등록증이 있어야 합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">사업자등록증이 있나요? | 있음 / 없음
-지금 사업을 하고 계신가요? | 영업 중 / 휴업 / 폐업
+    <t xml:space="preserve">사업자등록증이 있나요? | 있음 / 없음 [키워드=지원 대상]
+지금 사업을 하고 계신가요? | 영업 중 / 휴업 / 폐업 [구분=폐업자]
 대출이 협약 금융기관 대출인가요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
@@ -1349,8 +1349,8 @@
 일반 소상공인확인서를 내 주세요.</t>
   </si>
   <si>
-    <t xml:space="preserve">소상공인확인서는 어디서 받으셨나요? | 중소기업현황정보시스템 / 소진공 / 모름
-법인 소상공인이신가요? | 예 / 아니요
+    <t xml:space="preserve">소상공인확인서는 어디서 받으셨나요? | 중소기업현황정보시스템 / 소진공 [키워드=소상공인확인서] / 모름
+법인 소상공인이신가요? | 예 [구분=법인 소상공인] / 아니요
 착한임대인 세제혜택용 확인서인가요? | 예 / 아니요 / 모름</t>
   </si>
   <si>
@@ -1385,7 +1385,7 @@
   <si>
     <t xml:space="preserve">같은 대출이 두 번 보이나요? | 예 / 아니요
 그 대출이 연체 중인가요? | 예 / 아니요
-약정 단계까지 진행되었나요? | 약정 전 / 약정 단계</t>
+약정 단계까지 진행되었나요? | 약정 전 / 약정 단계 [단계=약정]</t>
   </si>
   <si>
     <t>중복으로 나온 건 빚이 두 배라는 뜻이에요</t>
@@ -1417,9 +1417,9 @@
 부동의하면 기금이 채권을 매입해요.</t>
   </si>
   <si>
-    <t xml:space="preserve">담보 금융회사가 부동의했나요? | 부동의 / 동의 / 모름
+    <t xml:space="preserve">담보 금융회사가 부동의했나요? | 부동의 [키워드=부동의] / 동의 / 모름
 담보 종류는 무엇인가요? | 부동산 / 기타
-미협약기관 대출이 있나요? | 있음 / 없음 / 모름</t>
+미협약기관 대출이 있나요? | 있음 [키워드=미협약] / 없음 / 모름</t>
   </si>
   <si>
     <t>금융회사가 부동의하면 채무조정이 끝납니다</t>
@@ -1453,9 +1453,9 @@
 재산가치 이상 갚으면 해제될 수 있어요.</t>
   </si>
   <si>
-    <t xml:space="preserve">걸려 있는 법조치는 무엇인가요? | 가압류 / 압류·경매 / 기타
-채무조정 약정을 체결하셨나요? | 체결함 / 아직
-해당 재산가치 이상 갚을 여력이 있나요? | 있음 / 없음 / 모름</t>
+    <t xml:space="preserve">걸려 있는 법조치는 무엇인가요? | 가압류 [키워드=가압류] / 압류·경매 [키워드=경매] / 기타
+채무조정 약정을 체결하셨나요? | 체결함 [단계=약정] / 아직
+해당 재산가치 이상 갚을 여력이 있나요? | 있음 [키워드=재산가치] / 없음 / 모름</t>
   </si>
   <si>
     <t>신청하시면 가압류가 바로 풀립니다</t>
@@ -1509,8 +1509,8 @@
   </si>
   <si>
     <t xml:space="preserve">해당 채무는 무엇인가요? | 카드론 / 카드대금 / 현금서비스
-그 카드사가 협약 금융회사인가요? | 예 / 아니요 / 모름
-연체 기간은 어느 정도인가요? | 3개월 이상 / 3개월 미만 / 없음</t>
+그 카드사가 협약 금융회사인가요? | 예 / 아니요 / 모름 [키워드=협약 금융기관]
+연체 기간은 어느 정도인가요? | 3개월 이상 [연체=90일 이상] / 3개월 미만 / 없음</t>
   </si>
   <si>
     <t>카드빚은 지원되지 않습니다</t>
@@ -1539,8 +1539,8 @@
   </si>
   <si>
     <t xml:space="preserve">심사 결과를 통보받으셨나요? | 받음 / 아직
-이미 이의신청을 하셨나요? | 했음 / 안 했음
-재심사 결과를 받으셨나요? | 받음 / 아직 / 해당 없음</t>
+이미 이의신청을 하셨나요? | 했음 / 안 했음 [키워드=이의신청]
+재심사 결과를 받으셨나요? | 받음 [키워드=도덕적 해이] / 아직 / 해당 없음</t>
   </si>
   <si>
     <t>몇 번이고 다시 심사받으실 수 있습니다</t>
@@ -1569,8 +1569,8 @@
 은닉재산이 나오면 조정이 무효예요.</t>
   </si>
   <si>
-    <t xml:space="preserve">약정 후 새로 생긴 재산이 있나요? | 있음 / 없음
-신청 때 신고하지 않은 재산이 있나요? | 있음 / 없음
+    <t xml:space="preserve">약정 후 새로 생긴 재산이 있나요? | 있음 [키워드=재산 은닉] / 없음
+신청 때 신고하지 않은 재산이 있나요? | 있음 [키워드=효력 상실] / 없음
 재산 조사 안내를 받으셨나요? | 받음 / 못 받음</t>
   </si>
   <si>
@@ -1620,9 +1620,9 @@
 밀린 상환금을 먼저 내셔야 해요.</t>
   </si>
   <si>
-    <t xml:space="preserve">지금 분할상환금 연체가 있나요? | 있음 / 없음
-유예 사유는 무엇인가요? | 입원·질병 / 실직·휴폐업 / 출산·육아·기타
-대출 종류는 무엇인가요? | 무담보·동산담보 / 부동산담보</t>
+    <t xml:space="preserve">지금 분할상환금 연체가 있나요? | 있음 [키워드=효력 상실; 단계=연체·실효] / 없음
+유예 사유는 무엇인가요? | 입원·질병 [키워드=상환유예] / 실직·휴폐업 [키워드=상환유예] / 출산·육아·기타 [키워드=상환유예]
+대출 종류는 무엇인가요? | 무담보·동산담보 [채무=무담보] / 부동산담보 [채무=담보]</t>
   </si>
   <si>
     <t>사유 없이도 유예해 드립니다</t>
@@ -1676,9 +1676,9 @@
 회생·파산 신청도 상실 사유입니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">분할상환금이 몇 회 밀렸나요? | 3회 이상 / 1~2회 / 없음
+    <t xml:space="preserve">분할상환금이 몇 회 밀렸나요? | 3회 이상 [키워드=효력 부활; 단계=연체·실효] / 1~2회 / 없음
 효력 상실 예정 통지를 받으셨나요? | 받음 / 못 받음
-파산·회생·신복위를 신청하셨나요? | 예 / 아니요</t>
+파산·회생·신복위를 신청하셨나요? | 예 [키워드=재약정] / 아니요</t>
   </si>
   <si>
     <t>몇 달 밀려도 괜찮습니다</t>
@@ -1712,9 +1712,9 @@
 1회분만 내고 부활할 수도 있어요.(제34조)</t>
   </si>
   <si>
-    <t xml:space="preserve">효력 상실 후 6개월이 지났나요? | 지남 / 안 지남
-상실 사유가 3개월 이상 연체인가요? | 예 / 아니요
-약정 후 새로 취득한 재산이 있나요? | 있음 / 없음</t>
+    <t xml:space="preserve">효력 상실 후 6개월이 지났나요? | 지남 [키워드=재약정] / 안 지남
+상실 사유가 3개월 이상 연체인가요? | 예 [연체=90일 이상] / 아니요
+약정 후 새로 취득한 재산이 있나요? | 있음 [키워드=재약정] / 없음</t>
   </si>
   <si>
     <t>언제든지 부활할 수 있습니다</t>
@@ -1751,7 +1751,7 @@
 재약정에는 거치기간이 없습니다.(제35조)</t>
   </si>
   <si>
-    <t xml:space="preserve">효력 상실 사유는 무엇인가요? | 연체 / 자료허위·재산은닉 / 파산·회생 신청
+    <t xml:space="preserve">효력 상실 사유는 무엇인가요? | 연체 [키워드=효력 부활] / 자료허위·재산은닉 / 파산·회생 신청
 그 사유가 해소되었나요? | 해소됨 / 아직 / 해당 없음
 차주 구분은 무엇인가요? | 부실차주 / 부실우려차주 / 모름</t>
   </si>
@@ -1794,9 +1794,9 @@
 최대 1년, 특례대상은 3년(제21조)</t>
   </si>
   <si>
-    <t xml:space="preserve">최초 약정 단계인가요? | 예 / 이미 약정함
-해당하는 사항이 있나요? | 취약계층 특례 / 저소득 / 해당 없음
-담보는 어떻게 되나요? | 부동산담보 / 무담보 / 둘 다</t>
+    <t xml:space="preserve">최초 약정 단계인가요? | 예 / 이미 약정함 [키워드=상환유예; 단계=상환 중]
+해당하는 사항이 있나요? | 취약계층 특례 [키워드=취약계층] / 저소득 [키워드=취약계층] / 해당 없음
+담보는 어떻게 되나요? | 부동산담보 [채무=담보] / 무담보 [채무=무담보] / 둘 다 [채무=둘 다]</t>
   </si>
   <si>
     <t>거치기간은 언제든 다시 받을 수 있습니다</t>
@@ -1840,9 +1840,9 @@
 CMS 자동이체 수수료는 기금 부담이에요.</t>
   </si>
   <si>
-    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환일 변경 / 납부 방법 / 일시상환
+    <t xml:space="preserve">원하시는 것은 무엇인가요? | 상환일 변경 [키워드=상환일 변경] / 납부 방법 [키워드=납부 방법] / 일시상환 [키워드=조기상환]
 상환일을 바꾼 적이 있나요? | 있음 / 없음
-지금 연체가 있나요? | 있음 / 없음</t>
+지금 연체가 있나요? | 있음 [키워드=효력 상실; 단계=연체·실효] / 없음</t>
   </si>
   <si>
     <t>상환일은 몇 번이든 바꿀 수 있습니다</t>
@@ -1883,7 +1883,7 @@
 정보 이용 동의서도 함께 받습니다.(제12조)</t>
   </si>
   <si>
-    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 / 법인 소상공인 / 특고·프리랜서
+    <t xml:space="preserve">사업자 형태는 무엇인가요? | 개인사업자 [구분=개인사업자] / 법인 소상공인 [구분=법인 소상공인] / 특고·프리랜서 [키워드=프리랜서]
 상환 방식은 무엇인가요? | 분할상환 / 일시상환
 신분증·사업자등록증을 준비하셨나요? | 준비함 / 아직</t>
   </si>
@@ -1927,7 +1927,7 @@
   <si>
     <t xml:space="preserve">누가 신청하시나요? | 본인 / 대리인
 대리인이라면 위임장이 있나요? | 있음 / 없음 / 해당 없음
-채무자 아닌 분이 대신 갚으려 하시나요? | 예 / 아니요</t>
+채무자 아닌 분이 대신 갚으려 하시나요? | 예 [키워드=대위변제] / 아니요</t>
   </si>
   <si>
     <t>가족이면 위임장 없이 대신 신청돼요</t>
@@ -1976,9 +1976,9 @@
 세부 산정기준표는 공개되지 않아요.</t>
   </si>
   <si>
-    <t xml:space="preserve">보유 재산이 있나요? | 있음 / 없음
-연체 기간이 3개월 이상인가요? | 예 / 아니요
-사회취약계층에 해당하나요? | 예 / 아니요 / 모름</t>
+    <t xml:space="preserve">보유 재산이 있나요? | 있음 [키워드=회수가능액] / 없음
+연체 기간이 3개월 이상인가요? | 예 [연체=90일 이상] / 아니요
+사회취약계층에 해당하나요? | 예 [키워드=취약계층] / 아니요 / 모름</t>
   </si>
   <si>
     <t>재산은 감면 계산과 상관없어요</t>
@@ -2077,7 +2077,7 @@
     <t>민원인을 안내할 담당 창구. 모든 줄에 채운다. 원문에 기관이 나오면 그 기관을, 없으면 새출발기금 콜센터를 적었다(2026-10-29 초안, 담당자 검토 필요).</t>
   </si>
   <si>
-    <t>정확히 안내하려고 민원인에게 물어볼 질문 3개(칸 안에서 줄바꿈으로 구분). 한 줄은 "질문 | 선택지 / 선택지" 꼴이고 선택지는 2~3개. FAQ 답변·요강 조문에 나온 조건만 묻고 이름·전화번호·고객번호 등 개인정보는 묻지 않는다. 비워 두면 data/default-questions.json의 주제별 기본 질문이 나온다(2026-10-29 초안, 담당자 검토 필요).</t>
+    <t>정확히 안내하려고 민원인에게 물어볼 질문 3개(칸 안에서 줄바꿈으로 구분). 한 줄은 "질문 | 선택지 / 선택지" 꼴이고 선택지는 2~3개. 선택지 뒤 [키워드=…; 단계=…]는 그 답을 누르면 바뀔 키워드와 상황 값(주제·연체·채무·단계·구분)이고, 대괄호가 없는 선택지는 누를 수 없다. FAQ 답변·요강 조문에 나온 조건만 묻고 이름·전화번호·고객번호 등 개인정보는 묻지 않는다. 비워 두면 data/default-questions.json의 주제별 기본 질문이 나온다(2026-10-29 초안, 담당자 검토 필요).</t>
   </si>
   <si>
     <t>조문</t>
